--- a/target/test-classes/data/User_Data.xlsx
+++ b/target/test-classes/data/User_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Zalo\DATN\Automation_AFF\src\test\resources\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB5DB951-7050-4BD0-944A-542DD8FA0F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E81E6C-6389-4419-80F6-74E668DE9254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="-120" windowWidth="28590" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="330" yWindow="-120" windowWidth="28590" windowHeight="16440" tabRatio="920" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -18,22 +18,26 @@
     <sheet name="Search" sheetId="3" r:id="rId3"/>
     <sheet name="Change_Pass" sheetId="4" r:id="rId4"/>
     <sheet name="Forgot_Pass" sheetId="5" r:id="rId5"/>
-    <sheet name="Information" sheetId="6" r:id="rId6"/>
-    <sheet name="SCart" sheetId="7" r:id="rId7"/>
-    <sheet name="SCart_Add" sheetId="8" r:id="rId8"/>
-    <sheet name="SCart_Upd" sheetId="9" r:id="rId9"/>
-    <sheet name="SCart_Del" sheetId="10" r:id="rId10"/>
-    <sheet name="Order" sheetId="11" r:id="rId11"/>
-    <sheet name="Indrect_Commission" sheetId="12" r:id="rId12"/>
-    <sheet name="Direct_Commission" sheetId="13" r:id="rId13"/>
-    <sheet name="Lưu ý" sheetId="14" r:id="rId14"/>
+    <sheet name="Informa1tion" sheetId="6" r:id="rId6"/>
+    <sheet name="Information" sheetId="18" r:id="rId7"/>
+    <sheet name="SCart" sheetId="7" r:id="rId8"/>
+    <sheet name="SCart_Add" sheetId="8" r:id="rId9"/>
+    <sheet name="SCart_Upd" sheetId="9" r:id="rId10"/>
+    <sheet name="SCart_Del" sheetId="10" r:id="rId11"/>
+    <sheet name="Order" sheetId="17" r:id="rId12"/>
+    <sheet name="Order_Indrect" sheetId="15" r:id="rId13"/>
+    <sheet name="Order_Bank" sheetId="11" r:id="rId14"/>
+    <sheet name="Order_Direct" sheetId="16" r:id="rId15"/>
+    <sheet name="Indrect_Commission" sheetId="12" r:id="rId16"/>
+    <sheet name="Direct_Commission" sheetId="13" r:id="rId17"/>
+    <sheet name="Lưu ý" sheetId="14" r:id="rId18"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="703">
   <si>
     <t>Cần để ý :</t>
   </si>
@@ -1388,25 +1392,10 @@
     <t>Kiểm tra nhập số điện thoại không hợp lệ</t>
   </si>
   <si>
-    <t>Kiểm tra chọn ngân hàng khi thanh toán</t>
-  </si>
-  <si>
-    <t>Kiểm tra phương thức thanh toán bằng ngân hàng</t>
-  </si>
-  <si>
-    <t>Kiểm tra phương thức thanh toán trực tiếp</t>
-  </si>
-  <si>
-    <t>Kiểm tra phương thức thanh toán gián tiếp</t>
-  </si>
-  <si>
     <t>Kiểm tra hiển thị tổng tiền</t>
   </si>
   <si>
     <t>Kiểm tra nhấn nút "ĐẶT HÀNG" với đủ thông tin</t>
-  </si>
-  <si>
-    <t>Kiểm tra nhấn nút "ĐẶT HÀNG" với các thông tin hợp lệ</t>
   </si>
   <si>
     <t>Xóa 1 sản phẩm</t>
@@ -1571,9 +1560,6 @@
     <t>Không nhập các trường không bắt buộc</t>
   </si>
   <si>
-    <t>Nhập tất cả hợp lệ</t>
-  </si>
-  <si>
     <t>PassNew</t>
   </si>
   <si>
@@ -2175,13 +2161,61 @@
   </si>
   <si>
     <t>enex zlda lgog vyvf</t>
+  </si>
+  <si>
+    <t>033203012145</t>
+  </si>
+  <si>
+    <t>033203012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           </t>
+  </si>
+  <si>
+    <t>Tân Lâp</t>
+  </si>
+  <si>
+    <t>Yên Mỹ</t>
+  </si>
+  <si>
+    <t>Abc</t>
+  </si>
+  <si>
+    <t>022222122</t>
+  </si>
+  <si>
+    <t>10/01/2001</t>
+  </si>
+  <si>
+    <t>MB</t>
+  </si>
+  <si>
+    <t>1172828282</t>
+  </si>
+  <si>
+    <t>Cập nhập thông tin thành công</t>
+  </si>
+  <si>
+    <t>http://localhost:4200/user-information</t>
+  </si>
+  <si>
+    <t>Vui lòng chấp thuận điều kiện giao dịch</t>
+  </si>
+  <si>
+    <t>PHƯƠNG THỨC THANH TOÁN</t>
+  </si>
+  <si>
+    <t>Kiểm tra không chọn ngân hàng khi thanh toán</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2222,12 +2256,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2238,6 +2266,95 @@
       <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2267,7 +2384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2308,17 +2425,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -2333,23 +2444,144 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2656,7 +2888,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.140625" style="11" bestFit="1" customWidth="1"/>
@@ -2673,295 +2905,304 @@
         <v>5</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>435</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="46" t="s">
+        <v>671</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>489</v>
+      </c>
+      <c r="E2" s="47" t="s">
+        <v>567</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>672</v>
+      </c>
+      <c r="G2" s="45" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="40"/>
+      <c r="B3" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>488</v>
+      </c>
+      <c r="D3" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="E3" s="42" t="s">
+        <v>567</v>
+      </c>
+      <c r="F3" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="G3" s="40" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="40" t="s">
+        <v>673</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>626</v>
+      </c>
+      <c r="D4" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="E4" s="42" t="s">
+        <v>567</v>
+      </c>
+      <c r="F4" s="40" t="s">
+        <v>494</v>
+      </c>
+      <c r="G4" s="40" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
+        <v>674</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>626</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="E5" s="42" t="s">
+        <v>567</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>495</v>
+      </c>
+      <c r="G5" s="40" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="40" t="s">
+        <v>675</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>626</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="E6" s="42" t="s">
+        <v>567</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>496</v>
+      </c>
+      <c r="G6" s="40" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="40" t="s">
+        <v>676</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>626</v>
+      </c>
+      <c r="D7" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="E7" s="42" t="s">
+        <v>567</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>497</v>
+      </c>
+      <c r="G7" s="40" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="40" t="s">
         <v>677</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="B8" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>626</v>
+      </c>
+      <c r="D8" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>567</v>
+      </c>
+      <c r="F8" s="40" t="s">
+        <v>498</v>
+      </c>
+      <c r="G8" s="40" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="40" t="s">
+        <v>636</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>626</v>
+      </c>
+      <c r="D9" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>567</v>
+      </c>
+      <c r="F9" s="40" t="s">
+        <v>499</v>
+      </c>
+      <c r="G9" s="40" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="40" t="s">
         <v>678</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4" t="s">
+      <c r="B10" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>494</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>497</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="C10" s="41" t="s">
         <v>679</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>500</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="D10" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>567</v>
+      </c>
+      <c r="F10" s="40" t="s">
         <v>680</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="G10" s="40" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="43"/>
+      <c r="C11" s="41" t="s">
+        <v>641</v>
+      </c>
+      <c r="D11" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>567</v>
+      </c>
+      <c r="F11" s="40" t="s">
+        <v>642</v>
+      </c>
+      <c r="G11" s="40" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="40" t="s">
+        <v>673</v>
+      </c>
+      <c r="C12" s="41" t="s">
         <v>681</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="D12" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>567</v>
+      </c>
+      <c r="F12" s="40" t="s">
+        <v>646</v>
+      </c>
+      <c r="G12" s="40" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="40" t="s">
         <v>682</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="C13" s="41" t="s">
+        <v>681</v>
+      </c>
+      <c r="D13" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="E13" s="42" t="s">
+        <v>567</v>
+      </c>
+      <c r="F13" s="40" t="s">
         <v>683</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>684</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>685</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>686</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="10" t="s">
-        <v>647</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>648</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>679</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>687</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>652</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>688</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>687</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>689</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>498</v>
-      </c>
+      <c r="G13" s="40" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="44"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2969,6 +3210,89 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="K1:L30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="10" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="51.42578125" style="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1" s="4" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="2" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K2" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="3" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K3" s="4" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="4" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K4" s="4" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="5" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L25" s="12"/>
+    </row>
+    <row r="26" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L26" s="4"/>
+    </row>
+    <row r="27" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L27" s="4"/>
+    </row>
+    <row r="28" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L28" s="4"/>
+    </row>
+    <row r="29" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L29" s="4"/>
+    </row>
+    <row r="30" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L30" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -2988,18 +3312,22 @@
     </row>
     <row r="2" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K2" s="4" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
     </row>
     <row r="3" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K3" s="4" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="4" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>455</v>
+      </c>
+    </row>
+    <row r="4" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K4" s="11">
+        <v>2</v>
+      </c>
+    </row>
     <row r="5" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3028,7 +3356,67 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{437290B0-5E81-4A05-A34E-6AB615E82B9D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="11" max="11" width="9.140625" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC05FA6D-AE89-4E2F-AB13-40AB94C75E25}">
+  <dimension ref="N1:N7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="14" max="14" width="36.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N1" s="10" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="2" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N2" s="10" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="3" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N3" s="10" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N4" s="10" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="5" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N5" s="10" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="6" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N6" s="10" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N7" s="10" t="s">
+        <v>451</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -3052,83 +3440,90 @@
       <c r="N2" s="10" t="s">
         <v>446</v>
       </c>
-      <c r="O2" s="10"/>
+      <c r="O2" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="P2" s="10"/>
     </row>
     <row r="3" spans="14:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N3" s="10" t="s">
         <v>447</v>
       </c>
-      <c r="O3" s="10"/>
+      <c r="O3" s="10" t="s">
+        <v>492</v>
+      </c>
       <c r="P3" s="10"/>
     </row>
     <row r="4" spans="14:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N4" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="O4" s="10"/>
+      <c r="O4" s="10" t="s">
+        <v>492</v>
+      </c>
       <c r="P4" s="10"/>
     </row>
     <row r="5" spans="14:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N5" s="10" t="s">
         <v>449</v>
       </c>
-      <c r="O5" s="10"/>
+      <c r="O5" s="10" t="s">
+        <v>492</v>
+      </c>
       <c r="P5" s="10"/>
     </row>
     <row r="6" spans="14:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N6" s="10" t="s">
         <v>450</v>
       </c>
-      <c r="O6" s="10"/>
+      <c r="O6" s="10" t="s">
+        <v>492</v>
+      </c>
       <c r="P6" s="10"/>
     </row>
     <row r="7" spans="14:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N7" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="O7" s="10"/>
+        <v>701</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>492</v>
+      </c>
       <c r="P7" s="10"/>
     </row>
     <row r="8" spans="14:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N8" s="10" t="s">
-        <v>452</v>
-      </c>
-      <c r="O8" s="10"/>
+        <v>451</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="P8" s="10"/>
     </row>
     <row r="9" spans="14:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N9" s="10" t="s">
-        <v>453</v>
-      </c>
-      <c r="O9" s="10"/>
+        <v>452</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="P9" s="10"/>
     </row>
     <row r="10" spans="14:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N10" s="10" t="s">
-        <v>454</v>
-      </c>
+      <c r="N10" s="10"/>
       <c r="O10" s="10"/>
       <c r="P10" s="10"/>
     </row>
     <row r="11" spans="14:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N11" s="10" t="s">
-        <v>455</v>
-      </c>
       <c r="O11" s="10"/>
       <c r="P11" s="10"/>
     </row>
-    <row r="12" spans="14:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N12" s="10" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="13" spans="14:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N13" s="10" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="14" spans="14:16" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="14:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="14:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="14:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N14" s="1">
+        <v>12</v>
+      </c>
+    </row>
     <row r="15" spans="14:16" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O15" s="10"/>
       <c r="P15" s="10"/>
@@ -3138,7 +3533,86 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3906E0C-2913-4420-B5BB-E88615191874}">
+  <dimension ref="N1:O8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="13" width="9.140625" style="30"/>
+    <col min="14" max="14" width="51.42578125" style="30" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N1" s="39" t="s">
+        <v>435</v>
+      </c>
+      <c r="O1" s="30" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="2" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N2" s="39" t="s">
+        <v>446</v>
+      </c>
+      <c r="O2" s="30" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="3" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N3" s="39" t="s">
+        <v>447</v>
+      </c>
+      <c r="O3" s="30" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="4" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N4" s="39" t="s">
+        <v>448</v>
+      </c>
+      <c r="O4" s="30" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="5" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N5" s="39" t="s">
+        <v>449</v>
+      </c>
+      <c r="O5" s="30" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="6" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N6" s="39" t="s">
+        <v>450</v>
+      </c>
+      <c r="O6" s="30" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="7" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N7" s="39" t="s">
+        <v>451</v>
+      </c>
+      <c r="O7" s="30" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="8" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N8" s="39" t="s">
+        <v>452</v>
+      </c>
+      <c r="O8" s="39" t="s">
+        <v>514</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -3146,122 +3620,162 @@
   <dimension ref="M1:P16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="12" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="75" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="12" width="14.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="44" style="38" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.140625" style="38" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="13:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1" spans="13:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M1" s="35" t="s">
+        <v>435</v>
+      </c>
+      <c r="N1" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
     <row r="2" spans="13:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M2" s="10" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="3" spans="13:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M3" s="10" t="s">
+      <c r="M2" s="35" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="4" spans="13:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M4" s="10" t="s">
+      <c r="N2" s="38" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="3" spans="13:16" s="38" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M3" s="35" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="5" spans="13:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M5" s="10" t="s">
+      <c r="N3" s="38" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="4" spans="13:16" s="38" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M4" s="35" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="6" spans="13:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M6" s="10" t="s">
+      <c r="N4" s="38" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="5" spans="13:16" s="38" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M5" s="35" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="7" spans="13:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M7" s="10" t="s">
+      <c r="N5" s="38" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="6" spans="13:16" s="38" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M6" s="35" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="8" spans="13:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M8" s="10" t="s">
+      <c r="N6" s="38" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="7" spans="13:16" s="38" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M7" s="35" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="9" spans="13:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M9" s="10" t="s">
+      <c r="N7" s="38" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="8" spans="13:16" s="38" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M8" s="35" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="10" spans="13:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-    </row>
-    <row r="11" spans="13:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-    </row>
-    <row r="12" spans="13:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-    </row>
-    <row r="13" spans="13:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-    </row>
-    <row r="14" spans="13:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-    </row>
-    <row r="15" spans="13:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-    </row>
-    <row r="16" spans="13:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
+      <c r="N8" s="38" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="9" spans="13:16" s="38" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
+    </row>
+    <row r="10" spans="13:16" s="38" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O10" s="35"/>
+      <c r="P10" s="35"/>
+    </row>
+    <row r="11" spans="13:16" s="38" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N11" s="35"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="35"/>
+    </row>
+    <row r="12" spans="13:16" s="38" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="35"/>
+    </row>
+    <row r="13" spans="13:16" s="38" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="35"/>
+    </row>
+    <row r="14" spans="13:16" s="38" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+    </row>
+    <row r="15" spans="13:16" s="38" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N15" s="35"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="35"/>
+    </row>
+    <row r="16" spans="13:16" s="38" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N16" s="35"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="K1:K4"/>
+  <dimension ref="K1:L4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="10" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="10" width="9.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="11:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K1" s="4" t="s">
+    <row r="1" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1" s="26" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="2" spans="11:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K2" s="4" t="s">
+      <c r="L1" s="27" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="2" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K2" s="26" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="3" spans="11:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K3" s="4" t="s">
+      <c r="L2" s="27" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="3" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K3" s="26" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="4" spans="11:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K4" s="4" t="s">
+      <c r="L3" s="27" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="4" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K4" s="26" t="s">
         <v>438</v>
+      </c>
+      <c r="L4" s="27" t="s">
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -3269,7 +3783,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -3344,12 +3858,12 @@
         <v>8</v>
       </c>
       <c r="I15" s="6"/>
-      <c r="J15" s="26" t="s">
+      <c r="J15" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
       <c r="N15" s="7"/>
       <c r="O15" s="8">
         <v>1</v>
@@ -3375,12 +3889,12 @@
         <v>14</v>
       </c>
       <c r="I16" s="6"/>
-      <c r="J16" s="26" t="s">
+      <c r="J16" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="26"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
       <c r="N16" s="7"/>
       <c r="O16" s="8">
         <v>50</v>
@@ -3401,12 +3915,12 @@
         <v>19</v>
       </c>
       <c r="I17" s="6"/>
-      <c r="J17" s="26" t="s">
+      <c r="J17" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="26"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
       <c r="N17" s="7"/>
       <c r="O17" s="8">
         <v>51</v>
@@ -3430,12 +3944,12 @@
         <v>25</v>
       </c>
       <c r="I18" s="6"/>
-      <c r="J18" s="26" t="s">
+      <c r="J18" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K18" s="26"/>
-      <c r="L18" s="26"/>
-      <c r="M18" s="26"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
       <c r="N18" s="7"/>
       <c r="O18" s="8">
         <v>52</v>
@@ -3453,12 +3967,12 @@
         <v>29</v>
       </c>
       <c r="I19" s="6"/>
-      <c r="J19" s="26" t="s">
+      <c r="J19" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="K19" s="26"/>
-      <c r="L19" s="26"/>
-      <c r="M19" s="26"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="22"/>
       <c r="N19" s="7"/>
       <c r="O19" s="8">
         <v>53</v>
@@ -3507,12 +4021,12 @@
       <c r="R21" s="6"/>
     </row>
     <row r="22" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
       <c r="I22" s="6"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -3531,12 +4045,12 @@
       <c r="R22" s="6"/>
     </row>
     <row r="23" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
       <c r="F23" s="4" t="s">
         <v>42</v>
       </c>
@@ -3554,12 +4068,12 @@
       <c r="R23" s="6"/>
     </row>
     <row r="24" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
       <c r="I24" s="6"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -3578,12 +4092,12 @@
       <c r="R24" s="6"/>
     </row>
     <row r="25" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
       <c r="I25" s="6"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -3602,12 +4116,12 @@
       <c r="R25" s="6"/>
     </row>
     <row r="26" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
       <c r="I26" s="6"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -3626,17 +4140,17 @@
       <c r="R26" s="6"/>
     </row>
     <row r="27" spans="2:18" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
       <c r="I27" s="6"/>
-      <c r="J27" s="25"/>
-      <c r="K27" s="25"/>
-      <c r="L27" s="25"/>
-      <c r="M27" s="25"/>
+      <c r="J27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="24"/>
+      <c r="M27" s="24"/>
       <c r="N27" s="7"/>
       <c r="O27" s="8">
         <v>61</v>
@@ -3650,17 +4164,17 @@
       <c r="R27" s="6"/>
     </row>
     <row r="28" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
       <c r="I28" s="6"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="26"/>
-      <c r="M28" s="26"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22"/>
       <c r="N28" s="9"/>
       <c r="O28" s="8">
         <v>62</v>
@@ -3675,10 +4189,10 @@
     </row>
     <row r="29" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I29" s="6"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-      <c r="M29" s="26"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="22"/>
       <c r="N29" s="9"/>
       <c r="O29" s="8">
         <v>63</v>
@@ -3693,10 +4207,10 @@
     </row>
     <row r="30" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I30" s="6"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="26"/>
-      <c r="L30" s="26"/>
-      <c r="M30" s="26"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="22"/>
       <c r="N30" s="9"/>
       <c r="O30" s="8">
         <v>64</v>
@@ -3711,10 +4225,10 @@
     </row>
     <row r="31" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I31" s="6"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-      <c r="M31" s="26"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="22"/>
       <c r="N31" s="9"/>
       <c r="O31" s="8">
         <v>65</v>
@@ -3729,10 +4243,10 @@
     </row>
     <row r="32" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I32" s="6"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="26"/>
-      <c r="M32" s="26"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="22"/>
       <c r="N32" s="9"/>
       <c r="O32" s="8">
         <v>66</v>
@@ -3747,10 +4261,10 @@
     </row>
     <row r="33" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I33" s="6"/>
-      <c r="J33" s="26"/>
-      <c r="K33" s="26"/>
-      <c r="L33" s="26"/>
-      <c r="M33" s="26"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="22"/>
       <c r="N33" s="9"/>
       <c r="O33" s="8">
         <v>67</v>
@@ -3765,10 +4279,10 @@
     </row>
     <row r="34" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I34" s="6"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-      <c r="M34" s="26"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="22"/>
       <c r="N34" s="9"/>
       <c r="O34" s="8">
         <v>68</v>
@@ -3783,10 +4297,10 @@
     </row>
     <row r="35" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I35" s="6"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="26"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="22"/>
       <c r="N35" s="9"/>
       <c r="O35" s="8">
         <v>69</v>
@@ -3801,10 +4315,10 @@
     </row>
     <row r="36" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I36" s="6"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="26"/>
-      <c r="L36" s="26"/>
-      <c r="M36" s="26"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="22"/>
       <c r="N36" s="9"/>
       <c r="O36" s="8">
         <v>70</v>
@@ -3822,10 +4336,10 @@
         <v>76</v>
       </c>
       <c r="I37" s="6"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="26"/>
-      <c r="L37" s="26"/>
-      <c r="M37" s="26"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="22"/>
       <c r="N37" s="9"/>
       <c r="O37" s="8">
         <v>71</v>
@@ -3840,10 +4354,10 @@
     </row>
     <row r="38" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I38" s="6"/>
-      <c r="J38" s="25"/>
-      <c r="K38" s="25"/>
-      <c r="L38" s="25"/>
-      <c r="M38" s="25"/>
+      <c r="J38" s="24"/>
+      <c r="K38" s="24"/>
+      <c r="L38" s="24"/>
+      <c r="M38" s="24"/>
       <c r="N38" s="9"/>
       <c r="O38" s="8">
         <v>72</v>
@@ -3858,10 +4372,10 @@
     </row>
     <row r="39" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I39" s="6"/>
-      <c r="J39" s="25"/>
-      <c r="K39" s="25"/>
-      <c r="L39" s="25"/>
-      <c r="M39" s="25"/>
+      <c r="J39" s="24"/>
+      <c r="K39" s="24"/>
+      <c r="L39" s="24"/>
+      <c r="M39" s="24"/>
       <c r="N39" s="9"/>
       <c r="O39" s="8">
         <v>73</v>
@@ -3876,10 +4390,10 @@
     </row>
     <row r="40" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I40" s="6"/>
-      <c r="J40" s="25"/>
-      <c r="K40" s="25"/>
-      <c r="L40" s="25"/>
-      <c r="M40" s="25"/>
+      <c r="J40" s="24"/>
+      <c r="K40" s="24"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="24"/>
       <c r="N40" s="7"/>
       <c r="O40" s="8">
         <v>74</v>
@@ -3894,10 +4408,10 @@
     </row>
     <row r="41" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I41" s="6"/>
-      <c r="J41" s="25"/>
-      <c r="K41" s="25"/>
-      <c r="L41" s="25"/>
-      <c r="M41" s="25"/>
+      <c r="J41" s="24"/>
+      <c r="K41" s="24"/>
+      <c r="L41" s="24"/>
+      <c r="M41" s="24"/>
       <c r="N41" s="7"/>
       <c r="O41" s="8">
         <v>75</v>
@@ -3912,12 +4426,12 @@
     </row>
     <row r="42" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I42" s="6"/>
-      <c r="J42" s="26" t="s">
+      <c r="J42" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="K42" s="26"/>
-      <c r="L42" s="26"/>
-      <c r="M42" s="26"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="22"/>
       <c r="N42" s="9"/>
       <c r="O42" s="8">
         <v>76</v>
@@ -3931,13 +4445,13 @@
       <c r="R42" s="6"/>
     </row>
     <row r="43" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I43" s="27"/>
-      <c r="J43" s="26" t="s">
+      <c r="I43" s="25"/>
+      <c r="J43" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="K43" s="26"/>
-      <c r="L43" s="26"/>
-      <c r="M43" s="26"/>
+      <c r="K43" s="22"/>
+      <c r="L43" s="22"/>
+      <c r="M43" s="22"/>
       <c r="N43" s="9"/>
       <c r="O43" s="8">
         <v>77</v>
@@ -3951,13 +4465,13 @@
       <c r="R43" s="6"/>
     </row>
     <row r="44" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I44" s="28"/>
-      <c r="J44" s="26" t="s">
+      <c r="I44" s="23"/>
+      <c r="J44" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="K44" s="26"/>
-      <c r="L44" s="26"/>
-      <c r="M44" s="26"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="22"/>
+      <c r="M44" s="22"/>
       <c r="N44" s="9"/>
       <c r="O44" s="8">
         <v>78</v>
@@ -3971,13 +4485,13 @@
       <c r="R44" s="6"/>
     </row>
     <row r="45" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I45" s="28"/>
-      <c r="J45" s="26" t="s">
+      <c r="I45" s="23"/>
+      <c r="J45" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="K45" s="26"/>
-      <c r="L45" s="26"/>
-      <c r="M45" s="26"/>
+      <c r="K45" s="22"/>
+      <c r="L45" s="22"/>
+      <c r="M45" s="22"/>
       <c r="N45" s="9"/>
       <c r="O45" s="8">
         <v>79</v>
@@ -3991,13 +4505,13 @@
       <c r="R45" s="6"/>
     </row>
     <row r="46" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I46" s="28"/>
-      <c r="J46" s="26" t="s">
+      <c r="I46" s="23"/>
+      <c r="J46" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="K46" s="26"/>
-      <c r="L46" s="26"/>
-      <c r="M46" s="26"/>
+      <c r="K46" s="22"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="22"/>
       <c r="N46" s="9"/>
       <c r="O46" s="8">
         <v>80</v>
@@ -4011,13 +4525,13 @@
       <c r="R46" s="6"/>
     </row>
     <row r="47" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I47" s="28"/>
-      <c r="J47" s="26" t="s">
+      <c r="I47" s="23"/>
+      <c r="J47" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="K47" s="26"/>
-      <c r="L47" s="26"/>
-      <c r="M47" s="26"/>
+      <c r="K47" s="22"/>
+      <c r="L47" s="22"/>
+      <c r="M47" s="22"/>
       <c r="N47" s="9"/>
       <c r="O47" s="8">
         <v>81</v>
@@ -4031,13 +4545,13 @@
       <c r="R47" s="6"/>
     </row>
     <row r="48" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I48" s="28"/>
-      <c r="J48" s="26" t="s">
+      <c r="I48" s="23"/>
+      <c r="J48" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="K48" s="26"/>
-      <c r="L48" s="26"/>
-      <c r="M48" s="26"/>
+      <c r="K48" s="22"/>
+      <c r="L48" s="22"/>
+      <c r="M48" s="22"/>
       <c r="N48" s="9"/>
       <c r="O48" s="8">
         <v>82</v>
@@ -4051,11 +4565,11 @@
       <c r="R48" s="6"/>
     </row>
     <row r="49" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I49" s="28"/>
-      <c r="J49" s="25"/>
-      <c r="K49" s="25"/>
-      <c r="L49" s="25"/>
-      <c r="M49" s="25"/>
+      <c r="I49" s="23"/>
+      <c r="J49" s="24"/>
+      <c r="K49" s="24"/>
+      <c r="L49" s="24"/>
+      <c r="M49" s="24"/>
       <c r="N49" s="9"/>
       <c r="O49" s="8">
         <v>83</v>
@@ -4069,11 +4583,11 @@
       <c r="R49" s="6"/>
     </row>
     <row r="50" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I50" s="28"/>
-      <c r="J50" s="25"/>
-      <c r="K50" s="25"/>
-      <c r="L50" s="25"/>
-      <c r="M50" s="25"/>
+      <c r="I50" s="23"/>
+      <c r="J50" s="24"/>
+      <c r="K50" s="24"/>
+      <c r="L50" s="24"/>
+      <c r="M50" s="24"/>
       <c r="N50" s="9"/>
       <c r="O50" s="8">
         <v>84</v>
@@ -4087,11 +4601,11 @@
       <c r="R50" s="6"/>
     </row>
     <row r="51" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I51" s="28"/>
-      <c r="J51" s="25"/>
-      <c r="K51" s="25"/>
-      <c r="L51" s="25"/>
-      <c r="M51" s="25"/>
+      <c r="I51" s="23"/>
+      <c r="J51" s="24"/>
+      <c r="K51" s="24"/>
+      <c r="L51" s="24"/>
+      <c r="M51" s="24"/>
       <c r="N51" s="9"/>
       <c r="O51" s="8">
         <v>85</v>
@@ -4105,11 +4619,11 @@
       <c r="R51" s="6"/>
     </row>
     <row r="52" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I52" s="28"/>
-      <c r="J52" s="25"/>
-      <c r="K52" s="25"/>
-      <c r="L52" s="25"/>
-      <c r="M52" s="25"/>
+      <c r="I52" s="23"/>
+      <c r="J52" s="24"/>
+      <c r="K52" s="24"/>
+      <c r="L52" s="24"/>
+      <c r="M52" s="24"/>
       <c r="N52" s="9"/>
       <c r="O52" s="8">
         <v>86</v>
@@ -4124,10 +4638,10 @@
     </row>
     <row r="53" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I53" s="6"/>
-      <c r="J53" s="25"/>
-      <c r="K53" s="25"/>
-      <c r="L53" s="25"/>
-      <c r="M53" s="25"/>
+      <c r="J53" s="24"/>
+      <c r="K53" s="24"/>
+      <c r="L53" s="24"/>
+      <c r="M53" s="24"/>
       <c r="N53" s="7"/>
       <c r="O53" s="8">
         <v>87</v>
@@ -4142,10 +4656,10 @@
     </row>
     <row r="54" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I54" s="6"/>
-      <c r="J54" s="25"/>
-      <c r="K54" s="25"/>
-      <c r="L54" s="25"/>
-      <c r="M54" s="25"/>
+      <c r="J54" s="24"/>
+      <c r="K54" s="24"/>
+      <c r="L54" s="24"/>
+      <c r="M54" s="24"/>
       <c r="N54" s="7"/>
       <c r="O54" s="8">
         <v>88</v>
@@ -4160,10 +4674,10 @@
     </row>
     <row r="55" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I55" s="6"/>
-      <c r="J55" s="25"/>
-      <c r="K55" s="25"/>
-      <c r="L55" s="25"/>
-      <c r="M55" s="25"/>
+      <c r="J55" s="24"/>
+      <c r="K55" s="24"/>
+      <c r="L55" s="24"/>
+      <c r="M55" s="24"/>
       <c r="N55" s="7"/>
       <c r="O55" s="8">
         <v>89</v>
@@ -4178,10 +4692,10 @@
     </row>
     <row r="56" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I56" s="6"/>
-      <c r="J56" s="25"/>
-      <c r="K56" s="25"/>
-      <c r="L56" s="25"/>
-      <c r="M56" s="25"/>
+      <c r="J56" s="24"/>
+      <c r="K56" s="24"/>
+      <c r="L56" s="24"/>
+      <c r="M56" s="24"/>
       <c r="N56" s="7"/>
       <c r="O56" s="8">
         <v>90</v>
@@ -4196,10 +4710,10 @@
     </row>
     <row r="57" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I57" s="6"/>
-      <c r="J57" s="25"/>
-      <c r="K57" s="25"/>
-      <c r="L57" s="25"/>
-      <c r="M57" s="25"/>
+      <c r="J57" s="24"/>
+      <c r="K57" s="24"/>
+      <c r="L57" s="24"/>
+      <c r="M57" s="24"/>
       <c r="N57" s="7"/>
       <c r="O57" s="8">
         <v>91</v>
@@ -4214,10 +4728,10 @@
     </row>
     <row r="58" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I58" s="6"/>
-      <c r="J58" s="25"/>
-      <c r="K58" s="25"/>
-      <c r="L58" s="25"/>
-      <c r="M58" s="25"/>
+      <c r="J58" s="24"/>
+      <c r="K58" s="24"/>
+      <c r="L58" s="24"/>
+      <c r="M58" s="24"/>
       <c r="N58" s="7"/>
       <c r="O58" s="8">
         <v>92</v>
@@ -4232,10 +4746,10 @@
     </row>
     <row r="59" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I59" s="6"/>
-      <c r="J59" s="25"/>
-      <c r="K59" s="25"/>
-      <c r="L59" s="25"/>
-      <c r="M59" s="25"/>
+      <c r="J59" s="24"/>
+      <c r="K59" s="24"/>
+      <c r="L59" s="24"/>
+      <c r="M59" s="24"/>
       <c r="N59" s="7"/>
       <c r="O59" s="8">
         <v>93</v>
@@ -4250,10 +4764,10 @@
     </row>
     <row r="60" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I60" s="6"/>
-      <c r="J60" s="25"/>
-      <c r="K60" s="25"/>
-      <c r="L60" s="25"/>
-      <c r="M60" s="25"/>
+      <c r="J60" s="24"/>
+      <c r="K60" s="24"/>
+      <c r="L60" s="24"/>
+      <c r="M60" s="24"/>
       <c r="N60" s="7"/>
       <c r="O60" s="8">
         <v>94</v>
@@ -4268,10 +4782,10 @@
     </row>
     <row r="61" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I61" s="6"/>
-      <c r="J61" s="25"/>
-      <c r="K61" s="25"/>
-      <c r="L61" s="25"/>
-      <c r="M61" s="25"/>
+      <c r="J61" s="24"/>
+      <c r="K61" s="24"/>
+      <c r="L61" s="24"/>
+      <c r="M61" s="24"/>
       <c r="N61" s="7"/>
       <c r="O61" s="8">
         <v>95</v>
@@ -4286,10 +4800,10 @@
     </row>
     <row r="62" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I62" s="6"/>
-      <c r="J62" s="25"/>
-      <c r="K62" s="25"/>
-      <c r="L62" s="25"/>
-      <c r="M62" s="25"/>
+      <c r="J62" s="24"/>
+      <c r="K62" s="24"/>
+      <c r="L62" s="24"/>
+      <c r="M62" s="24"/>
       <c r="N62" s="7"/>
       <c r="O62" s="8">
         <v>96</v>
@@ -4304,10 +4818,10 @@
     </row>
     <row r="63" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I63" s="6"/>
-      <c r="J63" s="25"/>
-      <c r="K63" s="25"/>
-      <c r="L63" s="25"/>
-      <c r="M63" s="25"/>
+      <c r="J63" s="24"/>
+      <c r="K63" s="24"/>
+      <c r="L63" s="24"/>
+      <c r="M63" s="24"/>
       <c r="N63" s="7"/>
       <c r="O63" s="8">
         <v>97</v>
@@ -4322,10 +4836,10 @@
     </row>
     <row r="64" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I64" s="6"/>
-      <c r="J64" s="25"/>
-      <c r="K64" s="25"/>
-      <c r="L64" s="25"/>
-      <c r="M64" s="25"/>
+      <c r="J64" s="24"/>
+      <c r="K64" s="24"/>
+      <c r="L64" s="24"/>
+      <c r="M64" s="24"/>
       <c r="N64" s="7"/>
       <c r="O64" s="8">
         <v>98</v>
@@ -4340,10 +4854,10 @@
     </row>
     <row r="65" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I65" s="6"/>
-      <c r="J65" s="25"/>
-      <c r="K65" s="25"/>
-      <c r="L65" s="25"/>
-      <c r="M65" s="25"/>
+      <c r="J65" s="24"/>
+      <c r="K65" s="24"/>
+      <c r="L65" s="24"/>
+      <c r="M65" s="24"/>
       <c r="N65" s="7"/>
       <c r="O65" s="8">
         <v>99</v>
@@ -4358,10 +4872,10 @@
     </row>
     <row r="66" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I66" s="6"/>
-      <c r="J66" s="25"/>
-      <c r="K66" s="25"/>
-      <c r="L66" s="25"/>
-      <c r="M66" s="25"/>
+      <c r="J66" s="24"/>
+      <c r="K66" s="24"/>
+      <c r="L66" s="24"/>
+      <c r="M66" s="24"/>
       <c r="N66" s="7"/>
       <c r="O66" s="8">
         <v>100</v>
@@ -4376,10 +4890,10 @@
     </row>
     <row r="67" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I67" s="6"/>
-      <c r="J67" s="25"/>
-      <c r="K67" s="25"/>
-      <c r="L67" s="25"/>
-      <c r="M67" s="25"/>
+      <c r="J67" s="24"/>
+      <c r="K67" s="24"/>
+      <c r="L67" s="24"/>
+      <c r="M67" s="24"/>
       <c r="N67" s="7"/>
       <c r="O67" s="8">
         <v>101</v>
@@ -4394,10 +4908,10 @@
     </row>
     <row r="68" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I68" s="6"/>
-      <c r="J68" s="25"/>
-      <c r="K68" s="25"/>
-      <c r="L68" s="25"/>
-      <c r="M68" s="25"/>
+      <c r="J68" s="24"/>
+      <c r="K68" s="24"/>
+      <c r="L68" s="24"/>
+      <c r="M68" s="24"/>
       <c r="N68" s="7"/>
       <c r="O68" s="8">
         <v>102</v>
@@ -4412,10 +4926,10 @@
     </row>
     <row r="69" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I69" s="6"/>
-      <c r="J69" s="25"/>
-      <c r="K69" s="25"/>
-      <c r="L69" s="25"/>
-      <c r="M69" s="25"/>
+      <c r="J69" s="24"/>
+      <c r="K69" s="24"/>
+      <c r="L69" s="24"/>
+      <c r="M69" s="24"/>
       <c r="N69" s="7"/>
       <c r="O69" s="8">
         <v>103</v>
@@ -4430,10 +4944,10 @@
     </row>
     <row r="70" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I70" s="6"/>
-      <c r="J70" s="25"/>
-      <c r="K70" s="25"/>
-      <c r="L70" s="25"/>
-      <c r="M70" s="25"/>
+      <c r="J70" s="24"/>
+      <c r="K70" s="24"/>
+      <c r="L70" s="24"/>
+      <c r="M70" s="24"/>
       <c r="N70" s="7"/>
       <c r="O70" s="8">
         <v>104</v>
@@ -4448,10 +4962,10 @@
     </row>
     <row r="71" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I71" s="6"/>
-      <c r="J71" s="25"/>
-      <c r="K71" s="25"/>
-      <c r="L71" s="25"/>
-      <c r="M71" s="25"/>
+      <c r="J71" s="24"/>
+      <c r="K71" s="24"/>
+      <c r="L71" s="24"/>
+      <c r="M71" s="24"/>
       <c r="N71" s="7"/>
       <c r="O71" s="8">
         <v>105</v>
@@ -4466,10 +4980,10 @@
     </row>
     <row r="72" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I72" s="6"/>
-      <c r="J72" s="25"/>
-      <c r="K72" s="25"/>
-      <c r="L72" s="25"/>
-      <c r="M72" s="25"/>
+      <c r="J72" s="24"/>
+      <c r="K72" s="24"/>
+      <c r="L72" s="24"/>
+      <c r="M72" s="24"/>
       <c r="N72" s="7"/>
       <c r="O72" s="8">
         <v>106</v>
@@ -4484,10 +4998,10 @@
     </row>
     <row r="73" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I73" s="6"/>
-      <c r="J73" s="25"/>
-      <c r="K73" s="25"/>
-      <c r="L73" s="25"/>
-      <c r="M73" s="25"/>
+      <c r="J73" s="24"/>
+      <c r="K73" s="24"/>
+      <c r="L73" s="24"/>
+      <c r="M73" s="24"/>
       <c r="N73" s="7"/>
       <c r="O73" s="8">
         <v>107</v>
@@ -4502,10 +5016,10 @@
     </row>
     <row r="74" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I74" s="6"/>
-      <c r="J74" s="25"/>
-      <c r="K74" s="25"/>
-      <c r="L74" s="25"/>
-      <c r="M74" s="25"/>
+      <c r="J74" s="24"/>
+      <c r="K74" s="24"/>
+      <c r="L74" s="24"/>
+      <c r="M74" s="24"/>
       <c r="N74" s="7"/>
       <c r="O74" s="8">
         <v>108</v>
@@ -4520,10 +5034,10 @@
     </row>
     <row r="75" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I75" s="6"/>
-      <c r="J75" s="25"/>
-      <c r="K75" s="25"/>
-      <c r="L75" s="25"/>
-      <c r="M75" s="25"/>
+      <c r="J75" s="24"/>
+      <c r="K75" s="24"/>
+      <c r="L75" s="24"/>
+      <c r="M75" s="24"/>
       <c r="N75" s="7"/>
       <c r="O75" s="8">
         <v>109</v>
@@ -4538,10 +5052,10 @@
     </row>
     <row r="76" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I76" s="6"/>
-      <c r="J76" s="25"/>
-      <c r="K76" s="25"/>
-      <c r="L76" s="25"/>
-      <c r="M76" s="25"/>
+      <c r="J76" s="24"/>
+      <c r="K76" s="24"/>
+      <c r="L76" s="24"/>
+      <c r="M76" s="24"/>
       <c r="N76" s="7"/>
       <c r="O76" s="8">
         <v>110</v>
@@ -4556,10 +5070,10 @@
     </row>
     <row r="77" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I77" s="6"/>
-      <c r="J77" s="25"/>
-      <c r="K77" s="25"/>
-      <c r="L77" s="25"/>
-      <c r="M77" s="25"/>
+      <c r="J77" s="24"/>
+      <c r="K77" s="24"/>
+      <c r="L77" s="24"/>
+      <c r="M77" s="24"/>
       <c r="N77" s="7"/>
       <c r="O77" s="8">
         <v>111</v>
@@ -4574,10 +5088,10 @@
     </row>
     <row r="78" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I78" s="6"/>
-      <c r="J78" s="25"/>
-      <c r="K78" s="25"/>
-      <c r="L78" s="25"/>
-      <c r="M78" s="25"/>
+      <c r="J78" s="24"/>
+      <c r="K78" s="24"/>
+      <c r="L78" s="24"/>
+      <c r="M78" s="24"/>
       <c r="N78" s="7"/>
       <c r="O78" s="8">
         <v>112</v>
@@ -4592,10 +5106,10 @@
     </row>
     <row r="79" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I79" s="6"/>
-      <c r="J79" s="25"/>
-      <c r="K79" s="25"/>
-      <c r="L79" s="25"/>
-      <c r="M79" s="25"/>
+      <c r="J79" s="24"/>
+      <c r="K79" s="24"/>
+      <c r="L79" s="24"/>
+      <c r="M79" s="24"/>
       <c r="N79" s="7"/>
       <c r="O79" s="8">
         <v>113</v>
@@ -4610,10 +5124,10 @@
     </row>
     <row r="80" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I80" s="6"/>
-      <c r="J80" s="25"/>
-      <c r="K80" s="25"/>
-      <c r="L80" s="25"/>
-      <c r="M80" s="25"/>
+      <c r="J80" s="24"/>
+      <c r="K80" s="24"/>
+      <c r="L80" s="24"/>
+      <c r="M80" s="24"/>
       <c r="N80" s="7"/>
       <c r="O80" s="8">
         <v>114</v>
@@ -4628,10 +5142,10 @@
     </row>
     <row r="81" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I81" s="6"/>
-      <c r="J81" s="25"/>
-      <c r="K81" s="25"/>
-      <c r="L81" s="25"/>
-      <c r="M81" s="25"/>
+      <c r="J81" s="24"/>
+      <c r="K81" s="24"/>
+      <c r="L81" s="24"/>
+      <c r="M81" s="24"/>
       <c r="N81" s="7"/>
       <c r="O81" s="8">
         <v>115</v>
@@ -4646,10 +5160,10 @@
     </row>
     <row r="82" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I82" s="6"/>
-      <c r="J82" s="25"/>
-      <c r="K82" s="25"/>
-      <c r="L82" s="25"/>
-      <c r="M82" s="25"/>
+      <c r="J82" s="24"/>
+      <c r="K82" s="24"/>
+      <c r="L82" s="24"/>
+      <c r="M82" s="24"/>
       <c r="N82" s="7"/>
       <c r="O82" s="8">
         <v>116</v>
@@ -4664,10 +5178,10 @@
     </row>
     <row r="83" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I83" s="6"/>
-      <c r="J83" s="25"/>
-      <c r="K83" s="25"/>
-      <c r="L83" s="25"/>
-      <c r="M83" s="25"/>
+      <c r="J83" s="24"/>
+      <c r="K83" s="24"/>
+      <c r="L83" s="24"/>
+      <c r="M83" s="24"/>
       <c r="N83" s="7"/>
       <c r="O83" s="8">
         <v>117</v>
@@ -4682,10 +5196,10 @@
     </row>
     <row r="84" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I84" s="6"/>
-      <c r="J84" s="25"/>
-      <c r="K84" s="25"/>
-      <c r="L84" s="25"/>
-      <c r="M84" s="25"/>
+      <c r="J84" s="24"/>
+      <c r="K84" s="24"/>
+      <c r="L84" s="24"/>
+      <c r="M84" s="24"/>
       <c r="N84" s="7"/>
       <c r="O84" s="8">
         <v>118</v>
@@ -4700,10 +5214,10 @@
     </row>
     <row r="85" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I85" s="6"/>
-      <c r="J85" s="25"/>
-      <c r="K85" s="25"/>
-      <c r="L85" s="25"/>
-      <c r="M85" s="25"/>
+      <c r="J85" s="24"/>
+      <c r="K85" s="24"/>
+      <c r="L85" s="24"/>
+      <c r="M85" s="24"/>
       <c r="N85" s="7"/>
       <c r="O85" s="8">
         <v>119</v>
@@ -4718,10 +5232,10 @@
     </row>
     <row r="86" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I86" s="6"/>
-      <c r="J86" s="25"/>
-      <c r="K86" s="25"/>
-      <c r="L86" s="25"/>
-      <c r="M86" s="25"/>
+      <c r="J86" s="24"/>
+      <c r="K86" s="24"/>
+      <c r="L86" s="24"/>
+      <c r="M86" s="24"/>
       <c r="N86" s="7"/>
       <c r="O86" s="8">
         <v>120</v>
@@ -4736,10 +5250,10 @@
     </row>
     <row r="87" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I87" s="6"/>
-      <c r="J87" s="25"/>
-      <c r="K87" s="25"/>
-      <c r="L87" s="25"/>
-      <c r="M87" s="25"/>
+      <c r="J87" s="24"/>
+      <c r="K87" s="24"/>
+      <c r="L87" s="24"/>
+      <c r="M87" s="24"/>
       <c r="N87" s="7"/>
       <c r="O87" s="8">
         <v>121</v>
@@ -4754,10 +5268,10 @@
     </row>
     <row r="88" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I88" s="6"/>
-      <c r="J88" s="25"/>
-      <c r="K88" s="25"/>
-      <c r="L88" s="25"/>
-      <c r="M88" s="25"/>
+      <c r="J88" s="24"/>
+      <c r="K88" s="24"/>
+      <c r="L88" s="24"/>
+      <c r="M88" s="24"/>
       <c r="N88" s="7"/>
       <c r="O88" s="8">
         <v>122</v>
@@ -4772,10 +5286,10 @@
     </row>
     <row r="89" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I89" s="6"/>
-      <c r="J89" s="25"/>
-      <c r="K89" s="25"/>
-      <c r="L89" s="25"/>
-      <c r="M89" s="25"/>
+      <c r="J89" s="24"/>
+      <c r="K89" s="24"/>
+      <c r="L89" s="24"/>
+      <c r="M89" s="24"/>
       <c r="N89" s="7"/>
       <c r="O89" s="8">
         <v>123</v>
@@ -4790,10 +5304,10 @@
     </row>
     <row r="90" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I90" s="6"/>
-      <c r="J90" s="25"/>
-      <c r="K90" s="25"/>
-      <c r="L90" s="25"/>
-      <c r="M90" s="25"/>
+      <c r="J90" s="24"/>
+      <c r="K90" s="24"/>
+      <c r="L90" s="24"/>
+      <c r="M90" s="24"/>
       <c r="N90" s="7"/>
       <c r="O90" s="8">
         <v>124</v>
@@ -4808,10 +5322,10 @@
     </row>
     <row r="91" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I91" s="6"/>
-      <c r="J91" s="25"/>
-      <c r="K91" s="25"/>
-      <c r="L91" s="25"/>
-      <c r="M91" s="25"/>
+      <c r="J91" s="24"/>
+      <c r="K91" s="24"/>
+      <c r="L91" s="24"/>
+      <c r="M91" s="24"/>
       <c r="N91" s="7"/>
       <c r="O91" s="8">
         <v>125</v>
@@ -4826,10 +5340,10 @@
     </row>
     <row r="92" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I92" s="6"/>
-      <c r="J92" s="25"/>
-      <c r="K92" s="25"/>
-      <c r="L92" s="25"/>
-      <c r="M92" s="25"/>
+      <c r="J92" s="24"/>
+      <c r="K92" s="24"/>
+      <c r="L92" s="24"/>
+      <c r="M92" s="24"/>
       <c r="N92" s="7"/>
       <c r="O92" s="8">
         <v>126</v>
@@ -4844,10 +5358,10 @@
     </row>
     <row r="93" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I93" s="6"/>
-      <c r="J93" s="25"/>
-      <c r="K93" s="25"/>
-      <c r="L93" s="25"/>
-      <c r="M93" s="25"/>
+      <c r="J93" s="24"/>
+      <c r="K93" s="24"/>
+      <c r="L93" s="24"/>
+      <c r="M93" s="24"/>
       <c r="N93" s="7"/>
       <c r="O93" s="8">
         <v>127</v>
@@ -7040,31 +7554,47 @@
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="J18:M18"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="J93:M93"/>
+    <mergeCell ref="J88:M88"/>
+    <mergeCell ref="J89:M89"/>
+    <mergeCell ref="J90:M90"/>
+    <mergeCell ref="J91:M91"/>
+    <mergeCell ref="J92:M92"/>
+    <mergeCell ref="J83:M83"/>
+    <mergeCell ref="J84:M84"/>
+    <mergeCell ref="J85:M85"/>
+    <mergeCell ref="J86:M86"/>
+    <mergeCell ref="J87:M87"/>
+    <mergeCell ref="J78:M78"/>
+    <mergeCell ref="J79:M79"/>
+    <mergeCell ref="J80:M80"/>
+    <mergeCell ref="J81:M81"/>
+    <mergeCell ref="J82:M82"/>
+    <mergeCell ref="J73:M73"/>
+    <mergeCell ref="J74:M74"/>
+    <mergeCell ref="J75:M75"/>
+    <mergeCell ref="J76:M76"/>
+    <mergeCell ref="J77:M77"/>
+    <mergeCell ref="J68:M68"/>
+    <mergeCell ref="J69:M69"/>
+    <mergeCell ref="J70:M70"/>
+    <mergeCell ref="J71:M71"/>
+    <mergeCell ref="J72:M72"/>
+    <mergeCell ref="J63:M63"/>
+    <mergeCell ref="J64:M64"/>
+    <mergeCell ref="J65:M65"/>
+    <mergeCell ref="J66:M66"/>
+    <mergeCell ref="J67:M67"/>
+    <mergeCell ref="J58:M58"/>
+    <mergeCell ref="J59:M59"/>
+    <mergeCell ref="J60:M60"/>
+    <mergeCell ref="J61:M61"/>
+    <mergeCell ref="J62:M62"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="J54:M54"/>
+    <mergeCell ref="J55:M55"/>
+    <mergeCell ref="J56:M56"/>
+    <mergeCell ref="J57:M57"/>
     <mergeCell ref="J40:M40"/>
     <mergeCell ref="J41:M41"/>
     <mergeCell ref="J42:M42"/>
@@ -7079,47 +7609,31 @@
     <mergeCell ref="J50:M50"/>
     <mergeCell ref="J51:M51"/>
     <mergeCell ref="J52:M52"/>
-    <mergeCell ref="J53:M53"/>
-    <mergeCell ref="J54:M54"/>
-    <mergeCell ref="J55:M55"/>
-    <mergeCell ref="J56:M56"/>
-    <mergeCell ref="J57:M57"/>
-    <mergeCell ref="J58:M58"/>
-    <mergeCell ref="J59:M59"/>
-    <mergeCell ref="J60:M60"/>
-    <mergeCell ref="J61:M61"/>
-    <mergeCell ref="J62:M62"/>
-    <mergeCell ref="J63:M63"/>
-    <mergeCell ref="J64:M64"/>
-    <mergeCell ref="J65:M65"/>
-    <mergeCell ref="J66:M66"/>
-    <mergeCell ref="J67:M67"/>
-    <mergeCell ref="J68:M68"/>
-    <mergeCell ref="J69:M69"/>
-    <mergeCell ref="J70:M70"/>
-    <mergeCell ref="J71:M71"/>
-    <mergeCell ref="J72:M72"/>
-    <mergeCell ref="J73:M73"/>
-    <mergeCell ref="J74:M74"/>
-    <mergeCell ref="J75:M75"/>
-    <mergeCell ref="J76:M76"/>
-    <mergeCell ref="J77:M77"/>
-    <mergeCell ref="J78:M78"/>
-    <mergeCell ref="J79:M79"/>
-    <mergeCell ref="J80:M80"/>
-    <mergeCell ref="J81:M81"/>
-    <mergeCell ref="J82:M82"/>
-    <mergeCell ref="J83:M83"/>
-    <mergeCell ref="J84:M84"/>
-    <mergeCell ref="J85:M85"/>
-    <mergeCell ref="J86:M86"/>
-    <mergeCell ref="J87:M87"/>
-    <mergeCell ref="J93:M93"/>
-    <mergeCell ref="J88:M88"/>
-    <mergeCell ref="J89:M89"/>
-    <mergeCell ref="J90:M90"/>
-    <mergeCell ref="J91:M91"/>
-    <mergeCell ref="J92:M92"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="J19:M19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7133,1211 +7647,1212 @@
   <dimension ref="A1:U28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" style="27" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7" style="27" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="26" t="s">
+        <v>559</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>560</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>469</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>562</v>
+      </c>
+      <c r="I1" s="26" t="s">
+        <v>471</v>
+      </c>
+      <c r="J1" s="26" t="s">
+        <v>472</v>
+      </c>
+      <c r="K1" s="26" t="s">
+        <v>473</v>
+      </c>
+      <c r="L1" s="26" t="s">
+        <v>474</v>
+      </c>
+      <c r="M1" s="26" t="s">
+        <v>475</v>
+      </c>
+      <c r="N1" s="26" t="s">
+        <v>476</v>
+      </c>
+      <c r="O1" s="26" t="s">
+        <v>477</v>
+      </c>
+      <c r="P1" s="26" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q1" s="26" t="s">
+        <v>479</v>
+      </c>
+      <c r="R1" s="26" t="s">
+        <v>435</v>
+      </c>
+      <c r="S1" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="T1" s="26" t="s">
+        <v>684</v>
+      </c>
+      <c r="U1" s="26"/>
+    </row>
+    <row r="2" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="48"/>
+      <c r="B2" s="48" t="s">
+        <v>563</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="49" t="s">
+        <v>564</v>
+      </c>
+      <c r="E2" s="48" t="s">
         <v>565</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="15" t="s">
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48" t="s">
         <v>566</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="P2" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q2" s="50" t="s">
         <v>567</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>474</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="R2" s="48" t="s">
         <v>568</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>485</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>690</v>
-      </c>
-      <c r="U1" s="4"/>
-    </row>
-    <row r="2" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4" t="s">
+      <c r="S2" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="48" t="s">
+        <v>523</v>
+      </c>
+      <c r="B3" s="48" t="s">
         <v>569</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C3" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D3" s="49" t="s">
         <v>570</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E3" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="48" t="s">
         <v>571</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4" t="s">
+      <c r="P3" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q3" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R3" s="48" t="s">
         <v>572</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="S3" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="48" t="s">
+        <v>573</v>
+      </c>
+      <c r="B4" s="48" t="s">
+        <v>574</v>
+      </c>
+      <c r="C4" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>575</v>
+      </c>
+      <c r="E4" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48" t="s">
+        <v>571</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q4" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>576</v>
+      </c>
+      <c r="S4" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="48" t="s">
+        <v>577</v>
+      </c>
+      <c r="B5" s="48" t="s">
+        <v>578</v>
+      </c>
+      <c r="C5" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="49" t="s">
+        <v>579</v>
+      </c>
+      <c r="E5" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="48" t="s">
+        <v>571</v>
+      </c>
+      <c r="P5" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q5" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R5" s="48" t="s">
+        <v>580</v>
+      </c>
+      <c r="S5" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="48" t="s">
+        <v>581</v>
+      </c>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="49" t="s">
+        <v>582</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="48" t="s">
+        <v>583</v>
+      </c>
+      <c r="P6" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q6" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R6" s="51" t="s">
+        <v>584</v>
+      </c>
+      <c r="S6" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="48" t="s">
+        <v>581</v>
+      </c>
+      <c r="B7" s="48" t="s">
+        <v>523</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="49" t="s">
+        <v>585</v>
+      </c>
+      <c r="E7" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="48" t="s">
+        <v>586</v>
+      </c>
+      <c r="P7" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q7" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R7" s="48" t="s">
+        <v>587</v>
+      </c>
+      <c r="S7" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="48" t="s">
+        <v>581</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>523</v>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="49" t="s">
+        <v>588</v>
+      </c>
+      <c r="E8" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="48" t="s">
+        <v>586</v>
+      </c>
+      <c r="P8" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q8" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R8" s="48" t="s">
+        <v>589</v>
+      </c>
+      <c r="S8" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="48" t="s">
+        <v>581</v>
+      </c>
+      <c r="B9" s="48" t="s">
+        <v>590</v>
+      </c>
+      <c r="C9" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="49" t="s">
+        <v>588</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="48"/>
+      <c r="O9" s="48" t="s">
+        <v>586</v>
+      </c>
+      <c r="P9" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q9" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R9" s="48" t="s">
+        <v>591</v>
+      </c>
+      <c r="S9" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="48" t="s">
+        <v>581</v>
+      </c>
+      <c r="B10" s="48" t="s">
+        <v>592</v>
+      </c>
+      <c r="C10" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>593</v>
+      </c>
+      <c r="E10" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="48"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="48" t="s">
+        <v>586</v>
+      </c>
+      <c r="P10" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q10" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R10" s="48" t="s">
+        <v>594</v>
+      </c>
+      <c r="S10" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="48" t="s">
+        <v>581</v>
+      </c>
+      <c r="B11" s="48" t="s">
+        <v>595</v>
+      </c>
+      <c r="C11" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>596</v>
+      </c>
+      <c r="E11" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="48"/>
+      <c r="O11" s="48" t="s">
+        <v>586</v>
+      </c>
+      <c r="P11" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q11" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R11" s="48" t="s">
+        <v>597</v>
+      </c>
+      <c r="S11" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="48" t="s">
+        <v>598</v>
+      </c>
+      <c r="B12" s="48" t="s">
+        <v>599</v>
+      </c>
+      <c r="C12" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="52"/>
+      <c r="E12" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="48"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="48"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="48" t="s">
+        <v>600</v>
+      </c>
+      <c r="P12" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q12" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R12" s="51" t="s">
+        <v>601</v>
+      </c>
+      <c r="S12" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="48" t="s">
+        <v>598</v>
+      </c>
+      <c r="B13" s="48" t="s">
+        <v>602</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="49" t="s">
+        <v>523</v>
+      </c>
+      <c r="E13" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="48"/>
+      <c r="M13" s="48"/>
+      <c r="N13" s="48"/>
+      <c r="O13" s="48" t="s">
+        <v>603</v>
+      </c>
+      <c r="P13" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q13" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R13" s="48" t="s">
+        <v>604</v>
+      </c>
+      <c r="S13" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="48" t="s">
+        <v>598</v>
+      </c>
+      <c r="B14" s="48" t="s">
+        <v>605</v>
+      </c>
+      <c r="C14" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>606</v>
+      </c>
+      <c r="E14" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="48"/>
+      <c r="N14" s="48"/>
+      <c r="O14" s="48" t="s">
+        <v>603</v>
+      </c>
+      <c r="P14" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q14" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R14" s="48" t="s">
+        <v>607</v>
+      </c>
+      <c r="S14" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="48" t="s">
+        <v>598</v>
+      </c>
+      <c r="B15" s="48" t="s">
+        <v>608</v>
+      </c>
+      <c r="C15" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="49" t="s">
+        <v>609</v>
+      </c>
+      <c r="E15" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="48"/>
+      <c r="M15" s="48"/>
+      <c r="N15" s="48"/>
+      <c r="O15" s="48" t="s">
+        <v>603</v>
+      </c>
+      <c r="P15" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q15" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R15" s="48" t="s">
+        <v>610</v>
+      </c>
+      <c r="S15" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" s="48" t="s">
+        <v>598</v>
+      </c>
+      <c r="B16" s="48" t="s">
+        <v>611</v>
+      </c>
+      <c r="C16" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="49" t="s">
+        <v>612</v>
+      </c>
+      <c r="E16" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="48"/>
+      <c r="K16" s="48"/>
+      <c r="L16" s="48"/>
+      <c r="M16" s="48"/>
+      <c r="N16" s="48"/>
+      <c r="O16" s="48" t="s">
+        <v>603</v>
+      </c>
+      <c r="P16" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q16" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R16" s="48" t="s">
+        <v>613</v>
+      </c>
+      <c r="S16" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="48" t="s">
+        <v>614</v>
+      </c>
+      <c r="B17" s="48" t="s">
+        <v>615</v>
+      </c>
+      <c r="C17" s="48"/>
+      <c r="D17" s="49" t="s">
+        <v>616</v>
+      </c>
+      <c r="E17" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="48"/>
+      <c r="L17" s="48"/>
+      <c r="M17" s="48"/>
+      <c r="N17" s="48"/>
+      <c r="O17" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="P17" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q17" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R17" s="48" t="s">
+        <v>491</v>
+      </c>
+      <c r="S17" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" s="48" t="s">
+        <v>614</v>
+      </c>
+      <c r="B18" s="48" t="s">
+        <v>617</v>
+      </c>
+      <c r="C18" s="48" t="s">
+        <v>523</v>
+      </c>
+      <c r="D18" s="49" t="s">
+        <v>618</v>
+      </c>
+      <c r="E18" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="48"/>
+      <c r="L18" s="48"/>
+      <c r="M18" s="48"/>
+      <c r="N18" s="48"/>
+      <c r="O18" s="48" t="s">
+        <v>619</v>
+      </c>
+      <c r="P18" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q18" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R18" s="48" t="s">
+        <v>494</v>
+      </c>
+      <c r="S18" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="48" t="s">
+        <v>614</v>
+      </c>
+      <c r="B19" s="48" t="s">
+        <v>620</v>
+      </c>
+      <c r="C19" s="48" t="s">
+        <v>621</v>
+      </c>
+      <c r="D19" s="49" t="s">
+        <v>622</v>
+      </c>
+      <c r="E19" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48" t="s">
+        <v>619</v>
+      </c>
+      <c r="P19" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q19" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R19" s="48" t="s">
         <v>495</v>
       </c>
-      <c r="Q2" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>574</v>
-      </c>
-      <c r="S2" s="4" t="s">
+      <c r="S19" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="48" t="s">
+        <v>614</v>
+      </c>
+      <c r="B20" s="48" t="s">
+        <v>623</v>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>624</v>
+      </c>
+      <c r="D20" s="49" t="s">
+        <v>625</v>
+      </c>
+      <c r="E20" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="48"/>
+      <c r="L20" s="48"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="48"/>
+      <c r="O20" s="48" t="s">
+        <v>626</v>
+      </c>
+      <c r="P20" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q20" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R20" s="48" t="s">
+        <v>496</v>
+      </c>
+      <c r="S20" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A21" s="48" t="s">
+        <v>614</v>
+      </c>
+      <c r="B21" s="48" t="s">
+        <v>627</v>
+      </c>
+      <c r="C21" s="48" t="s">
+        <v>628</v>
+      </c>
+      <c r="D21" s="49" t="s">
+        <v>629</v>
+      </c>
+      <c r="E21" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="48"/>
+      <c r="K21" s="48"/>
+      <c r="L21" s="48"/>
+      <c r="M21" s="48"/>
+      <c r="N21" s="48"/>
+      <c r="O21" s="48" t="s">
+        <v>619</v>
+      </c>
+      <c r="P21" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q21" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R21" s="48" t="s">
+        <v>497</v>
+      </c>
+      <c r="S21" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="48" t="s">
+        <v>630</v>
+      </c>
+      <c r="B22" s="48" t="s">
+        <v>631</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>632</v>
+      </c>
+      <c r="D22" s="49" t="s">
+        <v>633</v>
+      </c>
+      <c r="E22" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="48"/>
+      <c r="L22" s="48"/>
+      <c r="M22" s="48"/>
+      <c r="N22" s="48"/>
+      <c r="O22" s="48" t="s">
+        <v>626</v>
+      </c>
+      <c r="P22" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q22" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R22" s="48" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="S22" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="48" t="s">
+        <v>634</v>
+      </c>
+      <c r="B23" s="48" t="s">
+        <v>635</v>
+      </c>
+      <c r="C23" s="48" t="s">
+        <v>636</v>
+      </c>
+      <c r="D23" s="49" t="s">
+        <v>637</v>
+      </c>
+      <c r="E23" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F23" s="48"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="48"/>
+      <c r="L23" s="48"/>
+      <c r="M23" s="48"/>
+      <c r="N23" s="48"/>
+      <c r="O23" s="48" t="s">
+        <v>626</v>
+      </c>
+      <c r="P23" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q23" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R23" s="48" t="s">
+        <v>499</v>
+      </c>
+      <c r="S23" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="48" t="s">
+        <v>638</v>
+      </c>
+      <c r="B24" s="48" t="s">
+        <v>639</v>
+      </c>
+      <c r="C24" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>576</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q3" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="D24" s="49" t="s">
+        <v>640</v>
+      </c>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="48"/>
+      <c r="M24" s="48"/>
+      <c r="N24" s="48"/>
+      <c r="O24" s="48" t="s">
+        <v>641</v>
+      </c>
+      <c r="P24" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q24" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R24" s="48" t="s">
+        <v>642</v>
+      </c>
+      <c r="S24" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A25" s="48" t="s">
+        <v>643</v>
+      </c>
+      <c r="B25" s="48" t="s">
+        <v>644</v>
+      </c>
+      <c r="C25" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="15" t="s">
-        <v>581</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q4" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="D25" s="49" t="s">
+        <v>645</v>
+      </c>
+      <c r="E25" s="48" t="s">
+        <v>523</v>
+      </c>
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="48"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="48"/>
+      <c r="L25" s="48"/>
+      <c r="M25" s="48"/>
+      <c r="N25" s="48"/>
+      <c r="O25" s="48" t="s">
+        <v>503</v>
+      </c>
+      <c r="P25" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q25" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R25" s="48" t="s">
+        <v>646</v>
+      </c>
+      <c r="S25" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="48" t="s">
+        <v>647</v>
+      </c>
+      <c r="B26" s="48" t="s">
+        <v>648</v>
+      </c>
+      <c r="C26" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="15" t="s">
-        <v>585</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q5" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>586</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4" t="s">
+      <c r="D26" s="49" t="s">
+        <v>649</v>
+      </c>
+      <c r="E26" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="F26" s="48" t="s">
+        <v>650</v>
+      </c>
+      <c r="G26" s="48"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="48"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="48"/>
+      <c r="M26" s="48"/>
+      <c r="N26" s="48"/>
+      <c r="O26" s="48" t="s">
+        <v>651</v>
+      </c>
+      <c r="P26" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q26" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="R26" s="48" t="s">
+        <v>652</v>
+      </c>
+      <c r="S26" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27" s="53" t="s">
+        <v>647</v>
+      </c>
+      <c r="B27" s="53" t="s">
+        <v>653</v>
+      </c>
+      <c r="C27" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="15" t="s">
-        <v>588</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4" t="s">
-        <v>589</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q6" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R6" s="10" t="s">
-        <v>590</v>
-      </c>
-      <c r="S6" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>591</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q7" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R7" s="4" t="s">
-        <v>593</v>
-      </c>
-      <c r="S7" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>594</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q8" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R8" s="4" t="s">
-        <v>595</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>596</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>594</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q9" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R9" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="S9" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>598</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>599</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q10" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R10" s="4" t="s">
-        <v>600</v>
-      </c>
-      <c r="S10" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>602</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q11" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R11" s="4" t="s">
-        <v>603</v>
-      </c>
-      <c r="S11" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>605</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q12" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R12" s="10" t="s">
-        <v>607</v>
-      </c>
-      <c r="S12" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>608</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>529</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q13" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R13" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="S13" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>611</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>612</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q14" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R14" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="S14" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>614</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>615</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="P15" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q15" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R15" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="S15" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>617</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>618</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="P16" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q16" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R16" s="4" t="s">
-        <v>619</v>
-      </c>
-      <c r="S16" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>621</v>
-      </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="15" t="s">
-        <v>622</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4" t="s">
-        <v>494</v>
-      </c>
-      <c r="P17" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q17" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R17" s="4" t="s">
-        <v>497</v>
-      </c>
-      <c r="S17" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>624</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4" t="s">
-        <v>625</v>
-      </c>
-      <c r="P18" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q18" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R18" s="4" t="s">
-        <v>500</v>
-      </c>
-      <c r="S18" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>626</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>627</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>628</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4" t="s">
-        <v>625</v>
-      </c>
-      <c r="P19" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q19" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R19" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="S19" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>629</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>630</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>631</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="P20" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q20" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R20" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="S20" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>633</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>634</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>635</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4" t="s">
-        <v>625</v>
-      </c>
-      <c r="P21" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q21" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R21" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="S21" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>636</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>638</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>639</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="P22" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q22" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R22" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="S22" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>640</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>641</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>643</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="P23" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q23" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R23" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="S23" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>644</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>645</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>646</v>
-      </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4" t="s">
-        <v>647</v>
-      </c>
-      <c r="P24" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q24" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R24" s="4" t="s">
-        <v>648</v>
-      </c>
-      <c r="S24" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>649</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>650</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>651</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="P25" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q25" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R25" s="4" t="s">
-        <v>652</v>
-      </c>
-      <c r="S25" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="B26" s="4" t="s">
+      <c r="D27" s="54" t="s">
         <v>654</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="15" t="s">
+      <c r="E27" s="53" t="s">
+        <v>565</v>
+      </c>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="53" t="s">
         <v>655</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F26" s="4" t="s">
+      <c r="P27" s="53" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q27" s="55" t="s">
+        <v>567</v>
+      </c>
+      <c r="R27" s="53" t="s">
         <v>656</v>
       </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="4" t="s">
+      <c r="S27" s="53" t="s">
+        <v>514</v>
+      </c>
+      <c r="T27" s="56" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="53" t="s">
         <v>657</v>
       </c>
-      <c r="P26" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q26" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R26" s="4" t="s">
+      <c r="B28" s="53" t="s">
         <v>658</v>
       </c>
-      <c r="S26" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="B27" s="4" t="s">
+      <c r="C28" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="54" t="s">
         <v>659</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" s="15" t="s">
+      <c r="E28" s="53" t="s">
+        <v>565</v>
+      </c>
+      <c r="F28" s="53" t="s">
         <v>660</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4" t="s">
+      <c r="G28" s="53" t="s">
         <v>661</v>
       </c>
-      <c r="P27" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q27" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R27" s="4" t="s">
+      <c r="H28" s="53" t="s">
         <v>662</v>
       </c>
-      <c r="S27" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="T27" s="24" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="I28" s="53" t="s">
         <v>663</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="J28" s="53" t="s">
         <v>664</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="15" t="s">
+      <c r="K28" s="53" t="s">
         <v>665</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F28" s="4" t="s">
+      <c r="L28" s="53" t="s">
         <v>666</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="M28" s="53" t="s">
         <v>667</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="N28" s="53" t="s">
         <v>668</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="O28" s="53" t="s">
+        <v>655</v>
+      </c>
+      <c r="P28" s="53" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q28" s="55" t="s">
+        <v>567</v>
+      </c>
+      <c r="R28" s="53" t="s">
         <v>669</v>
       </c>
-      <c r="J28" s="4" t="s">
-        <v>670</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>671</v>
-      </c>
-      <c r="L28" s="4" t="s">
-        <v>672</v>
-      </c>
-      <c r="M28" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="N28" s="4" t="s">
-        <v>674</v>
-      </c>
-      <c r="O28" s="4" t="s">
-        <v>661</v>
-      </c>
-      <c r="P28" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q28" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="R28" s="4" t="s">
-        <v>675</v>
-      </c>
-      <c r="S28" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="T28" s="24" t="s">
-        <v>691</v>
+      <c r="S28" s="53" t="s">
+        <v>514</v>
+      </c>
+      <c r="T28" s="56" t="s">
+        <v>685</v>
       </c>
     </row>
   </sheetData>
@@ -8353,7 +8868,7 @@
   <dimension ref="A1:U26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" style="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" style="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.140625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.42578125" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="84.5703125" style="11" bestFit="1" customWidth="1"/>
@@ -8375,91 +8890,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>541</v>
+      <c r="A1" s="14" t="s">
+        <v>535</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>483</v>
+        <v>477</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>478</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>435</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
-      <c r="I1" s="16"/>
+      <c r="I1" s="15"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
-      <c r="N1" s="16"/>
+      <c r="N1" s="15"/>
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
       <c r="Q1" s="4"/>
       <c r="R1" s="4"/>
-      <c r="S1" s="16"/>
+      <c r="S1" s="15"/>
       <c r="T1" s="4"/>
       <c r="U1" s="4"/>
     </row>
     <row r="2" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
-        <v>542</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>543</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>520</v>
+      <c r="A2" s="58" t="s">
+        <v>536</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>536</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>489</v>
+      </c>
+      <c r="D2" s="59" t="s">
+        <v>537</v>
+      </c>
+      <c r="E2" s="59" t="s">
+        <v>538</v>
+      </c>
+      <c r="F2" s="59" t="s">
+        <v>514</v>
       </c>
       <c r="G2" s="4"/>
-      <c r="H2" s="16"/>
+      <c r="H2" s="15"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
-      <c r="M2" s="16"/>
+      <c r="M2" s="15"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
-      <c r="R2" s="16"/>
+      <c r="R2" s="15"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
     <row r="3" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15"/>
-      <c r="B3" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>546</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>547</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>520</v>
+      <c r="A3" s="58"/>
+      <c r="B3" s="59" t="s">
+        <v>539</v>
+      </c>
+      <c r="C3" s="59" t="s">
+        <v>489</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>540</v>
+      </c>
+      <c r="E3" s="59" t="s">
+        <v>541</v>
+      </c>
+      <c r="F3" s="59" t="s">
+        <v>514</v>
       </c>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
@@ -8468,23 +8983,23 @@
       <c r="S3" s="4"/>
     </row>
     <row r="4" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>529</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>549</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>520</v>
+      <c r="A4" s="58" t="s">
+        <v>523</v>
+      </c>
+      <c r="B4" s="59" t="s">
+        <v>539</v>
+      </c>
+      <c r="C4" s="59" t="s">
+        <v>489</v>
+      </c>
+      <c r="D4" s="59" t="s">
+        <v>542</v>
+      </c>
+      <c r="E4" s="59" t="s">
+        <v>543</v>
+      </c>
+      <c r="F4" s="59" t="s">
+        <v>514</v>
       </c>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
@@ -8493,23 +9008,23 @@
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>550</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>553</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>498</v>
+      <c r="A5" s="57" t="s">
+        <v>544</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>545</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>546</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>547</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>492</v>
       </c>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
@@ -8518,23 +9033,23 @@
       <c r="S5" s="4"/>
     </row>
     <row r="6" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
-        <v>554</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>556</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>520</v>
+      <c r="A6" s="58" t="s">
+        <v>548</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>548</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>489</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>549</v>
+      </c>
+      <c r="E6" s="59" t="s">
+        <v>550</v>
+      </c>
+      <c r="F6" s="59" t="s">
+        <v>514</v>
       </c>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
@@ -8543,23 +9058,23 @@
       <c r="S6" s="4"/>
     </row>
     <row r="7" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
-        <v>557</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>558</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>559</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>520</v>
+      <c r="A7" s="58" t="s">
+        <v>551</v>
+      </c>
+      <c r="B7" s="59" t="s">
+        <v>536</v>
+      </c>
+      <c r="C7" s="59" t="s">
+        <v>489</v>
+      </c>
+      <c r="D7" s="59" t="s">
+        <v>552</v>
+      </c>
+      <c r="E7" s="59" t="s">
+        <v>553</v>
+      </c>
+      <c r="F7" s="59" t="s">
+        <v>514</v>
       </c>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
@@ -8568,23 +9083,23 @@
       <c r="S7" s="4"/>
     </row>
     <row r="8" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15">
+      <c r="A8" s="57">
         <v>1000000</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>560</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>561</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>498</v>
+      <c r="B8" s="40" t="s">
+        <v>545</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="D8" s="40" t="s">
+        <v>554</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>555</v>
+      </c>
+      <c r="F8" s="40" t="s">
+        <v>492</v>
       </c>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
@@ -8593,23 +9108,23 @@
       <c r="S8" s="4"/>
     </row>
     <row r="9" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
-        <v>562</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>498</v>
+      <c r="A9" s="57" t="s">
+        <v>556</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>545</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="D9" s="40" t="s">
+        <v>557</v>
+      </c>
+      <c r="E9" s="40" t="s">
+        <v>558</v>
+      </c>
+      <c r="F9" s="40" t="s">
+        <v>492</v>
       </c>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
@@ -8625,7 +9140,7 @@
       <c r="S10" s="4"/>
     </row>
     <row r="11" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
+      <c r="A11" s="14"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -8638,7 +9153,7 @@
       <c r="S11" s="4"/>
     </row>
     <row r="12" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="15"/>
+      <c r="A12" s="14"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="E12" s="4"/>
@@ -8649,7 +9164,7 @@
       <c r="S12" s="4"/>
     </row>
     <row r="13" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -8661,7 +9176,7 @@
       <c r="S13" s="4"/>
     </row>
     <row r="14" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="15"/>
+      <c r="A14" s="14"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -8673,7 +9188,7 @@
       <c r="S14" s="4"/>
     </row>
     <row r="15" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
+      <c r="A15" s="14"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -8685,7 +9200,7 @@
       <c r="S15" s="4"/>
     </row>
     <row r="16" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="15"/>
+      <c r="A16" s="14"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -8697,7 +9212,7 @@
       <c r="S16" s="4"/>
     </row>
     <row r="17" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
+      <c r="A17" s="14"/>
       <c r="B17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -8708,7 +9223,7 @@
       <c r="S17" s="4"/>
     </row>
     <row r="18" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="15"/>
+      <c r="A18" s="14"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -8720,7 +9235,7 @@
       <c r="S18" s="4"/>
     </row>
     <row r="19" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
+      <c r="A19" s="14"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -8732,7 +9247,7 @@
       <c r="S19" s="4"/>
     </row>
     <row r="20" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="15"/>
+      <c r="A20" s="14"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -8744,7 +9259,7 @@
       <c r="S20" s="4"/>
     </row>
     <row r="21" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
+      <c r="A21" s="14"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -8756,7 +9271,7 @@
       <c r="S21" s="4"/>
     </row>
     <row r="22" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="15"/>
+      <c r="A22" s="14"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -8768,7 +9283,7 @@
       <c r="S22" s="4"/>
     </row>
     <row r="23" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
+      <c r="A23" s="14"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -8780,7 +9295,7 @@
       <c r="S23" s="4"/>
     </row>
     <row r="24" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="15"/>
+      <c r="A24" s="14"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -8791,7 +9306,7 @@
       <c r="S24" s="4"/>
     </row>
     <row r="25" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15"/>
+      <c r="A25" s="14"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -8803,7 +9318,7 @@
       <c r="S25" s="4"/>
     </row>
     <row r="26" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="15"/>
+      <c r="A26" s="14"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -8837,7 +9352,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="44.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
@@ -8853,212 +9368,212 @@
       <c r="A1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="19" t="s">
-        <v>521</v>
+      <c r="B1" s="17" t="s">
+        <v>515</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>435</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="57"/>
+      <c r="C2" s="40" t="s">
+        <v>516</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>517</v>
+      </c>
+      <c r="E2" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="F2" s="40" t="s">
+        <v>518</v>
+      </c>
+      <c r="G2" s="40" t="s">
+        <v>519</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="57">
+        <v>123</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>520</v>
+      </c>
+      <c r="D3" s="40" t="s">
+        <v>521</v>
+      </c>
+      <c r="E3" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="F3" s="40" t="s">
+        <v>518</v>
+      </c>
+      <c r="G3" s="40" t="s">
         <v>522</v>
       </c>
-      <c r="D2" s="18" t="s">
-        <v>523</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="19">
-        <v>123</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>498</v>
+      <c r="H3" s="40" t="s">
+        <v>492</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="57" t="s">
+        <v>523</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>524</v>
+      </c>
+      <c r="D4" s="40" t="s">
+        <v>525</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="F4" s="40" t="s">
+        <v>518</v>
+      </c>
+      <c r="G4" s="40" t="s">
+        <v>526</v>
+      </c>
+      <c r="H4" s="40" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>527</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>518</v>
+      </c>
+      <c r="G5" s="40" t="s">
+        <v>528</v>
+      </c>
+      <c r="H5" s="40" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="40"/>
+      <c r="D6" s="41" t="s">
+        <v>500</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>518</v>
+      </c>
+      <c r="G6" s="40" t="s">
         <v>529</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="H6" s="40" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="40" t="s">
         <v>530</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D7" s="40" t="s">
+        <v>525</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>518</v>
+      </c>
+      <c r="G7" s="40" t="s">
         <v>531</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="H7" s="40" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="60" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="61" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="60" t="s">
+        <v>516</v>
+      </c>
+      <c r="D8" s="60" t="s">
         <v>532</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="18" t="s">
+      <c r="E8" s="60" t="s">
+        <v>489</v>
+      </c>
+      <c r="F8" s="60" t="s">
         <v>533</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="G5" s="5" t="s">
+      <c r="G8" s="60" t="s">
         <v>534</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="18" t="s">
-        <v>506</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>536</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>531</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>537</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>538</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>540</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>520</v>
+      <c r="H8" s="60" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
-      <c r="B9" s="19"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -9072,14 +9587,14 @@
     <row r="13" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:12" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="21"/>
-      <c r="L15" s="18"/>
+      <c r="B15" s="19"/>
+      <c r="L15" s="16"/>
     </row>
     <row r="16" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="2:12" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="21"/>
-      <c r="L18" s="18"/>
+      <c r="B18" s="19"/>
+      <c r="L18" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9091,299 +9606,303 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="38.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="14.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.5703125" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.85546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="27" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="31" t="s">
+        <v>486</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>487</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>477</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>478</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>479</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>435</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="37"/>
+      <c r="D2" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="E2" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="F2" s="48" t="s">
+        <v>490</v>
+      </c>
+      <c r="G2" s="48" t="s">
+        <v>491</v>
+      </c>
+      <c r="H2" s="48" t="s">
         <v>492</v>
       </c>
-      <c r="C1" s="5" t="s">
+    </row>
+    <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="37"/>
+      <c r="D3" s="51" t="s">
         <v>493</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="17"/>
-      <c r="E2" s="5" t="s">
+      <c r="E3" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="F3" s="48" t="s">
+        <v>490</v>
+      </c>
+      <c r="G3" s="48" t="s">
         <v>494</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="H3" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="37"/>
+      <c r="D4" s="51" t="s">
+        <v>493</v>
+      </c>
+      <c r="E4" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="F4" s="48" t="s">
+        <v>490</v>
+      </c>
+      <c r="G4" s="48" t="s">
         <v>495</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H4" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="D5" s="51" t="s">
+        <v>493</v>
+      </c>
+      <c r="E5" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="F5" s="48" t="s">
+        <v>490</v>
+      </c>
+      <c r="G5" s="48" t="s">
         <v>496</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H5" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="D6" s="51" t="s">
+        <v>493</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>490</v>
+      </c>
+      <c r="G6" s="48" t="s">
         <v>497</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="H6" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="51" t="s">
+        <v>493</v>
+      </c>
+      <c r="E7" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="F7" s="48" t="s">
+        <v>490</v>
+      </c>
+      <c r="G7" s="48" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="17"/>
-      <c r="E3" s="18" t="s">
+      <c r="H7" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D8" s="51" t="s">
+        <v>493</v>
+      </c>
+      <c r="E8" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="F8" s="48" t="s">
+        <v>490</v>
+      </c>
+      <c r="G8" s="48" t="s">
         <v>499</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="H8" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D9" s="51" t="s">
         <v>500</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="17"/>
-      <c r="E4" s="18" t="s">
-        <v>499</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="H4" s="5" t="s">
+      <c r="E9" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="F9" s="48" t="s">
         <v>501</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="17"/>
-      <c r="E5" s="18" t="s">
-        <v>499</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="G9" s="48" t="s">
         <v>502</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="17"/>
-      <c r="E6" s="18" t="s">
-        <v>499</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="H9" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D10" s="51" t="s">
         <v>503</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E7" s="18" t="s">
-        <v>499</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="E10" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="F10" s="48" t="s">
+        <v>501</v>
+      </c>
+      <c r="G10" s="48" t="s">
         <v>504</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E8" s="18" t="s">
-        <v>499</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="H10" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D11" s="51" t="s">
+        <v>503</v>
+      </c>
+      <c r="E11" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="F11" s="48" t="s">
+        <v>501</v>
+      </c>
+      <c r="G11" s="48" t="s">
         <v>505</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E9" s="18" t="s">
+      <c r="H11" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D12" s="51" t="s">
         <v>506</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="G9" s="5" t="s">
+      <c r="E12" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="F12" s="48" t="s">
+        <v>501</v>
+      </c>
+      <c r="G12" s="48" t="s">
         <v>507</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H12" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D13" s="51" t="s">
+        <v>506</v>
+      </c>
+      <c r="E13" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="F13" s="48" t="s">
+        <v>501</v>
+      </c>
+      <c r="G13" s="48" t="s">
         <v>508</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E10" s="18" t="s">
+      <c r="H13" s="48" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D14" s="48" t="s">
         <v>509</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="H10" s="5" t="s">
+      <c r="E14" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="F14" s="48" t="s">
+        <v>501</v>
+      </c>
+      <c r="G14" s="48" t="s">
         <v>510</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E11" s="18" t="s">
+      <c r="H14" s="48" t="s">
+        <v>492</v>
+      </c>
+      <c r="I14" s="31" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D15" s="48" t="s">
         <v>509</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E12" s="18" t="s">
+      <c r="E15" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="F15" s="48" t="s">
+        <v>501</v>
+      </c>
+      <c r="G15" s="48" t="s">
         <v>512</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="H12" s="5" t="s">
+      <c r="H15" s="48" t="s">
+        <v>492</v>
+      </c>
+      <c r="I15" s="31" t="s">
         <v>513</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E13" s="18" t="s">
-        <v>512</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="H13" s="5" t="s">
+    </row>
+    <row r="16" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D16" s="62"/>
+      <c r="E16" s="53" t="s">
+        <v>489</v>
+      </c>
+      <c r="F16" s="62"/>
+      <c r="G16" s="62"/>
+      <c r="H16" s="53" t="s">
         <v>514</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E14" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>516</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E15" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F16" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>520</v>
       </c>
     </row>
   </sheetData>
@@ -9396,199 +9915,478 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:W52"/>
+  <dimension ref="A1:O1048576"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="13" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="10" width="14.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="36.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="35.85546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9" style="27" bestFit="1" customWidth="1"/>
+    <col min="16" max="23" width="14.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="29" t="s">
+        <v>468</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>469</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>470</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>471</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>472</v>
+      </c>
+      <c r="G1" s="29" t="s">
         <v>473</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="H1" s="29" t="s">
         <v>474</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="I1" s="29" t="s">
         <v>475</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="J1" s="29" t="s">
         <v>476</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="K1" s="29" t="s">
         <v>477</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="L1" s="29" t="s">
         <v>478</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="M1" s="29" t="s">
         <v>479</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="N1" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="O1" s="29" t="s">
         <v>480</v>
       </c>
-      <c r="J1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64" t="s">
+        <v>687</v>
+      </c>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63" t="s">
+        <v>566</v>
+      </c>
+      <c r="L2" s="63" t="s">
+        <v>489</v>
+      </c>
+      <c r="M2" s="63" t="s">
+        <v>698</v>
+      </c>
+      <c r="N2" s="65" t="s">
         <v>481</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="O2" s="63" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="63" t="s">
+        <v>630</v>
+      </c>
+      <c r="B3" s="64"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63" t="s">
+        <v>600</v>
+      </c>
+      <c r="L3" s="63" t="s">
+        <v>489</v>
+      </c>
+      <c r="M3" s="63" t="s">
+        <v>698</v>
+      </c>
+      <c r="N3" s="65" t="s">
         <v>482</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="O3" s="63" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="63" t="s">
+        <v>630</v>
+      </c>
+      <c r="B4" s="64" t="s">
+        <v>689</v>
+      </c>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63" t="s">
+        <v>603</v>
+      </c>
+      <c r="L4" s="63" t="s">
+        <v>489</v>
+      </c>
+      <c r="M4" s="63" t="s">
+        <v>698</v>
+      </c>
+      <c r="N4" s="65" t="s">
         <v>483</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="O4" s="63" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="66" t="s">
+        <v>630</v>
+      </c>
+      <c r="B5" s="67" t="s">
+        <v>687</v>
+      </c>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="66" t="s">
+        <v>697</v>
+      </c>
+      <c r="L5" s="66" t="s">
+        <v>489</v>
+      </c>
+      <c r="M5" s="66" t="s">
+        <v>698</v>
+      </c>
+      <c r="N5" s="68" t="s">
         <v>484</v>
       </c>
-      <c r="N1" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="O1" s="4" t="s">
+      <c r="O5" s="66" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="66" t="s">
+        <v>630</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>688</v>
+      </c>
+      <c r="C6" s="66" t="s">
+        <v>661</v>
+      </c>
+      <c r="D6" s="66" t="s">
+        <v>691</v>
+      </c>
+      <c r="E6" s="66" t="s">
+        <v>690</v>
+      </c>
+      <c r="F6" s="66" t="s">
+        <v>692</v>
+      </c>
+      <c r="G6" s="67" t="s">
+        <v>693</v>
+      </c>
+      <c r="H6" s="69" t="s">
+        <v>694</v>
+      </c>
+      <c r="I6" s="66" t="s">
+        <v>695</v>
+      </c>
+      <c r="J6" s="67" t="s">
+        <v>696</v>
+      </c>
+      <c r="K6" s="66" t="s">
+        <v>697</v>
+      </c>
+      <c r="L6" s="66" t="s">
+        <v>489</v>
+      </c>
+      <c r="M6" s="66" t="s">
+        <v>698</v>
+      </c>
+      <c r="N6" s="68" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N2" s="4" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N3" s="4" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N4" s="4" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N5" s="4" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N6" s="4" t="s">
-        <v>490</v>
+      <c r="O6" s="66" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N7" s="4" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="3:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="3:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="3:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="3:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="4"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="15"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="15"/>
-      <c r="Q20" s="4"/>
-    </row>
-    <row r="21" spans="3:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="3:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="3:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="3:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="3:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="3:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E26" s="4"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="15"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="4"/>
-      <c r="S26" s="4"/>
-      <c r="T26" s="4"/>
-      <c r="U26" s="16"/>
-      <c r="V26" s="4"/>
-      <c r="W26" s="4"/>
-    </row>
-    <row r="27" spans="3:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="3:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="3:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="3:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="3:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="3:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="N7" s="26"/>
+    </row>
+    <row r="1048576" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1048576" s="27" t="s">
+        <v>702</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="L1:L3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB64D4C3-956B-45AE-AEF9-289E9FE1CAC9}">
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="11" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="79.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L1" s="14" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>468</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>469</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>470</v>
+      </c>
+      <c r="E1" s="29" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="2" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L2" s="14" t="s">
+      <c r="F1" s="29" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="3" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L3" s="14"/>
+      <c r="G1" s="29" t="s">
+        <v>473</v>
+      </c>
+      <c r="H1" s="29" t="s">
+        <v>474</v>
+      </c>
+      <c r="I1" s="29" t="s">
+        <v>475</v>
+      </c>
+      <c r="J1" s="29" t="s">
+        <v>476</v>
+      </c>
+      <c r="K1" s="29" t="s">
+        <v>477</v>
+      </c>
+      <c r="L1" s="29" t="s">
+        <v>478</v>
+      </c>
+      <c r="M1" s="29" t="s">
+        <v>479</v>
+      </c>
+      <c r="N1" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="O1" s="29" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64" t="s">
+        <v>687</v>
+      </c>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63" t="s">
+        <v>566</v>
+      </c>
+      <c r="L2" s="63" t="s">
+        <v>489</v>
+      </c>
+      <c r="M2" s="63" t="s">
+        <v>698</v>
+      </c>
+      <c r="N2" s="65" t="s">
+        <v>481</v>
+      </c>
+      <c r="O2" s="63" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="63" t="s">
+        <v>630</v>
+      </c>
+      <c r="B3" s="64"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63" t="s">
+        <v>600</v>
+      </c>
+      <c r="L3" s="63" t="s">
+        <v>489</v>
+      </c>
+      <c r="M3" s="63" t="s">
+        <v>698</v>
+      </c>
+      <c r="N3" s="65" t="s">
+        <v>482</v>
+      </c>
+      <c r="O3" s="63" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="63" t="s">
+        <v>630</v>
+      </c>
+      <c r="B4" s="64" t="s">
+        <v>689</v>
+      </c>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63" t="s">
+        <v>603</v>
+      </c>
+      <c r="L4" s="63" t="s">
+        <v>489</v>
+      </c>
+      <c r="M4" s="63" t="s">
+        <v>698</v>
+      </c>
+      <c r="N4" s="65" t="s">
+        <v>483</v>
+      </c>
+      <c r="O4" s="63" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="66" t="s">
+        <v>630</v>
+      </c>
+      <c r="B5" s="67" t="s">
+        <v>687</v>
+      </c>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="66" t="s">
+        <v>697</v>
+      </c>
+      <c r="L5" s="66" t="s">
+        <v>489</v>
+      </c>
+      <c r="M5" s="66" t="s">
+        <v>698</v>
+      </c>
+      <c r="N5" s="68" t="s">
+        <v>484</v>
+      </c>
+      <c r="O5" s="66" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="66" t="s">
+        <v>630</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>688</v>
+      </c>
+      <c r="C6" s="66" t="s">
+        <v>661</v>
+      </c>
+      <c r="D6" s="66" t="s">
+        <v>691</v>
+      </c>
+      <c r="E6" s="66" t="s">
+        <v>690</v>
+      </c>
+      <c r="F6" s="66" t="s">
+        <v>692</v>
+      </c>
+      <c r="G6" s="67" t="s">
+        <v>693</v>
+      </c>
+      <c r="H6" s="69" t="s">
+        <v>694</v>
+      </c>
+      <c r="I6" s="66" t="s">
+        <v>695</v>
+      </c>
+      <c r="J6" s="67" t="s">
+        <v>696</v>
+      </c>
+      <c r="K6" s="66" t="s">
+        <v>697</v>
+      </c>
+      <c r="L6" s="66" t="s">
+        <v>489</v>
+      </c>
+      <c r="M6" s="66" t="s">
+        <v>698</v>
+      </c>
+      <c r="N6" s="68" t="s">
+        <v>485</v>
+      </c>
+      <c r="O6" s="66" t="s">
+        <v>514</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9596,6 +10394,61 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="H1:L3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="7" width="14.140625" style="32" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.7109375" style="32" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="76.28515625" style="32" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" style="32" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.7109375" style="32" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="79.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="32"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="8:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H1" s="32" t="s">
+        <v>477</v>
+      </c>
+      <c r="I1" s="33" t="s">
+        <v>435</v>
+      </c>
+      <c r="J1" s="32" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="2" spans="8:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H2" s="21" t="s">
+        <v>699</v>
+      </c>
+      <c r="I2" s="34" t="s">
+        <v>466</v>
+      </c>
+      <c r="J2" s="32" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="3" spans="8:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H3" s="32" t="s">
+        <v>700</v>
+      </c>
+      <c r="I3" s="34" t="s">
+        <v>467</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>514</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -9615,17 +10468,17 @@
     </row>
     <row r="2" spans="13:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M2" s="4" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="3" spans="13:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M3" s="4" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
     </row>
     <row r="4" spans="13:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M4" s="4" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="5" spans="13:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9669,7 +10522,7 @@
     <row r="43" spans="14:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="44" spans="14:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="N44" s="13" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="45" spans="14:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9677,100 +10530,21 @@
     </row>
     <row r="46" spans="14:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N46" s="4" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="47" spans="14:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N47" s="4" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="48" spans="14:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N48" s="4" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="49" spans="14:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N49" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="K1:L30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="10" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="51.42578125" style="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K1" s="4" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="2" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K2" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="3" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K3" s="4" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="4" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K4" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="5" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L25" s="12"/>
-    </row>
-    <row r="26" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L26" s="4"/>
-    </row>
-    <row r="27" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L27" s="4"/>
-    </row>
-    <row r="28" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L28" s="4"/>
-    </row>
-    <row r="29" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L29" s="4"/>
-    </row>
-    <row r="30" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L30" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/target/test-classes/data/User_Data.xlsx
+++ b/target/test-classes/data/User_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Zalo\DATN\Automation_AFF\src\test\resources\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E81E6C-6389-4419-80F6-74E668DE9254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22AA3D40-708D-4630-A562-53999C7F585F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="-120" windowWidth="28590" windowHeight="16440" tabRatio="920" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="330" yWindow="-120" windowWidth="28590" windowHeight="16440" tabRatio="920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -22,22 +22,21 @@
     <sheet name="Information" sheetId="18" r:id="rId7"/>
     <sheet name="SCart" sheetId="7" r:id="rId8"/>
     <sheet name="SCart_Add" sheetId="8" r:id="rId9"/>
-    <sheet name="SCart_Upd" sheetId="9" r:id="rId10"/>
+    <sheet name="SCard_Upd" sheetId="19" r:id="rId10"/>
     <sheet name="SCart_Del" sheetId="10" r:id="rId11"/>
-    <sheet name="Order" sheetId="17" r:id="rId12"/>
+    <sheet name="Order_Bank" sheetId="11" r:id="rId12"/>
     <sheet name="Order_Indrect" sheetId="15" r:id="rId13"/>
-    <sheet name="Order_Bank" sheetId="11" r:id="rId14"/>
-    <sheet name="Order_Direct" sheetId="16" r:id="rId15"/>
-    <sheet name="Indrect_Commission" sheetId="12" r:id="rId16"/>
-    <sheet name="Direct_Commission" sheetId="13" r:id="rId17"/>
-    <sheet name="Lưu ý" sheetId="14" r:id="rId18"/>
+    <sheet name="Order_Direct" sheetId="16" r:id="rId14"/>
+    <sheet name="Indrect_Commission" sheetId="12" r:id="rId15"/>
+    <sheet name="Direct_Commission" sheetId="13" r:id="rId16"/>
+    <sheet name="Lưu ý" sheetId="14" r:id="rId17"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="718">
   <si>
     <t>Cần để ý :</t>
   </si>
@@ -1389,30 +1388,15 @@
     <t>Kiểm tra để trống số điện thoại</t>
   </si>
   <si>
-    <t>Kiểm tra nhập số điện thoại không hợp lệ</t>
-  </si>
-  <si>
-    <t>Kiểm tra hiển thị tổng tiền</t>
-  </si>
-  <si>
     <t>Kiểm tra nhấn nút "ĐẶT HÀNG" với đủ thông tin</t>
   </si>
   <si>
     <t>Xóa 1 sản phẩm</t>
   </si>
   <si>
-    <t>Nhớ kiểm tra tiền, số lượng, thông báo, title</t>
-  </si>
-  <si>
     <t>Xóa toàn bộ sản phẩm</t>
   </si>
   <si>
-    <t>Tăng số lượng , Kiểm tra tiền</t>
-  </si>
-  <si>
-    <t>Giảm số lượng , kiểm tra tiền</t>
-  </si>
-  <si>
     <t>Giảm số lượng xem có về 0 được không</t>
   </si>
   <si>
@@ -1426,6 +1410,729 @@
   </si>
   <si>
     <t>. Thêm sản phẩm vào giỏ hàng (Add to Cart)</t>
+  </si>
+  <si>
+    <t>CMND</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Districts</t>
+  </si>
+  <si>
+    <t>Ward</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Mst</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Bank</t>
+  </si>
+  <si>
+    <t>Stk</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>TestType</t>
+  </si>
+  <si>
+    <t>Để trông tên</t>
+  </si>
+  <si>
+    <t>Để trông CMND</t>
+  </si>
+  <si>
+    <t>CMND chứa khoảng trắng</t>
+  </si>
+  <si>
+    <t>Nhập các trường không bắt buộc</t>
+  </si>
+  <si>
+    <t>Không nhập các trường không bắt buộc</t>
+  </si>
+  <si>
+    <t>PassNew</t>
+  </si>
+  <si>
+    <t>ComfirmPass</t>
+  </si>
+  <si>
+    <t>Vui lòng nhập email</t>
+  </si>
+  <si>
+    <t>Honivy</t>
+  </si>
+  <si>
+    <t>http://localhost:4200/resend-email-otp</t>
+  </si>
+  <si>
+    <t>Để trống email</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Email không hợp lệ.</t>
+  </si>
+  <si>
+    <t>Nhập email bằng ký tự trắng</t>
+  </si>
+  <si>
+    <t>Nhập email nhưng có ký tự trắng (Đầu)</t>
+  </si>
+  <si>
+    <t>Nhập email nhưng có ký tự trắng (Giữa)</t>
+  </si>
+  <si>
+    <t>Nhập email nhưng có ký tự trắng (Cuối)</t>
+  </si>
+  <si>
+    <t>Nhập email sai định dạng (Không có @)</t>
+  </si>
+  <si>
+    <t>Nhập email sai định dạng (Thiếu tên miền)</t>
+  </si>
+  <si>
+    <t>Vui lòng nhập mật khẩu mới</t>
+  </si>
+  <si>
+    <t>http://localhost:4200/set-password</t>
+  </si>
+  <si>
+    <t>Mất khẩu mới để trống</t>
+  </si>
+  <si>
+    <t>Mật khẩu không được chứa khoảng trắng</t>
+  </si>
+  <si>
+    <t>Mật khẩu mới là khoảng trắng</t>
+  </si>
+  <si>
+    <t>Mật khẩu mới chứa khoảng trắng</t>
+  </si>
+  <si>
+    <t>Mật khẩu xác nhận không khớp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Để trống xác nhận mật khẩu mới </t>
+  </si>
+  <si>
+    <t>Mật khẩu xác nhận không hợp lệ</t>
+  </si>
+  <si>
+    <t>Vui lòng nhập OTP</t>
+  </si>
+  <si>
+    <t>Không điền OTP</t>
+  </si>
+  <si>
+    <t>Thêm 1 cái xác nhận email ở action để nhập OTP</t>
+  </si>
+  <si>
+    <t>Điền OTP không hợp lệ</t>
+  </si>
+  <si>
+    <t>Còn đâu cứ fail là không cho nhập OTP</t>
+  </si>
+  <si>
+    <t>Success</t>
+  </si>
+  <si>
+    <t>PassOld</t>
+  </si>
+  <si>
+    <t>adminmaster1</t>
+  </si>
+  <si>
+    <t>Vui lòng nhập mật khẩu cũ</t>
+  </si>
+  <si>
+    <t>http://localhost:4200/change-password</t>
+  </si>
+  <si>
+    <t>Để trống mật khẩu cũ</t>
+  </si>
+  <si>
+    <t>adminmaster2</t>
+  </si>
+  <si>
+    <t>Mật khẩu cũ không hợp lệ</t>
+  </si>
+  <si>
+    <t>Nhập sai mật khẩu cũ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     </t>
+  </si>
+  <si>
+    <t>adminmaster3</t>
+  </si>
+  <si>
+    <t>Mật khẩu không được chứa khoảng trắng.</t>
+  </si>
+  <si>
+    <t>Nhập khoảng trắng mật khẩu cũ</t>
+  </si>
+  <si>
+    <t>Mật khẩu mới không được trùng với mật khẩu cũ.</t>
+  </si>
+  <si>
+    <t>Nhập cũ trùng mới</t>
+  </si>
+  <si>
+    <t>Để trống mật khẩu mới</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          </t>
+  </si>
+  <si>
+    <t>Nhập khoảng trắng mật khẩu mới</t>
+  </si>
+  <si>
+    <t>Mật khẩu đã thay đổi. Hãy đăng nhập lại</t>
+  </si>
+  <si>
+    <t>http://localhost:4200</t>
+  </si>
+  <si>
+    <t>Nhập hợp lệ</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>Sữa hạt khỏe</t>
+  </si>
+  <si>
+    <t>http://localhost:4200/productsearch?KeyWord=Sữa%20hạt%20khỏe</t>
+  </si>
+  <si>
+    <t>Nhập đúng tên sản phẩm</t>
+  </si>
+  <si>
+    <t>Tất cả sản phẩm</t>
+  </si>
+  <si>
+    <t>http://localhost:4200/productsearch</t>
+  </si>
+  <si>
+    <t>Không nhập tên sản phẩm</t>
+  </si>
+  <si>
+    <t>http://localhost:4200/productsearch?KeyWord=%20%20%20%20%20</t>
+  </si>
+  <si>
+    <t>Nhập khoảng trắng tên sản phẩm</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>Không có sản phẩm</t>
+  </si>
+  <si>
+    <t>http://localhost:4200/productsearch?KeyWord=abc</t>
+  </si>
+  <si>
+    <t>Nhập sản phẩm không tồn tại</t>
+  </si>
+  <si>
+    <t>Sữa</t>
+  </si>
+  <si>
+    <t>http://localhost:4200/productsearch?KeyWord=S%E1%BB%Afa</t>
+  </si>
+  <si>
+    <t>Nhập 1 phần tên sản phẩm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Sữa hạt khỏe   </t>
+  </si>
+  <si>
+    <t>http://localhost:4200/productsearch?KeyWord=%20%20%20%20Sữa%20hạt%20khỏe%20%20%20</t>
+  </si>
+  <si>
+    <t>Nhập khoảng trắng ở đầu, cuối</t>
+  </si>
+  <si>
+    <t>http://localhost:4200/productsearch?KeyWord=1.000.000</t>
+  </si>
+  <si>
+    <t>Nhập tên sản phẩm là số</t>
+  </si>
+  <si>
+    <t>@!@</t>
+  </si>
+  <si>
+    <t>http://localhost:4200/productsearch?KeyWord=@!@</t>
+  </si>
+  <si>
+    <t>Nhập tên sản phẩm là ký tự đặc biệt</t>
+  </si>
+  <si>
+    <t>Sdt</t>
+  </si>
+  <si>
+    <t>Cmnd</t>
+  </si>
+  <si>
+    <t>Mgt</t>
+  </si>
+  <si>
+    <t>District</t>
+  </si>
+  <si>
+    <t>0373824300</t>
+  </si>
+  <si>
+    <t>003203003111</t>
+  </si>
+  <si>
+    <t>Adminmaster</t>
+  </si>
+  <si>
+    <t>Vui lòng nhập tên</t>
+  </si>
+  <si>
+    <t>http://localhost:4200/</t>
+  </si>
+  <si>
+    <t>Để trống tên người dùng</t>
+  </si>
+  <si>
+    <t>0373824301</t>
+  </si>
+  <si>
+    <t>003203003112</t>
+  </si>
+  <si>
+    <t>Tên không được chứa khoảng trắng</t>
+  </si>
+  <si>
+    <t>Nhập tên bằng ký tự trắng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Trần Thị Kim Chi</t>
+  </si>
+  <si>
+    <t>0373824302</t>
+  </si>
+  <si>
+    <t>003203003113</t>
+  </si>
+  <si>
+    <t>Nhập tên chứa ký tự trắng (Đầu)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trần Thị Kim Chi   </t>
+  </si>
+  <si>
+    <t>0373824303</t>
+  </si>
+  <si>
+    <t>003203003114</t>
+  </si>
+  <si>
+    <t>Nhập tên chứa ký tự trắng (Cuối)</t>
+  </si>
+  <si>
+    <t>Ngô Quang Dũng</t>
+  </si>
+  <si>
+    <t>003203003115</t>
+  </si>
+  <si>
+    <t>Vui lòng nhập số điện thoại</t>
+  </si>
+  <si>
+    <t>Để trống Sđt</t>
+  </si>
+  <si>
+    <t>003203003116</t>
+  </si>
+  <si>
+    <t>SĐT không được chứa khoảng trắng</t>
+  </si>
+  <si>
+    <t>Nhập sđt bằng ký tự trắng</t>
+  </si>
+  <si>
+    <t>003203003117</t>
+  </si>
+  <si>
+    <t>Nhập sđt đã tồn tại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   0373824306</t>
+  </si>
+  <si>
+    <t>Nhập sđt chứa ký tự trắng (Đầu)</t>
+  </si>
+  <si>
+    <t>0373   824307</t>
+  </si>
+  <si>
+    <t>003203003118</t>
+  </si>
+  <si>
+    <t>Nhập sđt chứa ký tự trắng (Giữa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0373824308   </t>
+  </si>
+  <si>
+    <t>003203003119</t>
+  </si>
+  <si>
+    <t>Nhập sđt chứa ký tự trắng (Cuối)</t>
+  </si>
+  <si>
+    <t>Trịnh Công Sơn</t>
+  </si>
+  <si>
+    <t>0373824309</t>
+  </si>
+  <si>
+    <t>Vui lòng nhập CMND/CCCD</t>
+  </si>
+  <si>
+    <t>Để trống CMND</t>
+  </si>
+  <si>
+    <t>0373824310</t>
+  </si>
+  <si>
+    <t>CCCD không được chứa khoảng trắng</t>
+  </si>
+  <si>
+    <t>Nhập CMND bằng ký tự trắng</t>
+  </si>
+  <si>
+    <t>0373824311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   003203003122</t>
+  </si>
+  <si>
+    <t>Nhập CMND chứa ký tự trắng (Đầu)</t>
+  </si>
+  <si>
+    <t>0373824312</t>
+  </si>
+  <si>
+    <t>003203   003123</t>
+  </si>
+  <si>
+    <t>Nhập CMND chứa ký tự trắng (Giữa)</t>
+  </si>
+  <si>
+    <t>0373824313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">003203003124    </t>
+  </si>
+  <si>
+    <t>Nhập CMND chứa ký tự trắng (Cuối)</t>
+  </si>
+  <si>
+    <t>Lê Xuân Thu</t>
+  </si>
+  <si>
+    <t>0373824314</t>
+  </si>
+  <si>
+    <t>003203003125</t>
+  </si>
+  <si>
+    <t>0373824315</t>
+  </si>
+  <si>
+    <t>003203003126</t>
+  </si>
+  <si>
+    <t>Email không được chứa khoảng trắng</t>
+  </si>
+  <si>
+    <t>0373824316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Tungsyo1910@gmail.com</t>
+  </si>
+  <si>
+    <t>003203003127</t>
+  </si>
+  <si>
+    <t>0373824317</t>
+  </si>
+  <si>
+    <t>Tungsyo 1910@gmail.com</t>
+  </si>
+  <si>
+    <t>003203003128</t>
+  </si>
+  <si>
+    <t>Định dạng email không hợp lệ</t>
+  </si>
+  <si>
+    <t>0373824318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tungsyo1910@gmail.com     </t>
+  </si>
+  <si>
+    <t>003203003129</t>
+  </si>
+  <si>
+    <t>Lê Thị Lệ</t>
+  </si>
+  <si>
+    <t>0373824319</t>
+  </si>
+  <si>
+    <t>Tungsyo1910gmail.com</t>
+  </si>
+  <si>
+    <t>003203003130</t>
+  </si>
+  <si>
+    <t>Đỗ Thị Kiều Trang</t>
+  </si>
+  <si>
+    <t>0373824320</t>
+  </si>
+  <si>
+    <t>@gmail.com</t>
+  </si>
+  <si>
+    <t>003203003131</t>
+  </si>
+  <si>
+    <t>Đỗ Hữu Quyết</t>
+  </si>
+  <si>
+    <t>0373824321</t>
+  </si>
+  <si>
+    <t>003203003132</t>
+  </si>
+  <si>
+    <t>Vui lòng nhập mật khẩu</t>
+  </si>
+  <si>
+    <t>Để trống mật khẩu</t>
+  </si>
+  <si>
+    <t>Đỗ Hữu Tùng</t>
+  </si>
+  <si>
+    <t>0373824322</t>
+  </si>
+  <si>
+    <t>003203003133</t>
+  </si>
+  <si>
+    <t>Nhập mật khẩu bằng ký tự trắng</t>
+  </si>
+  <si>
+    <t>Đỗ Thu Thuận</t>
+  </si>
+  <si>
+    <t>0373824323</t>
+  </si>
+  <si>
+    <t>003203003134</t>
+  </si>
+  <si>
+    <t>1111111111</t>
+  </si>
+  <si>
+    <t>Mã mời không hợp lệ, người mời không tồn tại</t>
+  </si>
+  <si>
+    <t>Nhập các trường bắt buộc hợp lệ, mã mời không hợp lệ</t>
+  </si>
+  <si>
+    <t>0373824324</t>
+  </si>
+  <si>
+    <t>003203003135</t>
+  </si>
+  <si>
+    <t>Đăng ký thành công</t>
+  </si>
+  <si>
+    <t>Để trống các trường không bắt buộc</t>
+  </si>
+  <si>
+    <t>Ngô Thị Mỹ Linh</t>
+  </si>
+  <si>
+    <t>0373824326</t>
+  </si>
+  <si>
+    <t>003203003137</t>
+  </si>
+  <si>
+    <t>0373824364</t>
+  </si>
+  <si>
+    <t>Hưng Yên</t>
+  </si>
+  <si>
+    <t>Khoái Châu</t>
+  </si>
+  <si>
+    <t>Đông Kết</t>
+  </si>
+  <si>
+    <t>Xóm 17</t>
+  </si>
+  <si>
+    <t>1234567890</t>
+  </si>
+  <si>
+    <t>19/10/2003</t>
+  </si>
+  <si>
+    <t>MB Bank</t>
+  </si>
+  <si>
+    <t>0373824202</t>
+  </si>
+  <si>
+    <t>Nhập tất cả dữ liệu hợp lệ</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công</t>
+  </si>
+  <si>
+    <t>Tài khoản hợp lệ - Case thành công</t>
+  </si>
+  <si>
+    <t xml:space="preserve">              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   adminmaster@gmail.com</t>
+  </si>
+  <si>
+    <t>adminmaste r@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adminmaster@gmail.com    </t>
+  </si>
+  <si>
+    <t>adminmastergmail.com</t>
+  </si>
+  <si>
+    <t>tungtet2003@gmail.com</t>
+  </si>
+  <si>
+    <t>Email người dùng không tồn tại!</t>
+  </si>
+  <si>
+    <t>Nhập email không tồn tại trong CSDL</t>
+  </si>
+  <si>
+    <t>Tài khoản hoặc mật khẩu người dùng không chính xác!</t>
+  </si>
+  <si>
+    <t>adminmas1ter</t>
+  </si>
+  <si>
+    <t>Nhập mật khẩu sai</t>
+  </si>
+  <si>
+    <t>Pop3</t>
+  </si>
+  <si>
+    <t>rdij bbom eecf ahmd</t>
+  </si>
+  <si>
+    <t>enex zlda lgog vyvf</t>
+  </si>
+  <si>
+    <t>033203012145</t>
+  </si>
+  <si>
+    <t>033203012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           </t>
+  </si>
+  <si>
+    <t>Tân Lâp</t>
+  </si>
+  <si>
+    <t>Yên Mỹ</t>
+  </si>
+  <si>
+    <t>Abc</t>
+  </si>
+  <si>
+    <t>022222122</t>
+  </si>
+  <si>
+    <t>10/01/2001</t>
+  </si>
+  <si>
+    <t>MB</t>
+  </si>
+  <si>
+    <t>1172828282</t>
+  </si>
+  <si>
+    <t>Cập nhập thông tin thành công</t>
+  </si>
+  <si>
+    <t>http://localhost:4200/user-information</t>
+  </si>
+  <si>
+    <t>Vui lòng chấp thuận điều kiện giao dịch</t>
+  </si>
+  <si>
+    <t>PHƯƠNG THỨC THANH TOÁN</t>
+  </si>
+  <si>
+    <t>Kiểm tra không chọn ngân hàng khi thanh toán</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>TypeCase</t>
+  </si>
+  <si>
+    <t>One</t>
+  </si>
+  <si>
+    <t>Two</t>
+  </si>
+  <si>
+    <t>Three</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Count</t>
   </si>
   <si>
     <r>
@@ -1437,7 +2144,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <family val="2"/>
+        <family val="1"/>
       </rPr>
       <t>TC_01</t>
     </r>
@@ -1446,7 +2153,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <family val="2"/>
+        <family val="1"/>
       </rPr>
       <t>: Thêm một sản phẩm hợp lệ vào giỏ hàng</t>
     </r>
@@ -1461,7 +2168,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <family val="2"/>
+        <family val="1"/>
       </rPr>
       <t>TC_02</t>
     </r>
@@ -1470,7 +2177,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <family val="2"/>
+        <family val="1"/>
       </rPr>
       <t>: Thêm nhiều sản phẩm khác nhau vào giỏ hàng</t>
     </r>
@@ -1485,7 +2192,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <family val="2"/>
+        <family val="1"/>
       </rPr>
       <t>TC_03</t>
     </r>
@@ -1494,728 +2201,65 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <family val="2"/>
+        <family val="1"/>
       </rPr>
       <t>: Thêm cùng một sản phẩm nhiều lần (check tăng số lượng)</t>
     </r>
   </si>
   <si>
-    <t>Kiểm tra nếu không tích sản phẩm, tích điều khoản có tiến hành thanh toán được không</t>
-  </si>
-  <si>
-    <t>Kiểm tra nếu tích sản phẩm, tích điều khoản có tiến hành thanh toán được không</t>
-  </si>
-  <si>
-    <t>CMND</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>Districts</t>
-  </si>
-  <si>
-    <t>Ward</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Mst</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Bank</t>
-  </si>
-  <si>
-    <t>Stk</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Link</t>
-  </si>
-  <si>
-    <t>TestType</t>
-  </si>
-  <si>
-    <t>Để trông tên</t>
-  </si>
-  <si>
-    <t>Để trông CMND</t>
-  </si>
-  <si>
-    <t>CMND chứa khoảng trắng</t>
-  </si>
-  <si>
-    <t>Nhập các trường không bắt buộc</t>
-  </si>
-  <si>
-    <t>Không nhập các trường không bắt buộc</t>
-  </si>
-  <si>
-    <t>PassNew</t>
-  </si>
-  <si>
-    <t>ComfirmPass</t>
-  </si>
-  <si>
-    <t>Vui lòng nhập email</t>
-  </si>
-  <si>
-    <t>Honivy</t>
-  </si>
-  <si>
-    <t>http://localhost:4200/resend-email-otp</t>
-  </si>
-  <si>
-    <t>Để trống email</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Email không hợp lệ.</t>
-  </si>
-  <si>
-    <t>Nhập email bằng ký tự trắng</t>
-  </si>
-  <si>
-    <t>Nhập email nhưng có ký tự trắng (Đầu)</t>
-  </si>
-  <si>
-    <t>Nhập email nhưng có ký tự trắng (Giữa)</t>
-  </si>
-  <si>
-    <t>Nhập email nhưng có ký tự trắng (Cuối)</t>
-  </si>
-  <si>
-    <t>Nhập email sai định dạng (Không có @)</t>
-  </si>
-  <si>
-    <t>Nhập email sai định dạng (Thiếu tên miền)</t>
-  </si>
-  <si>
-    <t>Vui lòng nhập mật khẩu mới</t>
-  </si>
-  <si>
-    <t>http://localhost:4200/set-password</t>
-  </si>
-  <si>
-    <t>Mất khẩu mới để trống</t>
-  </si>
-  <si>
-    <t>Mật khẩu không được chứa khoảng trắng</t>
-  </si>
-  <si>
-    <t>Mật khẩu mới là khoảng trắng</t>
-  </si>
-  <si>
-    <t>Mật khẩu mới chứa khoảng trắng</t>
-  </si>
-  <si>
-    <t>Mật khẩu xác nhận không khớp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Để trống xác nhận mật khẩu mới </t>
-  </si>
-  <si>
-    <t>Mật khẩu xác nhận không hợp lệ</t>
-  </si>
-  <si>
-    <t>Vui lòng nhập OTP</t>
-  </si>
-  <si>
-    <t>Không điền OTP</t>
-  </si>
-  <si>
-    <t>Thêm 1 cái xác nhận email ở action để nhập OTP</t>
-  </si>
-  <si>
-    <t>Điền OTP không hợp lệ</t>
-  </si>
-  <si>
-    <t>Còn đâu cứ fail là không cho nhập OTP</t>
-  </si>
-  <si>
-    <t>Success</t>
-  </si>
-  <si>
-    <t>PassOld</t>
-  </si>
-  <si>
-    <t>adminmaster1</t>
-  </si>
-  <si>
-    <t>Vui lòng nhập mật khẩu cũ</t>
-  </si>
-  <si>
-    <t>http://localhost:4200/change-password</t>
-  </si>
-  <si>
-    <t>Để trống mật khẩu cũ</t>
-  </si>
-  <si>
-    <t>adminmaster2</t>
-  </si>
-  <si>
-    <t>Mật khẩu cũ không hợp lệ</t>
-  </si>
-  <si>
-    <t>Nhập sai mật khẩu cũ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     </t>
-  </si>
-  <si>
-    <t>adminmaster3</t>
-  </si>
-  <si>
-    <t>Mật khẩu không được chứa khoảng trắng.</t>
-  </si>
-  <si>
-    <t>Nhập khoảng trắng mật khẩu cũ</t>
-  </si>
-  <si>
-    <t>Mật khẩu mới không được trùng với mật khẩu cũ.</t>
-  </si>
-  <si>
-    <t>Nhập cũ trùng mới</t>
-  </si>
-  <si>
-    <t>Để trống mật khẩu mới</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          </t>
-  </si>
-  <si>
-    <t>Nhập khoảng trắng mật khẩu mới</t>
-  </si>
-  <si>
-    <t>Mật khẩu đã thay đổi. Hãy đăng nhập lại</t>
-  </si>
-  <si>
-    <t>http://localhost:4200</t>
-  </si>
-  <si>
-    <t>Nhập hợp lệ</t>
-  </si>
-  <si>
-    <t>Search</t>
-  </si>
-  <si>
-    <t>Sữa hạt khỏe</t>
-  </si>
-  <si>
-    <t>http://localhost:4200/productsearch?KeyWord=Sữa%20hạt%20khỏe</t>
-  </si>
-  <si>
-    <t>Nhập đúng tên sản phẩm</t>
-  </si>
-  <si>
-    <t>Tất cả sản phẩm</t>
-  </si>
-  <si>
-    <t>http://localhost:4200/productsearch</t>
-  </si>
-  <si>
-    <t>Không nhập tên sản phẩm</t>
-  </si>
-  <si>
-    <t>http://localhost:4200/productsearch?KeyWord=%20%20%20%20%20</t>
-  </si>
-  <si>
-    <t>Nhập khoảng trắng tên sản phẩm</t>
-  </si>
-  <si>
-    <t>abc</t>
-  </si>
-  <si>
-    <t>Không có sản phẩm</t>
-  </si>
-  <si>
-    <t>http://localhost:4200/productsearch?KeyWord=abc</t>
-  </si>
-  <si>
-    <t>Nhập sản phẩm không tồn tại</t>
-  </si>
-  <si>
-    <t>Sữa</t>
-  </si>
-  <si>
-    <t>http://localhost:4200/productsearch?KeyWord=S%E1%BB%Afa</t>
-  </si>
-  <si>
-    <t>Nhập 1 phần tên sản phẩm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Sữa hạt khỏe   </t>
-  </si>
-  <si>
-    <t>http://localhost:4200/productsearch?KeyWord=%20%20%20%20Sữa%20hạt%20khỏe%20%20%20</t>
-  </si>
-  <si>
-    <t>Nhập khoảng trắng ở đầu, cuối</t>
-  </si>
-  <si>
-    <t>http://localhost:4200/productsearch?KeyWord=1.000.000</t>
-  </si>
-  <si>
-    <t>Nhập tên sản phẩm là số</t>
-  </si>
-  <si>
-    <t>@!@</t>
-  </si>
-  <si>
-    <t>http://localhost:4200/productsearch?KeyWord=@!@</t>
-  </si>
-  <si>
-    <t>Nhập tên sản phẩm là ký tự đặc biệt</t>
-  </si>
-  <si>
-    <t>Sdt</t>
-  </si>
-  <si>
-    <t>Cmnd</t>
-  </si>
-  <si>
-    <t>Mgt</t>
-  </si>
-  <si>
-    <t>District</t>
-  </si>
-  <si>
-    <t>0373824300</t>
-  </si>
-  <si>
-    <t>003203003111</t>
-  </si>
-  <si>
-    <t>Adminmaster</t>
-  </si>
-  <si>
-    <t>Vui lòng nhập tên</t>
-  </si>
-  <si>
-    <t>http://localhost:4200/</t>
-  </si>
-  <si>
-    <t>Để trống tên người dùng</t>
-  </si>
-  <si>
-    <t>0373824301</t>
-  </si>
-  <si>
-    <t>003203003112</t>
-  </si>
-  <si>
-    <t>Tên không được chứa khoảng trắng</t>
-  </si>
-  <si>
-    <t>Nhập tên bằng ký tự trắng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Trần Thị Kim Chi</t>
-  </si>
-  <si>
-    <t>0373824302</t>
-  </si>
-  <si>
-    <t>003203003113</t>
-  </si>
-  <si>
-    <t>Nhập tên chứa ký tự trắng (Đầu)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trần Thị Kim Chi   </t>
-  </si>
-  <si>
-    <t>0373824303</t>
-  </si>
-  <si>
-    <t>003203003114</t>
-  </si>
-  <si>
-    <t>Nhập tên chứa ký tự trắng (Cuối)</t>
-  </si>
-  <si>
-    <t>Ngô Quang Dũng</t>
-  </si>
-  <si>
-    <t>003203003115</t>
-  </si>
-  <si>
-    <t>Vui lòng nhập số điện thoại</t>
-  </si>
-  <si>
-    <t>Để trống Sđt</t>
-  </si>
-  <si>
-    <t>003203003116</t>
-  </si>
-  <si>
-    <t>SĐT không được chứa khoảng trắng</t>
-  </si>
-  <si>
-    <t>Nhập sđt bằng ký tự trắng</t>
-  </si>
-  <si>
-    <t>003203003117</t>
-  </si>
-  <si>
-    <t>Nhập sđt đã tồn tại</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   0373824306</t>
-  </si>
-  <si>
-    <t>Nhập sđt chứa ký tự trắng (Đầu)</t>
-  </si>
-  <si>
-    <t>0373   824307</t>
-  </si>
-  <si>
-    <t>003203003118</t>
-  </si>
-  <si>
-    <t>Nhập sđt chứa ký tự trắng (Giữa)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0373824308   </t>
-  </si>
-  <si>
-    <t>003203003119</t>
-  </si>
-  <si>
-    <t>Nhập sđt chứa ký tự trắng (Cuối)</t>
-  </si>
-  <si>
-    <t>Trịnh Công Sơn</t>
-  </si>
-  <si>
-    <t>0373824309</t>
-  </si>
-  <si>
-    <t>Vui lòng nhập CMND/CCCD</t>
-  </si>
-  <si>
-    <t>Để trống CMND</t>
-  </si>
-  <si>
-    <t>0373824310</t>
-  </si>
-  <si>
-    <t>CCCD không được chứa khoảng trắng</t>
-  </si>
-  <si>
-    <t>Nhập CMND bằng ký tự trắng</t>
-  </si>
-  <si>
-    <t>0373824311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   003203003122</t>
-  </si>
-  <si>
-    <t>Nhập CMND chứa ký tự trắng (Đầu)</t>
-  </si>
-  <si>
-    <t>0373824312</t>
-  </si>
-  <si>
-    <t>003203   003123</t>
-  </si>
-  <si>
-    <t>Nhập CMND chứa ký tự trắng (Giữa)</t>
-  </si>
-  <si>
-    <t>0373824313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">003203003124    </t>
-  </si>
-  <si>
-    <t>Nhập CMND chứa ký tự trắng (Cuối)</t>
-  </si>
-  <si>
-    <t>Lê Xuân Thu</t>
-  </si>
-  <si>
-    <t>0373824314</t>
-  </si>
-  <si>
-    <t>003203003125</t>
-  </si>
-  <si>
-    <t>0373824315</t>
-  </si>
-  <si>
-    <t>003203003126</t>
-  </si>
-  <si>
-    <t>Email không được chứa khoảng trắng</t>
-  </si>
-  <si>
-    <t>0373824316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     Tungsyo1910@gmail.com</t>
-  </si>
-  <si>
-    <t>003203003127</t>
-  </si>
-  <si>
-    <t>0373824317</t>
-  </si>
-  <si>
-    <t>Tungsyo 1910@gmail.com</t>
-  </si>
-  <si>
-    <t>003203003128</t>
-  </si>
-  <si>
-    <t>Định dạng email không hợp lệ</t>
-  </si>
-  <si>
-    <t>0373824318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tungsyo1910@gmail.com     </t>
-  </si>
-  <si>
-    <t>003203003129</t>
-  </si>
-  <si>
-    <t>Lê Thị Lệ</t>
-  </si>
-  <si>
-    <t>0373824319</t>
-  </si>
-  <si>
-    <t>Tungsyo1910gmail.com</t>
-  </si>
-  <si>
-    <t>003203003130</t>
-  </si>
-  <si>
-    <t>Đỗ Thị Kiều Trang</t>
-  </si>
-  <si>
-    <t>0373824320</t>
-  </si>
-  <si>
-    <t>@gmail.com</t>
-  </si>
-  <si>
-    <t>003203003131</t>
-  </si>
-  <si>
-    <t>Đỗ Hữu Quyết</t>
-  </si>
-  <si>
-    <t>0373824321</t>
-  </si>
-  <si>
-    <t>003203003132</t>
-  </si>
-  <si>
-    <t>Vui lòng nhập mật khẩu</t>
-  </si>
-  <si>
-    <t>Để trống mật khẩu</t>
-  </si>
-  <si>
-    <t>Đỗ Hữu Tùng</t>
-  </si>
-  <si>
-    <t>0373824322</t>
-  </si>
-  <si>
-    <t>003203003133</t>
-  </si>
-  <si>
-    <t>Nhập mật khẩu bằng ký tự trắng</t>
-  </si>
-  <si>
-    <t>Đỗ Thu Thuận</t>
-  </si>
-  <si>
-    <t>0373824323</t>
-  </si>
-  <si>
-    <t>003203003134</t>
-  </si>
-  <si>
-    <t>1111111111</t>
-  </si>
-  <si>
-    <t>Mã mời không hợp lệ, người mời không tồn tại</t>
-  </si>
-  <si>
-    <t>Nhập các trường bắt buộc hợp lệ, mã mời không hợp lệ</t>
-  </si>
-  <si>
-    <t>0373824324</t>
-  </si>
-  <si>
-    <t>003203003135</t>
-  </si>
-  <si>
-    <t>Đăng ký thành công</t>
-  </si>
-  <si>
-    <t>Để trống các trường không bắt buộc</t>
-  </si>
-  <si>
-    <t>Ngô Thị Mỹ Linh</t>
-  </si>
-  <si>
-    <t>0373824326</t>
-  </si>
-  <si>
-    <t>003203003137</t>
-  </si>
-  <si>
-    <t>0373824364</t>
-  </si>
-  <si>
-    <t>Hưng Yên</t>
-  </si>
-  <si>
-    <t>Khoái Châu</t>
-  </si>
-  <si>
-    <t>Đông Kết</t>
-  </si>
-  <si>
-    <t>Xóm 17</t>
-  </si>
-  <si>
-    <t>1234567890</t>
-  </si>
-  <si>
-    <t>19/10/2003</t>
-  </si>
-  <si>
-    <t>MB Bank</t>
-  </si>
-  <si>
-    <t>0373824202</t>
-  </si>
-  <si>
-    <t>Nhập tất cả dữ liệu hợp lệ</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Đăng nhập thành công</t>
-  </si>
-  <si>
-    <t>Tài khoản hợp lệ - Case thành công</t>
-  </si>
-  <si>
-    <t xml:space="preserve">              </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   adminmaster@gmail.com</t>
-  </si>
-  <si>
-    <t>adminmaste r@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adminmaster@gmail.com    </t>
-  </si>
-  <si>
-    <t>adminmastergmail.com</t>
-  </si>
-  <si>
-    <t>tungtet2003@gmail.com</t>
-  </si>
-  <si>
-    <t>Email người dùng không tồn tại!</t>
-  </si>
-  <si>
-    <t>Nhập email không tồn tại trong CSDL</t>
-  </si>
-  <si>
-    <t>Tài khoản hoặc mật khẩu người dùng không chính xác!</t>
-  </si>
-  <si>
-    <t>adminmas1ter</t>
-  </si>
-  <si>
-    <t>Nhập mật khẩu sai</t>
-  </si>
-  <si>
-    <t>Pop3</t>
-  </si>
-  <si>
-    <t>rdij bbom eecf ahmd</t>
-  </si>
-  <si>
-    <t>enex zlda lgog vyvf</t>
-  </si>
-  <si>
-    <t>033203012145</t>
-  </si>
-  <si>
-    <t>033203012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">           </t>
-  </si>
-  <si>
-    <t>Tân Lâp</t>
-  </si>
-  <si>
-    <t>Yên Mỹ</t>
-  </si>
-  <si>
-    <t>Abc</t>
-  </si>
-  <si>
-    <t>022222122</t>
-  </si>
-  <si>
-    <t>10/01/2001</t>
-  </si>
-  <si>
-    <t>MB</t>
-  </si>
-  <si>
-    <t>1172828282</t>
-  </si>
-  <si>
-    <t>Cập nhập thông tin thành công</t>
-  </si>
-  <si>
-    <t>http://localhost:4200/user-information</t>
-  </si>
-  <si>
-    <t>Vui lòng chấp thuận điều kiện giao dịch</t>
-  </si>
-  <si>
-    <t>PHƯƠNG THỨC THANH TOÁN</t>
-  </si>
-  <si>
-    <t>Kiểm tra không chọn ngân hàng khi thanh toán</t>
-  </si>
-  <si>
-    <t>s</t>
+    <t>Tăng số lượng</t>
+  </si>
+  <si>
+    <t>Giảm số lượng</t>
+  </si>
+  <si>
+    <t>Kiểm tra nếu không tích sản phẩm, tích điều khoản</t>
+  </si>
+  <si>
+    <t>Kiểm tra nếu tích sản phẩm, tích điều khoản</t>
+  </si>
+  <si>
+    <t>Không có sản phẩm nào được chọn để thanh toán</t>
+  </si>
+  <si>
+    <t>Kiểm tra nếu tích sản phẩm, không tích điều khoản</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm vào giỏ thành công</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Sữa hạt tươi</t>
+  </si>
+  <si>
+    <t>1,000,000</t>
+  </si>
+  <si>
+    <t>3,000,000</t>
+  </si>
+  <si>
+    <t>5,000,000</t>
+  </si>
+  <si>
+    <t>http://localhost:4200/cart</t>
+  </si>
+  <si>
+    <t>Khi code thêm sữa hạt tươi 1 lần rồi tăng số lượng lên 5 trong giỏ hàng</t>
+  </si>
+  <si>
+    <t>Khi code thêm 5 lần rồi giảm về 3</t>
+  </si>
+  <si>
+    <t>Khi code thêm 1 rồi xem có giảm về 0 được không</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2237,20 +2281,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="2"/>
@@ -2356,6 +2386,13 @@
       <name val="Times New Roman"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2384,7 +2421,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2419,16 +2456,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2444,80 +2475,83 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2528,40 +2562,34 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2571,17 +2599,35 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2905,304 +2951,304 @@
         <v>5</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>435</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="40" t="s">
+        <v>661</v>
+      </c>
+      <c r="D2" s="39" t="s">
+        <v>479</v>
+      </c>
+      <c r="E2" s="41" t="s">
+        <v>557</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>662</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="34"/>
+      <c r="B3" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>478</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>557</v>
+      </c>
+      <c r="F3" s="34" t="s">
+        <v>481</v>
+      </c>
+      <c r="G3" s="34" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="34" t="s">
+        <v>663</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>616</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>557</v>
+      </c>
+      <c r="F4" s="34" t="s">
+        <v>484</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="34" t="s">
+        <v>664</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>616</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>557</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>485</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="34" t="s">
+        <v>665</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>616</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>557</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>486</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="34" t="s">
+        <v>666</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>616</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>557</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>487</v>
+      </c>
+      <c r="G7" s="34" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="34" t="s">
+        <v>667</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>616</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>557</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>488</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="34" t="s">
+        <v>626</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>616</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>557</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>489</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="34" t="s">
+        <v>668</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>669</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="E10" s="36" t="s">
+        <v>557</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>670</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="37"/>
+      <c r="C11" s="35" t="s">
+        <v>631</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>557</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>632</v>
+      </c>
+      <c r="G11" s="34" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>663</v>
+      </c>
+      <c r="C12" s="35" t="s">
         <v>671</v>
       </c>
-      <c r="D2" s="45" t="s">
-        <v>489</v>
-      </c>
-      <c r="E2" s="47" t="s">
-        <v>567</v>
-      </c>
-      <c r="F2" s="45" t="s">
+      <c r="D12" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="E12" s="36" t="s">
+        <v>557</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>636</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="34" t="s">
         <v>672</v>
       </c>
-      <c r="G2" s="45" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40"/>
-      <c r="B3" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="41" t="s">
-        <v>488</v>
-      </c>
-      <c r="D3" s="40" t="s">
-        <v>489</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>567</v>
-      </c>
-      <c r="F3" s="40" t="s">
-        <v>491</v>
-      </c>
-      <c r="G3" s="40" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
+      <c r="C13" s="35" t="s">
+        <v>671</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>557</v>
+      </c>
+      <c r="F13" s="34" t="s">
         <v>673</v>
       </c>
-      <c r="B4" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="40" t="s">
-        <v>626</v>
-      </c>
-      <c r="D4" s="40" t="s">
-        <v>489</v>
-      </c>
-      <c r="E4" s="42" t="s">
-        <v>567</v>
-      </c>
-      <c r="F4" s="40" t="s">
-        <v>494</v>
-      </c>
-      <c r="G4" s="40" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
-        <v>674</v>
-      </c>
-      <c r="B5" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="40" t="s">
-        <v>626</v>
-      </c>
-      <c r="D5" s="40" t="s">
-        <v>489</v>
-      </c>
-      <c r="E5" s="42" t="s">
-        <v>567</v>
-      </c>
-      <c r="F5" s="40" t="s">
-        <v>495</v>
-      </c>
-      <c r="G5" s="40" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
-        <v>675</v>
-      </c>
-      <c r="B6" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>626</v>
-      </c>
-      <c r="D6" s="40" t="s">
-        <v>489</v>
-      </c>
-      <c r="E6" s="42" t="s">
-        <v>567</v>
-      </c>
-      <c r="F6" s="40" t="s">
-        <v>496</v>
-      </c>
-      <c r="G6" s="40" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="40" t="s">
-        <v>676</v>
-      </c>
-      <c r="B7" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>626</v>
-      </c>
-      <c r="D7" s="40" t="s">
-        <v>489</v>
-      </c>
-      <c r="E7" s="42" t="s">
-        <v>567</v>
-      </c>
-      <c r="F7" s="40" t="s">
-        <v>497</v>
-      </c>
-      <c r="G7" s="40" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="40" t="s">
-        <v>677</v>
-      </c>
-      <c r="B8" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>626</v>
-      </c>
-      <c r="D8" s="40" t="s">
-        <v>489</v>
-      </c>
-      <c r="E8" s="42" t="s">
-        <v>567</v>
-      </c>
-      <c r="F8" s="40" t="s">
-        <v>498</v>
-      </c>
-      <c r="G8" s="40" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="40" t="s">
-        <v>636</v>
-      </c>
-      <c r="B9" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>626</v>
-      </c>
-      <c r="D9" s="40" t="s">
-        <v>489</v>
-      </c>
-      <c r="E9" s="42" t="s">
-        <v>567</v>
-      </c>
-      <c r="F9" s="40" t="s">
-        <v>499</v>
-      </c>
-      <c r="G9" s="40" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="40" t="s">
-        <v>678</v>
-      </c>
-      <c r="B10" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>679</v>
-      </c>
-      <c r="D10" s="40" t="s">
-        <v>489</v>
-      </c>
-      <c r="E10" s="42" t="s">
-        <v>567</v>
-      </c>
-      <c r="F10" s="40" t="s">
-        <v>680</v>
-      </c>
-      <c r="G10" s="40" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="41" t="s">
-        <v>641</v>
-      </c>
-      <c r="D11" s="40" t="s">
-        <v>489</v>
-      </c>
-      <c r="E11" s="42" t="s">
-        <v>567</v>
-      </c>
-      <c r="F11" s="40" t="s">
-        <v>642</v>
-      </c>
-      <c r="G11" s="40" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="40" t="s">
-        <v>673</v>
-      </c>
-      <c r="C12" s="41" t="s">
-        <v>681</v>
-      </c>
-      <c r="D12" s="40" t="s">
-        <v>489</v>
-      </c>
-      <c r="E12" s="42" t="s">
-        <v>567</v>
-      </c>
-      <c r="F12" s="40" t="s">
-        <v>646</v>
-      </c>
-      <c r="G12" s="40" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="40" t="s">
-        <v>682</v>
-      </c>
-      <c r="C13" s="41" t="s">
-        <v>681</v>
-      </c>
-      <c r="D13" s="40" t="s">
-        <v>489</v>
-      </c>
-      <c r="E13" s="42" t="s">
-        <v>567</v>
-      </c>
-      <c r="F13" s="40" t="s">
-        <v>683</v>
-      </c>
-      <c r="G13" s="40" t="s">
-        <v>492</v>
+      <c r="G13" s="34" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="44"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
+      <c r="A14" s="38"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3210,82 +3256,121 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="K1:L30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5F8304C-5BAE-4226-B1AC-AE8EDE2ABD4B}">
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="10" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="51.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="21"/>
+    <col min="2" max="2" width="11.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="21"/>
+    <col min="4" max="4" width="21.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="21"/>
+    <col min="8" max="8" width="61.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K1" s="4" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>697</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>467</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>468</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>469</v>
+      </c>
+      <c r="E1" s="20" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="2" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K2" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="3" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K3" s="4" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="4" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K4" s="4" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="5" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L25" s="12"/>
-    </row>
-    <row r="26" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L26" s="4"/>
-    </row>
-    <row r="27" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L27" s="4"/>
-    </row>
-    <row r="28" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L28" s="4"/>
-    </row>
-    <row r="29" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L29" s="4"/>
-    </row>
-    <row r="30" spans="12:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L30" s="4"/>
+      <c r="F1" s="64" t="s">
+        <v>470</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
+        <v>713</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>710</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>479</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>714</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>702</v>
+      </c>
+      <c r="F2" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>694</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>712</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>710</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>479</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>714</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>703</v>
+      </c>
+      <c r="F3" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>695</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>711</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>710</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>479</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>714</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="F4" s="64" t="s">
+        <v>482</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>696</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>717</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3297,54 +3382,87 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="K1:L25"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="10" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="57.85546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="9.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20" style="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="9.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="38" style="64" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="40.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K1" s="4" t="s">
+    <row r="1" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>697</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>467</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>468</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>469</v>
+      </c>
+      <c r="E1" s="20" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="2" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K2" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="3" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K3" s="4" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="4" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K4" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="F1" s="64" t="s">
+        <v>470</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>693</v>
+      </c>
+      <c r="K1" s="20"/>
+      <c r="L1" s="64"/>
+    </row>
+    <row r="2" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="F2" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E3" s="20" t="s">
+        <v>452</v>
+      </c>
+      <c r="F3" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E4" s="20"/>
+      <c r="F4" s="64"/>
+    </row>
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K7" s="20"/>
+    </row>
+    <row r="8" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="11:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="11:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="11:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="20" spans="11:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K20" s="12"/>
+      <c r="K20" s="65"/>
     </row>
     <row r="21" spans="11:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="11:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3357,71 +3475,11 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{437290B0-5E81-4A05-A34E-6AB615E82B9D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="11" max="11" width="9.140625" customWidth="1"/>
-  </cols>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC05FA6D-AE89-4E2F-AB13-40AB94C75E25}">
-  <dimension ref="N1:N7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="14" max="14" width="36.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="14:14" x14ac:dyDescent="0.25">
-      <c r="N1" s="10" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="2" spans="14:14" x14ac:dyDescent="0.25">
-      <c r="N2" s="10" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="3" spans="14:14" x14ac:dyDescent="0.25">
-      <c r="N3" s="10" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="4" spans="14:14" x14ac:dyDescent="0.25">
-      <c r="N4" s="10" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="5" spans="14:14" x14ac:dyDescent="0.25">
-      <c r="N5" s="10" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="6" spans="14:14" x14ac:dyDescent="0.25">
-      <c r="N6" s="10" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="7" spans="14:14" x14ac:dyDescent="0.25">
-      <c r="N7" s="10" t="s">
-        <v>451</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="N1:P15"/>
+  <dimension ref="N1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="13" width="9.140625" bestFit="1" customWidth="1"/>
@@ -3433,7 +3491,9 @@
       <c r="N1" s="10" t="s">
         <v>435</v>
       </c>
-      <c r="O1" s="10"/>
+      <c r="O1" s="10" t="s">
+        <v>470</v>
+      </c>
       <c r="P1" s="10"/>
     </row>
     <row r="2" spans="14:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3450,7 +3510,7 @@
         <v>447</v>
       </c>
       <c r="O3" s="10" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="P3" s="10"/>
     </row>
@@ -3459,7 +3519,7 @@
         <v>448</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="P4" s="10"/>
     </row>
@@ -3468,65 +3528,175 @@
         <v>449</v>
       </c>
       <c r="O5" s="10" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="P5" s="10"/>
     </row>
     <row r="6" spans="14:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N6" s="10" t="s">
+        <v>691</v>
+      </c>
+      <c r="O6" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="P6" s="10"/>
+    </row>
+    <row r="7" spans="14:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N7" s="10" t="s">
         <v>450</v>
       </c>
-      <c r="O6" s="10" t="s">
-        <v>492</v>
-      </c>
-      <c r="P6" s="10"/>
-    </row>
-    <row r="7" spans="14:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N7" s="10" t="s">
-        <v>701</v>
-      </c>
       <c r="O7" s="10" t="s">
-        <v>492</v>
+        <v>6</v>
       </c>
       <c r="P7" s="10"/>
     </row>
     <row r="8" spans="14:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N8" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="O8" s="10" t="s">
-        <v>6</v>
-      </c>
+      <c r="O8" s="10"/>
       <c r="P8" s="10"/>
     </row>
     <row r="9" spans="14:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N9" s="10" t="s">
-        <v>452</v>
-      </c>
-      <c r="O9" s="10" t="s">
-        <v>6</v>
-      </c>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
       <c r="P9" s="10"/>
     </row>
-    <row r="10" spans="14:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N10" s="10"/>
+    <row r="10" spans="14:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O10" s="10"/>
       <c r="P10" s="10"/>
     </row>
-    <row r="11" spans="14:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-    </row>
-    <row r="12" spans="14:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="14:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="14:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N14" s="1">
+    <row r="11" spans="14:16" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="14:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="14:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="14:16" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
+    <row r="14" spans="14:16" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC05FA6D-AE89-4E2F-AB13-40AB94C75E25}">
+  <dimension ref="N1:O6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="14" max="14" width="45" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N1" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="2" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N2" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N3" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N4" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="O4" s="10" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="5" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N5" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="6" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N6" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="O6" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3906E0C-2913-4420-B5BB-E88615191874}">
+  <dimension ref="N1:O6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="13" width="9.140625" style="24"/>
+    <col min="14" max="14" width="51.42578125" style="24" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N1" s="33" t="s">
+        <v>435</v>
+      </c>
+      <c r="O1" s="24" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="2" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N2" s="33" t="s">
+        <v>446</v>
+      </c>
+      <c r="O2" s="24" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="3" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N3" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="O3" s="24" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N4" s="33" t="s">
+        <v>448</v>
+      </c>
+      <c r="O4" s="24" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="5" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N5" s="33" t="s">
+        <v>449</v>
+      </c>
+      <c r="O5" s="24" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="6" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N6" s="33" t="s">
+        <v>450</v>
+      </c>
+      <c r="O6" s="33" t="s">
+        <v>504</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3534,85 +3704,6 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3906E0C-2913-4420-B5BB-E88615191874}">
-  <dimension ref="N1:O8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="13" width="9.140625" style="30"/>
-    <col min="14" max="14" width="51.42578125" style="30" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="30"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="14:15" x14ac:dyDescent="0.25">
-      <c r="N1" s="39" t="s">
-        <v>435</v>
-      </c>
-      <c r="O1" s="30" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="2" spans="14:15" x14ac:dyDescent="0.25">
-      <c r="N2" s="39" t="s">
-        <v>446</v>
-      </c>
-      <c r="O2" s="30" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="3" spans="14:15" x14ac:dyDescent="0.25">
-      <c r="N3" s="39" t="s">
-        <v>447</v>
-      </c>
-      <c r="O3" s="30" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="4" spans="14:15" x14ac:dyDescent="0.25">
-      <c r="N4" s="39" t="s">
-        <v>448</v>
-      </c>
-      <c r="O4" s="30" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="5" spans="14:15" x14ac:dyDescent="0.25">
-      <c r="N5" s="39" t="s">
-        <v>449</v>
-      </c>
-      <c r="O5" s="30" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="6" spans="14:15" x14ac:dyDescent="0.25">
-      <c r="N6" s="39" t="s">
-        <v>450</v>
-      </c>
-      <c r="O6" s="30" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="7" spans="14:15" x14ac:dyDescent="0.25">
-      <c r="N7" s="39" t="s">
-        <v>451</v>
-      </c>
-      <c r="O7" s="30" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="8" spans="14:15" x14ac:dyDescent="0.25">
-      <c r="N8" s="39" t="s">
-        <v>452</v>
-      </c>
-      <c r="O8" s="39" t="s">
-        <v>514</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -3620,120 +3711,120 @@
   <dimension ref="M1:P16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="12" width="14.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="44" style="38" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.140625" style="38" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="27"/>
+    <col min="1" max="12" width="14.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="44" style="32" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.140625" style="32" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="13:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M1" s="35" t="s">
+      <c r="M1" s="29" t="s">
         <v>435</v>
       </c>
-      <c r="N1" s="38" t="s">
-        <v>480</v>
+      <c r="N1" s="32" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="2" spans="13:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M2" s="35" t="s">
+      <c r="M2" s="29" t="s">
         <v>439</v>
       </c>
-      <c r="N2" s="38" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="3" spans="13:16" s="38" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M3" s="35" t="s">
+      <c r="N2" s="32" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="3" spans="13:16" s="32" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M3" s="29" t="s">
         <v>440</v>
       </c>
-      <c r="N3" s="38" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="4" spans="13:16" s="38" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M4" s="35" t="s">
+      <c r="N3" s="32" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="13:16" s="32" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M4" s="29" t="s">
         <v>441</v>
       </c>
-      <c r="N4" s="38" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="5" spans="13:16" s="38" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M5" s="35" t="s">
+      <c r="N4" s="32" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="5" spans="13:16" s="32" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M5" s="29" t="s">
         <v>442</v>
       </c>
-      <c r="N5" s="38" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="6" spans="13:16" s="38" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M6" s="35" t="s">
+      <c r="N5" s="32" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="6" spans="13:16" s="32" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M6" s="29" t="s">
         <v>443</v>
       </c>
-      <c r="N6" s="38" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="7" spans="13:16" s="38" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M7" s="35" t="s">
+      <c r="N6" s="32" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="7" spans="13:16" s="32" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M7" s="29" t="s">
         <v>444</v>
       </c>
-      <c r="N7" s="38" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="8" spans="13:16" s="38" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M8" s="35" t="s">
+      <c r="N7" s="32" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="8" spans="13:16" s="32" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M8" s="29" t="s">
         <v>445</v>
       </c>
-      <c r="N8" s="38" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="9" spans="13:16" s="38" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M9" s="35"/>
-      <c r="N9" s="35"/>
-    </row>
-    <row r="10" spans="13:16" s="38" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O10" s="35"/>
-      <c r="P10" s="35"/>
-    </row>
-    <row r="11" spans="13:16" s="38" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N11" s="35"/>
-      <c r="O11" s="35"/>
-      <c r="P11" s="35"/>
-    </row>
-    <row r="12" spans="13:16" s="38" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N12" s="35"/>
-      <c r="O12" s="35"/>
-      <c r="P12" s="35"/>
-    </row>
-    <row r="13" spans="13:16" s="38" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N13" s="35"/>
-      <c r="O13" s="35"/>
-      <c r="P13" s="35"/>
-    </row>
-    <row r="14" spans="13:16" s="38" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N14" s="35"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
-    </row>
-    <row r="15" spans="13:16" s="38" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N15" s="35"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="35"/>
-    </row>
-    <row r="16" spans="13:16" s="38" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N16" s="35"/>
-      <c r="O16" s="35"/>
-      <c r="P16" s="35"/>
+      <c r="N8" s="32" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="9" spans="13:16" s="32" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+    </row>
+    <row r="10" spans="13:16" s="32" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O10" s="29"/>
+      <c r="P10" s="29"/>
+    </row>
+    <row r="11" spans="13:16" s="32" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="29"/>
+    </row>
+    <row r="12" spans="13:16" s="32" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N12" s="29"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="29"/>
+    </row>
+    <row r="13" spans="13:16" s="32" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+    </row>
+    <row r="14" spans="13:16" s="32" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+    </row>
+    <row r="15" spans="13:16" s="32" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+    </row>
+    <row r="16" spans="13:16" s="32" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -3741,41 +3832,41 @@
   <dimension ref="K1:L4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="10" width="9.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="27"/>
+    <col min="1" max="10" width="9.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="20" t="s">
         <v>435</v>
       </c>
-      <c r="L1" s="27" t="s">
-        <v>480</v>
+      <c r="L1" s="21" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="2" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="20" t="s">
         <v>436</v>
       </c>
-      <c r="L2" s="27" t="s">
-        <v>514</v>
+      <c r="L2" s="21" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="3" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="20" t="s">
         <v>437</v>
       </c>
-      <c r="L3" s="27" t="s">
-        <v>492</v>
+      <c r="L3" s="21" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="4" spans="11:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K4" s="26" t="s">
+      <c r="K4" s="20" t="s">
         <v>438</v>
       </c>
-      <c r="L4" s="27" t="s">
-        <v>492</v>
+      <c r="L4" s="21" t="s">
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -3783,7 +3874,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -3858,12 +3949,12 @@
         <v>8</v>
       </c>
       <c r="I15" s="6"/>
-      <c r="J15" s="22" t="s">
+      <c r="J15" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="22"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="70"/>
+      <c r="M15" s="70"/>
       <c r="N15" s="7"/>
       <c r="O15" s="8">
         <v>1</v>
@@ -3889,12 +3980,12 @@
         <v>14</v>
       </c>
       <c r="I16" s="6"/>
-      <c r="J16" s="22" t="s">
+      <c r="J16" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="22"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="70"/>
+      <c r="M16" s="70"/>
       <c r="N16" s="7"/>
       <c r="O16" s="8">
         <v>50</v>
@@ -3915,12 +4006,12 @@
         <v>19</v>
       </c>
       <c r="I17" s="6"/>
-      <c r="J17" s="22" t="s">
+      <c r="J17" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="70"/>
+      <c r="M17" s="70"/>
       <c r="N17" s="7"/>
       <c r="O17" s="8">
         <v>51</v>
@@ -3944,12 +4035,12 @@
         <v>25</v>
       </c>
       <c r="I18" s="6"/>
-      <c r="J18" s="22" t="s">
+      <c r="J18" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="22"/>
+      <c r="K18" s="70"/>
+      <c r="L18" s="70"/>
+      <c r="M18" s="70"/>
       <c r="N18" s="7"/>
       <c r="O18" s="8">
         <v>52</v>
@@ -3967,12 +4058,12 @@
         <v>29</v>
       </c>
       <c r="I19" s="6"/>
-      <c r="J19" s="22" t="s">
+      <c r="J19" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="22"/>
+      <c r="K19" s="70"/>
+      <c r="L19" s="70"/>
+      <c r="M19" s="70"/>
       <c r="N19" s="7"/>
       <c r="O19" s="8">
         <v>53</v>
@@ -4021,12 +4112,12 @@
       <c r="R21" s="6"/>
     </row>
     <row r="22" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
       <c r="I22" s="6"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -4045,12 +4136,12 @@
       <c r="R22" s="6"/>
     </row>
     <row r="23" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
+      <c r="C23" s="72"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
       <c r="F23" s="4" t="s">
         <v>42</v>
       </c>
@@ -4068,12 +4159,12 @@
       <c r="R23" s="6"/>
     </row>
     <row r="24" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
       <c r="I24" s="6"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -4092,12 +4183,12 @@
       <c r="R24" s="6"/>
     </row>
     <row r="25" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
+      <c r="C25" s="72"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="72"/>
       <c r="I25" s="6"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -4116,12 +4207,12 @@
       <c r="R25" s="6"/>
     </row>
     <row r="26" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
+      <c r="C26" s="72"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="72"/>
       <c r="I26" s="6"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -4140,17 +4231,17 @@
       <c r="R26" s="6"/>
     </row>
     <row r="27" spans="2:18" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="72" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
+      <c r="C27" s="72"/>
+      <c r="D27" s="72"/>
+      <c r="E27" s="72"/>
       <c r="I27" s="6"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="24"/>
+      <c r="J27" s="69"/>
+      <c r="K27" s="69"/>
+      <c r="L27" s="69"/>
+      <c r="M27" s="69"/>
       <c r="N27" s="7"/>
       <c r="O27" s="8">
         <v>61</v>
@@ -4164,17 +4255,17 @@
       <c r="R27" s="6"/>
     </row>
     <row r="28" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
       <c r="I28" s="6"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="22"/>
+      <c r="J28" s="70"/>
+      <c r="K28" s="70"/>
+      <c r="L28" s="70"/>
+      <c r="M28" s="70"/>
       <c r="N28" s="9"/>
       <c r="O28" s="8">
         <v>62</v>
@@ -4189,10 +4280,10 @@
     </row>
     <row r="29" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I29" s="6"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="22"/>
-      <c r="M29" s="22"/>
+      <c r="J29" s="70"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="70"/>
+      <c r="M29" s="70"/>
       <c r="N29" s="9"/>
       <c r="O29" s="8">
         <v>63</v>
@@ -4207,10 +4298,10 @@
     </row>
     <row r="30" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I30" s="6"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="22"/>
+      <c r="J30" s="70"/>
+      <c r="K30" s="70"/>
+      <c r="L30" s="70"/>
+      <c r="M30" s="70"/>
       <c r="N30" s="9"/>
       <c r="O30" s="8">
         <v>64</v>
@@ -4225,10 +4316,10 @@
     </row>
     <row r="31" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I31" s="6"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
-      <c r="M31" s="22"/>
+      <c r="J31" s="70"/>
+      <c r="K31" s="70"/>
+      <c r="L31" s="70"/>
+      <c r="M31" s="70"/>
       <c r="N31" s="9"/>
       <c r="O31" s="8">
         <v>65</v>
@@ -4243,10 +4334,10 @@
     </row>
     <row r="32" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I32" s="6"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="22"/>
+      <c r="J32" s="70"/>
+      <c r="K32" s="70"/>
+      <c r="L32" s="70"/>
+      <c r="M32" s="70"/>
       <c r="N32" s="9"/>
       <c r="O32" s="8">
         <v>66</v>
@@ -4261,10 +4352,10 @@
     </row>
     <row r="33" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I33" s="6"/>
-      <c r="J33" s="22"/>
-      <c r="K33" s="22"/>
-      <c r="L33" s="22"/>
-      <c r="M33" s="22"/>
+      <c r="J33" s="70"/>
+      <c r="K33" s="70"/>
+      <c r="L33" s="70"/>
+      <c r="M33" s="70"/>
       <c r="N33" s="9"/>
       <c r="O33" s="8">
         <v>67</v>
@@ -4279,10 +4370,10 @@
     </row>
     <row r="34" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I34" s="6"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="22"/>
-      <c r="L34" s="22"/>
-      <c r="M34" s="22"/>
+      <c r="J34" s="70"/>
+      <c r="K34" s="70"/>
+      <c r="L34" s="70"/>
+      <c r="M34" s="70"/>
       <c r="N34" s="9"/>
       <c r="O34" s="8">
         <v>68</v>
@@ -4297,10 +4388,10 @@
     </row>
     <row r="35" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I35" s="6"/>
-      <c r="J35" s="22"/>
-      <c r="K35" s="22"/>
-      <c r="L35" s="22"/>
-      <c r="M35" s="22"/>
+      <c r="J35" s="70"/>
+      <c r="K35" s="70"/>
+      <c r="L35" s="70"/>
+      <c r="M35" s="70"/>
       <c r="N35" s="9"/>
       <c r="O35" s="8">
         <v>69</v>
@@ -4315,10 +4406,10 @@
     </row>
     <row r="36" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I36" s="6"/>
-      <c r="J36" s="22"/>
-      <c r="K36" s="22"/>
-      <c r="L36" s="22"/>
-      <c r="M36" s="22"/>
+      <c r="J36" s="70"/>
+      <c r="K36" s="70"/>
+      <c r="L36" s="70"/>
+      <c r="M36" s="70"/>
       <c r="N36" s="9"/>
       <c r="O36" s="8">
         <v>70</v>
@@ -4336,10 +4427,10 @@
         <v>76</v>
       </c>
       <c r="I37" s="6"/>
-      <c r="J37" s="22"/>
-      <c r="K37" s="22"/>
-      <c r="L37" s="22"/>
-      <c r="M37" s="22"/>
+      <c r="J37" s="70"/>
+      <c r="K37" s="70"/>
+      <c r="L37" s="70"/>
+      <c r="M37" s="70"/>
       <c r="N37" s="9"/>
       <c r="O37" s="8">
         <v>71</v>
@@ -4354,10 +4445,10 @@
     </row>
     <row r="38" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I38" s="6"/>
-      <c r="J38" s="24"/>
-      <c r="K38" s="24"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="24"/>
+      <c r="J38" s="69"/>
+      <c r="K38" s="69"/>
+      <c r="L38" s="69"/>
+      <c r="M38" s="69"/>
       <c r="N38" s="9"/>
       <c r="O38" s="8">
         <v>72</v>
@@ -4372,10 +4463,10 @@
     </row>
     <row r="39" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I39" s="6"/>
-      <c r="J39" s="24"/>
-      <c r="K39" s="24"/>
-      <c r="L39" s="24"/>
-      <c r="M39" s="24"/>
+      <c r="J39" s="69"/>
+      <c r="K39" s="69"/>
+      <c r="L39" s="69"/>
+      <c r="M39" s="69"/>
       <c r="N39" s="9"/>
       <c r="O39" s="8">
         <v>73</v>
@@ -4390,10 +4481,10 @@
     </row>
     <row r="40" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I40" s="6"/>
-      <c r="J40" s="24"/>
-      <c r="K40" s="24"/>
-      <c r="L40" s="24"/>
-      <c r="M40" s="24"/>
+      <c r="J40" s="69"/>
+      <c r="K40" s="69"/>
+      <c r="L40" s="69"/>
+      <c r="M40" s="69"/>
       <c r="N40" s="7"/>
       <c r="O40" s="8">
         <v>74</v>
@@ -4408,10 +4499,10 @@
     </row>
     <row r="41" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I41" s="6"/>
-      <c r="J41" s="24"/>
-      <c r="K41" s="24"/>
-      <c r="L41" s="24"/>
-      <c r="M41" s="24"/>
+      <c r="J41" s="69"/>
+      <c r="K41" s="69"/>
+      <c r="L41" s="69"/>
+      <c r="M41" s="69"/>
       <c r="N41" s="7"/>
       <c r="O41" s="8">
         <v>75</v>
@@ -4426,12 +4517,12 @@
     </row>
     <row r="42" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I42" s="6"/>
-      <c r="J42" s="22" t="s">
+      <c r="J42" s="70" t="s">
         <v>86</v>
       </c>
-      <c r="K42" s="22"/>
-      <c r="L42" s="22"/>
-      <c r="M42" s="22"/>
+      <c r="K42" s="70"/>
+      <c r="L42" s="70"/>
+      <c r="M42" s="70"/>
       <c r="N42" s="9"/>
       <c r="O42" s="8">
         <v>76</v>
@@ -4445,13 +4536,13 @@
       <c r="R42" s="6"/>
     </row>
     <row r="43" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I43" s="25"/>
-      <c r="J43" s="22" t="s">
+      <c r="I43" s="71"/>
+      <c r="J43" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="K43" s="22"/>
-      <c r="L43" s="22"/>
-      <c r="M43" s="22"/>
+      <c r="K43" s="70"/>
+      <c r="L43" s="70"/>
+      <c r="M43" s="70"/>
       <c r="N43" s="9"/>
       <c r="O43" s="8">
         <v>77</v>
@@ -4465,13 +4556,13 @@
       <c r="R43" s="6"/>
     </row>
     <row r="44" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I44" s="23"/>
-      <c r="J44" s="22" t="s">
+      <c r="I44" s="72"/>
+      <c r="J44" s="70" t="s">
         <v>92</v>
       </c>
-      <c r="K44" s="22"/>
-      <c r="L44" s="22"/>
-      <c r="M44" s="22"/>
+      <c r="K44" s="70"/>
+      <c r="L44" s="70"/>
+      <c r="M44" s="70"/>
       <c r="N44" s="9"/>
       <c r="O44" s="8">
         <v>78</v>
@@ -4485,13 +4576,13 @@
       <c r="R44" s="6"/>
     </row>
     <row r="45" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I45" s="23"/>
-      <c r="J45" s="22" t="s">
+      <c r="I45" s="72"/>
+      <c r="J45" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="K45" s="22"/>
-      <c r="L45" s="22"/>
-      <c r="M45" s="22"/>
+      <c r="K45" s="70"/>
+      <c r="L45" s="70"/>
+      <c r="M45" s="70"/>
       <c r="N45" s="9"/>
       <c r="O45" s="8">
         <v>79</v>
@@ -4505,13 +4596,13 @@
       <c r="R45" s="6"/>
     </row>
     <row r="46" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I46" s="23"/>
-      <c r="J46" s="22" t="s">
+      <c r="I46" s="72"/>
+      <c r="J46" s="70" t="s">
         <v>98</v>
       </c>
-      <c r="K46" s="22"/>
-      <c r="L46" s="22"/>
-      <c r="M46" s="22"/>
+      <c r="K46" s="70"/>
+      <c r="L46" s="70"/>
+      <c r="M46" s="70"/>
       <c r="N46" s="9"/>
       <c r="O46" s="8">
         <v>80</v>
@@ -4525,13 +4616,13 @@
       <c r="R46" s="6"/>
     </row>
     <row r="47" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I47" s="23"/>
-      <c r="J47" s="22" t="s">
+      <c r="I47" s="72"/>
+      <c r="J47" s="70" t="s">
         <v>101</v>
       </c>
-      <c r="K47" s="22"/>
-      <c r="L47" s="22"/>
-      <c r="M47" s="22"/>
+      <c r="K47" s="70"/>
+      <c r="L47" s="70"/>
+      <c r="M47" s="70"/>
       <c r="N47" s="9"/>
       <c r="O47" s="8">
         <v>81</v>
@@ -4545,13 +4636,13 @@
       <c r="R47" s="6"/>
     </row>
     <row r="48" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I48" s="23"/>
-      <c r="J48" s="22" t="s">
+      <c r="I48" s="72"/>
+      <c r="J48" s="70" t="s">
         <v>104</v>
       </c>
-      <c r="K48" s="22"/>
-      <c r="L48" s="22"/>
-      <c r="M48" s="22"/>
+      <c r="K48" s="70"/>
+      <c r="L48" s="70"/>
+      <c r="M48" s="70"/>
       <c r="N48" s="9"/>
       <c r="O48" s="8">
         <v>82</v>
@@ -4565,11 +4656,11 @@
       <c r="R48" s="6"/>
     </row>
     <row r="49" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I49" s="23"/>
-      <c r="J49" s="24"/>
-      <c r="K49" s="24"/>
-      <c r="L49" s="24"/>
-      <c r="M49" s="24"/>
+      <c r="I49" s="72"/>
+      <c r="J49" s="69"/>
+      <c r="K49" s="69"/>
+      <c r="L49" s="69"/>
+      <c r="M49" s="69"/>
       <c r="N49" s="9"/>
       <c r="O49" s="8">
         <v>83</v>
@@ -4583,11 +4674,11 @@
       <c r="R49" s="6"/>
     </row>
     <row r="50" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I50" s="23"/>
-      <c r="J50" s="24"/>
-      <c r="K50" s="24"/>
-      <c r="L50" s="24"/>
-      <c r="M50" s="24"/>
+      <c r="I50" s="72"/>
+      <c r="J50" s="69"/>
+      <c r="K50" s="69"/>
+      <c r="L50" s="69"/>
+      <c r="M50" s="69"/>
       <c r="N50" s="9"/>
       <c r="O50" s="8">
         <v>84</v>
@@ -4601,11 +4692,11 @@
       <c r="R50" s="6"/>
     </row>
     <row r="51" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I51" s="23"/>
-      <c r="J51" s="24"/>
-      <c r="K51" s="24"/>
-      <c r="L51" s="24"/>
-      <c r="M51" s="24"/>
+      <c r="I51" s="72"/>
+      <c r="J51" s="69"/>
+      <c r="K51" s="69"/>
+      <c r="L51" s="69"/>
+      <c r="M51" s="69"/>
       <c r="N51" s="9"/>
       <c r="O51" s="8">
         <v>85</v>
@@ -4619,11 +4710,11 @@
       <c r="R51" s="6"/>
     </row>
     <row r="52" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I52" s="23"/>
-      <c r="J52" s="24"/>
-      <c r="K52" s="24"/>
-      <c r="L52" s="24"/>
-      <c r="M52" s="24"/>
+      <c r="I52" s="72"/>
+      <c r="J52" s="69"/>
+      <c r="K52" s="69"/>
+      <c r="L52" s="69"/>
+      <c r="M52" s="69"/>
       <c r="N52" s="9"/>
       <c r="O52" s="8">
         <v>86</v>
@@ -4638,10 +4729,10 @@
     </row>
     <row r="53" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I53" s="6"/>
-      <c r="J53" s="24"/>
-      <c r="K53" s="24"/>
-      <c r="L53" s="24"/>
-      <c r="M53" s="24"/>
+      <c r="J53" s="69"/>
+      <c r="K53" s="69"/>
+      <c r="L53" s="69"/>
+      <c r="M53" s="69"/>
       <c r="N53" s="7"/>
       <c r="O53" s="8">
         <v>87</v>
@@ -4656,10 +4747,10 @@
     </row>
     <row r="54" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I54" s="6"/>
-      <c r="J54" s="24"/>
-      <c r="K54" s="24"/>
-      <c r="L54" s="24"/>
-      <c r="M54" s="24"/>
+      <c r="J54" s="69"/>
+      <c r="K54" s="69"/>
+      <c r="L54" s="69"/>
+      <c r="M54" s="69"/>
       <c r="N54" s="7"/>
       <c r="O54" s="8">
         <v>88</v>
@@ -4674,10 +4765,10 @@
     </row>
     <row r="55" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I55" s="6"/>
-      <c r="J55" s="24"/>
-      <c r="K55" s="24"/>
-      <c r="L55" s="24"/>
-      <c r="M55" s="24"/>
+      <c r="J55" s="69"/>
+      <c r="K55" s="69"/>
+      <c r="L55" s="69"/>
+      <c r="M55" s="69"/>
       <c r="N55" s="7"/>
       <c r="O55" s="8">
         <v>89</v>
@@ -4692,10 +4783,10 @@
     </row>
     <row r="56" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I56" s="6"/>
-      <c r="J56" s="24"/>
-      <c r="K56" s="24"/>
-      <c r="L56" s="24"/>
-      <c r="M56" s="24"/>
+      <c r="J56" s="69"/>
+      <c r="K56" s="69"/>
+      <c r="L56" s="69"/>
+      <c r="M56" s="69"/>
       <c r="N56" s="7"/>
       <c r="O56" s="8">
         <v>90</v>
@@ -4710,10 +4801,10 @@
     </row>
     <row r="57" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I57" s="6"/>
-      <c r="J57" s="24"/>
-      <c r="K57" s="24"/>
-      <c r="L57" s="24"/>
-      <c r="M57" s="24"/>
+      <c r="J57" s="69"/>
+      <c r="K57" s="69"/>
+      <c r="L57" s="69"/>
+      <c r="M57" s="69"/>
       <c r="N57" s="7"/>
       <c r="O57" s="8">
         <v>91</v>
@@ -4728,10 +4819,10 @@
     </row>
     <row r="58" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I58" s="6"/>
-      <c r="J58" s="24"/>
-      <c r="K58" s="24"/>
-      <c r="L58" s="24"/>
-      <c r="M58" s="24"/>
+      <c r="J58" s="69"/>
+      <c r="K58" s="69"/>
+      <c r="L58" s="69"/>
+      <c r="M58" s="69"/>
       <c r="N58" s="7"/>
       <c r="O58" s="8">
         <v>92</v>
@@ -4746,10 +4837,10 @@
     </row>
     <row r="59" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I59" s="6"/>
-      <c r="J59" s="24"/>
-      <c r="K59" s="24"/>
-      <c r="L59" s="24"/>
-      <c r="M59" s="24"/>
+      <c r="J59" s="69"/>
+      <c r="K59" s="69"/>
+      <c r="L59" s="69"/>
+      <c r="M59" s="69"/>
       <c r="N59" s="7"/>
       <c r="O59" s="8">
         <v>93</v>
@@ -4764,10 +4855,10 @@
     </row>
     <row r="60" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I60" s="6"/>
-      <c r="J60" s="24"/>
-      <c r="K60" s="24"/>
-      <c r="L60" s="24"/>
-      <c r="M60" s="24"/>
+      <c r="J60" s="69"/>
+      <c r="K60" s="69"/>
+      <c r="L60" s="69"/>
+      <c r="M60" s="69"/>
       <c r="N60" s="7"/>
       <c r="O60" s="8">
         <v>94</v>
@@ -4782,10 +4873,10 @@
     </row>
     <row r="61" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I61" s="6"/>
-      <c r="J61" s="24"/>
-      <c r="K61" s="24"/>
-      <c r="L61" s="24"/>
-      <c r="M61" s="24"/>
+      <c r="J61" s="69"/>
+      <c r="K61" s="69"/>
+      <c r="L61" s="69"/>
+      <c r="M61" s="69"/>
       <c r="N61" s="7"/>
       <c r="O61" s="8">
         <v>95</v>
@@ -4800,10 +4891,10 @@
     </row>
     <row r="62" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I62" s="6"/>
-      <c r="J62" s="24"/>
-      <c r="K62" s="24"/>
-      <c r="L62" s="24"/>
-      <c r="M62" s="24"/>
+      <c r="J62" s="69"/>
+      <c r="K62" s="69"/>
+      <c r="L62" s="69"/>
+      <c r="M62" s="69"/>
       <c r="N62" s="7"/>
       <c r="O62" s="8">
         <v>96</v>
@@ -4818,10 +4909,10 @@
     </row>
     <row r="63" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I63" s="6"/>
-      <c r="J63" s="24"/>
-      <c r="K63" s="24"/>
-      <c r="L63" s="24"/>
-      <c r="M63" s="24"/>
+      <c r="J63" s="69"/>
+      <c r="K63" s="69"/>
+      <c r="L63" s="69"/>
+      <c r="M63" s="69"/>
       <c r="N63" s="7"/>
       <c r="O63" s="8">
         <v>97</v>
@@ -4836,10 +4927,10 @@
     </row>
     <row r="64" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I64" s="6"/>
-      <c r="J64" s="24"/>
-      <c r="K64" s="24"/>
-      <c r="L64" s="24"/>
-      <c r="M64" s="24"/>
+      <c r="J64" s="69"/>
+      <c r="K64" s="69"/>
+      <c r="L64" s="69"/>
+      <c r="M64" s="69"/>
       <c r="N64" s="7"/>
       <c r="O64" s="8">
         <v>98</v>
@@ -4854,10 +4945,10 @@
     </row>
     <row r="65" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I65" s="6"/>
-      <c r="J65" s="24"/>
-      <c r="K65" s="24"/>
-      <c r="L65" s="24"/>
-      <c r="M65" s="24"/>
+      <c r="J65" s="69"/>
+      <c r="K65" s="69"/>
+      <c r="L65" s="69"/>
+      <c r="M65" s="69"/>
       <c r="N65" s="7"/>
       <c r="O65" s="8">
         <v>99</v>
@@ -4872,10 +4963,10 @@
     </row>
     <row r="66" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I66" s="6"/>
-      <c r="J66" s="24"/>
-      <c r="K66" s="24"/>
-      <c r="L66" s="24"/>
-      <c r="M66" s="24"/>
+      <c r="J66" s="69"/>
+      <c r="K66" s="69"/>
+      <c r="L66" s="69"/>
+      <c r="M66" s="69"/>
       <c r="N66" s="7"/>
       <c r="O66" s="8">
         <v>100</v>
@@ -4890,10 +4981,10 @@
     </row>
     <row r="67" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I67" s="6"/>
-      <c r="J67" s="24"/>
-      <c r="K67" s="24"/>
-      <c r="L67" s="24"/>
-      <c r="M67" s="24"/>
+      <c r="J67" s="69"/>
+      <c r="K67" s="69"/>
+      <c r="L67" s="69"/>
+      <c r="M67" s="69"/>
       <c r="N67" s="7"/>
       <c r="O67" s="8">
         <v>101</v>
@@ -4908,10 +4999,10 @@
     </row>
     <row r="68" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I68" s="6"/>
-      <c r="J68" s="24"/>
-      <c r="K68" s="24"/>
-      <c r="L68" s="24"/>
-      <c r="M68" s="24"/>
+      <c r="J68" s="69"/>
+      <c r="K68" s="69"/>
+      <c r="L68" s="69"/>
+      <c r="M68" s="69"/>
       <c r="N68" s="7"/>
       <c r="O68" s="8">
         <v>102</v>
@@ -4926,10 +5017,10 @@
     </row>
     <row r="69" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I69" s="6"/>
-      <c r="J69" s="24"/>
-      <c r="K69" s="24"/>
-      <c r="L69" s="24"/>
-      <c r="M69" s="24"/>
+      <c r="J69" s="69"/>
+      <c r="K69" s="69"/>
+      <c r="L69" s="69"/>
+      <c r="M69" s="69"/>
       <c r="N69" s="7"/>
       <c r="O69" s="8">
         <v>103</v>
@@ -4944,10 +5035,10 @@
     </row>
     <row r="70" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I70" s="6"/>
-      <c r="J70" s="24"/>
-      <c r="K70" s="24"/>
-      <c r="L70" s="24"/>
-      <c r="M70" s="24"/>
+      <c r="J70" s="69"/>
+      <c r="K70" s="69"/>
+      <c r="L70" s="69"/>
+      <c r="M70" s="69"/>
       <c r="N70" s="7"/>
       <c r="O70" s="8">
         <v>104</v>
@@ -4962,10 +5053,10 @@
     </row>
     <row r="71" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I71" s="6"/>
-      <c r="J71" s="24"/>
-      <c r="K71" s="24"/>
-      <c r="L71" s="24"/>
-      <c r="M71" s="24"/>
+      <c r="J71" s="69"/>
+      <c r="K71" s="69"/>
+      <c r="L71" s="69"/>
+      <c r="M71" s="69"/>
       <c r="N71" s="7"/>
       <c r="O71" s="8">
         <v>105</v>
@@ -4980,10 +5071,10 @@
     </row>
     <row r="72" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I72" s="6"/>
-      <c r="J72" s="24"/>
-      <c r="K72" s="24"/>
-      <c r="L72" s="24"/>
-      <c r="M72" s="24"/>
+      <c r="J72" s="69"/>
+      <c r="K72" s="69"/>
+      <c r="L72" s="69"/>
+      <c r="M72" s="69"/>
       <c r="N72" s="7"/>
       <c r="O72" s="8">
         <v>106</v>
@@ -4998,10 +5089,10 @@
     </row>
     <row r="73" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I73" s="6"/>
-      <c r="J73" s="24"/>
-      <c r="K73" s="24"/>
-      <c r="L73" s="24"/>
-      <c r="M73" s="24"/>
+      <c r="J73" s="69"/>
+      <c r="K73" s="69"/>
+      <c r="L73" s="69"/>
+      <c r="M73" s="69"/>
       <c r="N73" s="7"/>
       <c r="O73" s="8">
         <v>107</v>
@@ -5016,10 +5107,10 @@
     </row>
     <row r="74" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I74" s="6"/>
-      <c r="J74" s="24"/>
-      <c r="K74" s="24"/>
-      <c r="L74" s="24"/>
-      <c r="M74" s="24"/>
+      <c r="J74" s="69"/>
+      <c r="K74" s="69"/>
+      <c r="L74" s="69"/>
+      <c r="M74" s="69"/>
       <c r="N74" s="7"/>
       <c r="O74" s="8">
         <v>108</v>
@@ -5034,10 +5125,10 @@
     </row>
     <row r="75" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I75" s="6"/>
-      <c r="J75" s="24"/>
-      <c r="K75" s="24"/>
-      <c r="L75" s="24"/>
-      <c r="M75" s="24"/>
+      <c r="J75" s="69"/>
+      <c r="K75" s="69"/>
+      <c r="L75" s="69"/>
+      <c r="M75" s="69"/>
       <c r="N75" s="7"/>
       <c r="O75" s="8">
         <v>109</v>
@@ -5052,10 +5143,10 @@
     </row>
     <row r="76" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I76" s="6"/>
-      <c r="J76" s="24"/>
-      <c r="K76" s="24"/>
-      <c r="L76" s="24"/>
-      <c r="M76" s="24"/>
+      <c r="J76" s="69"/>
+      <c r="K76" s="69"/>
+      <c r="L76" s="69"/>
+      <c r="M76" s="69"/>
       <c r="N76" s="7"/>
       <c r="O76" s="8">
         <v>110</v>
@@ -5070,10 +5161,10 @@
     </row>
     <row r="77" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I77" s="6"/>
-      <c r="J77" s="24"/>
-      <c r="K77" s="24"/>
-      <c r="L77" s="24"/>
-      <c r="M77" s="24"/>
+      <c r="J77" s="69"/>
+      <c r="K77" s="69"/>
+      <c r="L77" s="69"/>
+      <c r="M77" s="69"/>
       <c r="N77" s="7"/>
       <c r="O77" s="8">
         <v>111</v>
@@ -5088,10 +5179,10 @@
     </row>
     <row r="78" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I78" s="6"/>
-      <c r="J78" s="24"/>
-      <c r="K78" s="24"/>
-      <c r="L78" s="24"/>
-      <c r="M78" s="24"/>
+      <c r="J78" s="69"/>
+      <c r="K78" s="69"/>
+      <c r="L78" s="69"/>
+      <c r="M78" s="69"/>
       <c r="N78" s="7"/>
       <c r="O78" s="8">
         <v>112</v>
@@ -5106,10 +5197,10 @@
     </row>
     <row r="79" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I79" s="6"/>
-      <c r="J79" s="24"/>
-      <c r="K79" s="24"/>
-      <c r="L79" s="24"/>
-      <c r="M79" s="24"/>
+      <c r="J79" s="69"/>
+      <c r="K79" s="69"/>
+      <c r="L79" s="69"/>
+      <c r="M79" s="69"/>
       <c r="N79" s="7"/>
       <c r="O79" s="8">
         <v>113</v>
@@ -5124,10 +5215,10 @@
     </row>
     <row r="80" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I80" s="6"/>
-      <c r="J80" s="24"/>
-      <c r="K80" s="24"/>
-      <c r="L80" s="24"/>
-      <c r="M80" s="24"/>
+      <c r="J80" s="69"/>
+      <c r="K80" s="69"/>
+      <c r="L80" s="69"/>
+      <c r="M80" s="69"/>
       <c r="N80" s="7"/>
       <c r="O80" s="8">
         <v>114</v>
@@ -5142,10 +5233,10 @@
     </row>
     <row r="81" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I81" s="6"/>
-      <c r="J81" s="24"/>
-      <c r="K81" s="24"/>
-      <c r="L81" s="24"/>
-      <c r="M81" s="24"/>
+      <c r="J81" s="69"/>
+      <c r="K81" s="69"/>
+      <c r="L81" s="69"/>
+      <c r="M81" s="69"/>
       <c r="N81" s="7"/>
       <c r="O81" s="8">
         <v>115</v>
@@ -5160,10 +5251,10 @@
     </row>
     <row r="82" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I82" s="6"/>
-      <c r="J82" s="24"/>
-      <c r="K82" s="24"/>
-      <c r="L82" s="24"/>
-      <c r="M82" s="24"/>
+      <c r="J82" s="69"/>
+      <c r="K82" s="69"/>
+      <c r="L82" s="69"/>
+      <c r="M82" s="69"/>
       <c r="N82" s="7"/>
       <c r="O82" s="8">
         <v>116</v>
@@ -5178,10 +5269,10 @@
     </row>
     <row r="83" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I83" s="6"/>
-      <c r="J83" s="24"/>
-      <c r="K83" s="24"/>
-      <c r="L83" s="24"/>
-      <c r="M83" s="24"/>
+      <c r="J83" s="69"/>
+      <c r="K83" s="69"/>
+      <c r="L83" s="69"/>
+      <c r="M83" s="69"/>
       <c r="N83" s="7"/>
       <c r="O83" s="8">
         <v>117</v>
@@ -5196,10 +5287,10 @@
     </row>
     <row r="84" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I84" s="6"/>
-      <c r="J84" s="24"/>
-      <c r="K84" s="24"/>
-      <c r="L84" s="24"/>
-      <c r="M84" s="24"/>
+      <c r="J84" s="69"/>
+      <c r="K84" s="69"/>
+      <c r="L84" s="69"/>
+      <c r="M84" s="69"/>
       <c r="N84" s="7"/>
       <c r="O84" s="8">
         <v>118</v>
@@ -5214,10 +5305,10 @@
     </row>
     <row r="85" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I85" s="6"/>
-      <c r="J85" s="24"/>
-      <c r="K85" s="24"/>
-      <c r="L85" s="24"/>
-      <c r="M85" s="24"/>
+      <c r="J85" s="69"/>
+      <c r="K85" s="69"/>
+      <c r="L85" s="69"/>
+      <c r="M85" s="69"/>
       <c r="N85" s="7"/>
       <c r="O85" s="8">
         <v>119</v>
@@ -5232,10 +5323,10 @@
     </row>
     <row r="86" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I86" s="6"/>
-      <c r="J86" s="24"/>
-      <c r="K86" s="24"/>
-      <c r="L86" s="24"/>
-      <c r="M86" s="24"/>
+      <c r="J86" s="69"/>
+      <c r="K86" s="69"/>
+      <c r="L86" s="69"/>
+      <c r="M86" s="69"/>
       <c r="N86" s="7"/>
       <c r="O86" s="8">
         <v>120</v>
@@ -5250,10 +5341,10 @@
     </row>
     <row r="87" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I87" s="6"/>
-      <c r="J87" s="24"/>
-      <c r="K87" s="24"/>
-      <c r="L87" s="24"/>
-      <c r="M87" s="24"/>
+      <c r="J87" s="69"/>
+      <c r="K87" s="69"/>
+      <c r="L87" s="69"/>
+      <c r="M87" s="69"/>
       <c r="N87" s="7"/>
       <c r="O87" s="8">
         <v>121</v>
@@ -5268,10 +5359,10 @@
     </row>
     <row r="88" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I88" s="6"/>
-      <c r="J88" s="24"/>
-      <c r="K88" s="24"/>
-      <c r="L88" s="24"/>
-      <c r="M88" s="24"/>
+      <c r="J88" s="69"/>
+      <c r="K88" s="69"/>
+      <c r="L88" s="69"/>
+      <c r="M88" s="69"/>
       <c r="N88" s="7"/>
       <c r="O88" s="8">
         <v>122</v>
@@ -5286,10 +5377,10 @@
     </row>
     <row r="89" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I89" s="6"/>
-      <c r="J89" s="24"/>
-      <c r="K89" s="24"/>
-      <c r="L89" s="24"/>
-      <c r="M89" s="24"/>
+      <c r="J89" s="69"/>
+      <c r="K89" s="69"/>
+      <c r="L89" s="69"/>
+      <c r="M89" s="69"/>
       <c r="N89" s="7"/>
       <c r="O89" s="8">
         <v>123</v>
@@ -5304,10 +5395,10 @@
     </row>
     <row r="90" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I90" s="6"/>
-      <c r="J90" s="24"/>
-      <c r="K90" s="24"/>
-      <c r="L90" s="24"/>
-      <c r="M90" s="24"/>
+      <c r="J90" s="69"/>
+      <c r="K90" s="69"/>
+      <c r="L90" s="69"/>
+      <c r="M90" s="69"/>
       <c r="N90" s="7"/>
       <c r="O90" s="8">
         <v>124</v>
@@ -5322,10 +5413,10 @@
     </row>
     <row r="91" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I91" s="6"/>
-      <c r="J91" s="24"/>
-      <c r="K91" s="24"/>
-      <c r="L91" s="24"/>
-      <c r="M91" s="24"/>
+      <c r="J91" s="69"/>
+      <c r="K91" s="69"/>
+      <c r="L91" s="69"/>
+      <c r="M91" s="69"/>
       <c r="N91" s="7"/>
       <c r="O91" s="8">
         <v>125</v>
@@ -5340,10 +5431,10 @@
     </row>
     <row r="92" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I92" s="6"/>
-      <c r="J92" s="24"/>
-      <c r="K92" s="24"/>
-      <c r="L92" s="24"/>
-      <c r="M92" s="24"/>
+      <c r="J92" s="69"/>
+      <c r="K92" s="69"/>
+      <c r="L92" s="69"/>
+      <c r="M92" s="69"/>
       <c r="N92" s="7"/>
       <c r="O92" s="8">
         <v>126</v>
@@ -5358,10 +5449,10 @@
     </row>
     <row r="93" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I93" s="6"/>
-      <c r="J93" s="24"/>
-      <c r="K93" s="24"/>
-      <c r="L93" s="24"/>
-      <c r="M93" s="24"/>
+      <c r="J93" s="69"/>
+      <c r="K93" s="69"/>
+      <c r="L93" s="69"/>
+      <c r="M93" s="69"/>
       <c r="N93" s="7"/>
       <c r="O93" s="8">
         <v>127</v>
@@ -7554,47 +7645,31 @@
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="J93:M93"/>
-    <mergeCell ref="J88:M88"/>
-    <mergeCell ref="J89:M89"/>
-    <mergeCell ref="J90:M90"/>
-    <mergeCell ref="J91:M91"/>
-    <mergeCell ref="J92:M92"/>
-    <mergeCell ref="J83:M83"/>
-    <mergeCell ref="J84:M84"/>
-    <mergeCell ref="J85:M85"/>
-    <mergeCell ref="J86:M86"/>
-    <mergeCell ref="J87:M87"/>
-    <mergeCell ref="J78:M78"/>
-    <mergeCell ref="J79:M79"/>
-    <mergeCell ref="J80:M80"/>
-    <mergeCell ref="J81:M81"/>
-    <mergeCell ref="J82:M82"/>
-    <mergeCell ref="J73:M73"/>
-    <mergeCell ref="J74:M74"/>
-    <mergeCell ref="J75:M75"/>
-    <mergeCell ref="J76:M76"/>
-    <mergeCell ref="J77:M77"/>
-    <mergeCell ref="J68:M68"/>
-    <mergeCell ref="J69:M69"/>
-    <mergeCell ref="J70:M70"/>
-    <mergeCell ref="J71:M71"/>
-    <mergeCell ref="J72:M72"/>
-    <mergeCell ref="J63:M63"/>
-    <mergeCell ref="J64:M64"/>
-    <mergeCell ref="J65:M65"/>
-    <mergeCell ref="J66:M66"/>
-    <mergeCell ref="J67:M67"/>
-    <mergeCell ref="J58:M58"/>
-    <mergeCell ref="J59:M59"/>
-    <mergeCell ref="J60:M60"/>
-    <mergeCell ref="J61:M61"/>
-    <mergeCell ref="J62:M62"/>
-    <mergeCell ref="J53:M53"/>
-    <mergeCell ref="J54:M54"/>
-    <mergeCell ref="J55:M55"/>
-    <mergeCell ref="J56:M56"/>
-    <mergeCell ref="J57:M57"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="J39:M39"/>
     <mergeCell ref="J40:M40"/>
     <mergeCell ref="J41:M41"/>
     <mergeCell ref="J42:M42"/>
@@ -7609,31 +7684,47 @@
     <mergeCell ref="J50:M50"/>
     <mergeCell ref="J51:M51"/>
     <mergeCell ref="J52:M52"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="J39:M39"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="J18:M18"/>
-    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="J54:M54"/>
+    <mergeCell ref="J55:M55"/>
+    <mergeCell ref="J56:M56"/>
+    <mergeCell ref="J57:M57"/>
+    <mergeCell ref="J58:M58"/>
+    <mergeCell ref="J59:M59"/>
+    <mergeCell ref="J60:M60"/>
+    <mergeCell ref="J61:M61"/>
+    <mergeCell ref="J62:M62"/>
+    <mergeCell ref="J63:M63"/>
+    <mergeCell ref="J64:M64"/>
+    <mergeCell ref="J65:M65"/>
+    <mergeCell ref="J66:M66"/>
+    <mergeCell ref="J67:M67"/>
+    <mergeCell ref="J68:M68"/>
+    <mergeCell ref="J69:M69"/>
+    <mergeCell ref="J70:M70"/>
+    <mergeCell ref="J71:M71"/>
+    <mergeCell ref="J72:M72"/>
+    <mergeCell ref="J73:M73"/>
+    <mergeCell ref="J74:M74"/>
+    <mergeCell ref="J75:M75"/>
+    <mergeCell ref="J76:M76"/>
+    <mergeCell ref="J77:M77"/>
+    <mergeCell ref="J78:M78"/>
+    <mergeCell ref="J79:M79"/>
+    <mergeCell ref="J80:M80"/>
+    <mergeCell ref="J81:M81"/>
+    <mergeCell ref="J82:M82"/>
+    <mergeCell ref="J83:M83"/>
+    <mergeCell ref="J84:M84"/>
+    <mergeCell ref="J85:M85"/>
+    <mergeCell ref="J86:M86"/>
+    <mergeCell ref="J87:M87"/>
+    <mergeCell ref="J93:M93"/>
+    <mergeCell ref="J88:M88"/>
+    <mergeCell ref="J89:M89"/>
+    <mergeCell ref="J90:M90"/>
+    <mergeCell ref="J91:M91"/>
+    <mergeCell ref="J92:M92"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7647,1212 +7738,1212 @@
   <dimension ref="A1:U28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="36" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" style="27" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7" style="27" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="23.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="27"/>
+    <col min="1" max="1" width="17.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="30" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" style="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7" style="21" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="20" t="s">
+        <v>549</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>550</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>551</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>459</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>552</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>461</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>462</v>
+      </c>
+      <c r="K1" s="20" t="s">
+        <v>463</v>
+      </c>
+      <c r="L1" s="20" t="s">
+        <v>464</v>
+      </c>
+      <c r="M1" s="20" t="s">
+        <v>465</v>
+      </c>
+      <c r="N1" s="20" t="s">
+        <v>466</v>
+      </c>
+      <c r="O1" s="20" t="s">
+        <v>467</v>
+      </c>
+      <c r="P1" s="20" t="s">
+        <v>468</v>
+      </c>
+      <c r="Q1" s="20" t="s">
+        <v>469</v>
+      </c>
+      <c r="R1" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="S1" s="20" t="s">
+        <v>470</v>
+      </c>
+      <c r="T1" s="20" t="s">
+        <v>674</v>
+      </c>
+      <c r="U1" s="20"/>
+    </row>
+    <row r="2" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="42"/>
+      <c r="B2" s="42" t="s">
+        <v>553</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>554</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42" t="s">
+        <v>556</v>
+      </c>
+      <c r="P2" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q2" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R2" s="42" t="s">
+        <v>558</v>
+      </c>
+      <c r="S2" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="42" t="s">
+        <v>513</v>
+      </c>
+      <c r="B3" s="42" t="s">
         <v>559</v>
       </c>
-      <c r="C1" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="28" t="s">
+      <c r="C3" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="43" t="s">
         <v>560</v>
       </c>
-      <c r="E1" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="26" t="s">
+      <c r="E3" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42" t="s">
         <v>561</v>
       </c>
-      <c r="G1" s="26" t="s">
-        <v>469</v>
-      </c>
-      <c r="H1" s="26" t="s">
+      <c r="P3" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q3" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R3" s="42" t="s">
         <v>562</v>
       </c>
-      <c r="I1" s="26" t="s">
-        <v>471</v>
-      </c>
-      <c r="J1" s="26" t="s">
-        <v>472</v>
-      </c>
-      <c r="K1" s="26" t="s">
-        <v>473</v>
-      </c>
-      <c r="L1" s="26" t="s">
-        <v>474</v>
-      </c>
-      <c r="M1" s="26" t="s">
-        <v>475</v>
-      </c>
-      <c r="N1" s="26" t="s">
-        <v>476</v>
-      </c>
-      <c r="O1" s="26" t="s">
-        <v>477</v>
-      </c>
-      <c r="P1" s="26" t="s">
+      <c r="S3" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="42" t="s">
+        <v>563</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>564</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>565</v>
+      </c>
+      <c r="E4" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42" t="s">
+        <v>561</v>
+      </c>
+      <c r="P4" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q4" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R4" s="42" t="s">
+        <v>566</v>
+      </c>
+      <c r="S4" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="42" t="s">
+        <v>567</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>568</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>569</v>
+      </c>
+      <c r="E5" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42" t="s">
+        <v>561</v>
+      </c>
+      <c r="P5" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q5" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R5" s="42" t="s">
+        <v>570</v>
+      </c>
+      <c r="S5" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="42" t="s">
+        <v>571</v>
+      </c>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>572</v>
+      </c>
+      <c r="E6" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42" t="s">
+        <v>573</v>
+      </c>
+      <c r="P6" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q6" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R6" s="45" t="s">
+        <v>574</v>
+      </c>
+      <c r="S6" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="42" t="s">
+        <v>571</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>513</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>575</v>
+      </c>
+      <c r="E7" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42" t="s">
+        <v>576</v>
+      </c>
+      <c r="P7" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q7" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R7" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="S7" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="42" t="s">
+        <v>571</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>513</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>578</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
+      <c r="N8" s="42"/>
+      <c r="O8" s="42" t="s">
+        <v>576</v>
+      </c>
+      <c r="P8" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q8" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R8" s="42" t="s">
+        <v>579</v>
+      </c>
+      <c r="S8" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="42" t="s">
+        <v>571</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>580</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="43" t="s">
+        <v>578</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="42"/>
+      <c r="O9" s="42" t="s">
+        <v>576</v>
+      </c>
+      <c r="P9" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q9" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R9" s="42" t="s">
+        <v>581</v>
+      </c>
+      <c r="S9" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="42" t="s">
+        <v>571</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>582</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>583</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="42"/>
+      <c r="O10" s="42" t="s">
+        <v>576</v>
+      </c>
+      <c r="P10" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q10" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R10" s="42" t="s">
+        <v>584</v>
+      </c>
+      <c r="S10" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="42" t="s">
+        <v>571</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>585</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>586</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="42"/>
+      <c r="O11" s="42" t="s">
+        <v>576</v>
+      </c>
+      <c r="P11" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q11" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R11" s="42" t="s">
+        <v>587</v>
+      </c>
+      <c r="S11" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="42" t="s">
+        <v>588</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>589</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="46"/>
+      <c r="E12" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
+      <c r="O12" s="42" t="s">
+        <v>590</v>
+      </c>
+      <c r="P12" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q12" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R12" s="45" t="s">
+        <v>591</v>
+      </c>
+      <c r="S12" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="42" t="s">
+        <v>588</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>592</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>513</v>
+      </c>
+      <c r="E13" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="42" t="s">
+        <v>593</v>
+      </c>
+      <c r="P13" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q13" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R13" s="42" t="s">
+        <v>594</v>
+      </c>
+      <c r="S13" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="42" t="s">
+        <v>588</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>595</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="43" t="s">
+        <v>596</v>
+      </c>
+      <c r="E14" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="42"/>
+      <c r="O14" s="42" t="s">
+        <v>593</v>
+      </c>
+      <c r="P14" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q14" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R14" s="42" t="s">
+        <v>597</v>
+      </c>
+      <c r="S14" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="42" t="s">
+        <v>588</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>598</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>599</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="42" t="s">
+        <v>593</v>
+      </c>
+      <c r="P15" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q15" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R15" s="42" t="s">
+        <v>600</v>
+      </c>
+      <c r="S15" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" s="42" t="s">
+        <v>588</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>601</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>602</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="42" t="s">
+        <v>593</v>
+      </c>
+      <c r="P16" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q16" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R16" s="42" t="s">
+        <v>603</v>
+      </c>
+      <c r="S16" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="42" t="s">
+        <v>604</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>605</v>
+      </c>
+      <c r="C17" s="42"/>
+      <c r="D17" s="43" t="s">
+        <v>606</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="42"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="42" t="s">
         <v>478</v>
       </c>
-      <c r="Q1" s="26" t="s">
+      <c r="P17" s="42" t="s">
         <v>479</v>
       </c>
-      <c r="R1" s="26" t="s">
-        <v>435</v>
-      </c>
-      <c r="S1" s="26" t="s">
-        <v>480</v>
-      </c>
-      <c r="T1" s="26" t="s">
-        <v>684</v>
-      </c>
-      <c r="U1" s="26"/>
-    </row>
-    <row r="2" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48" t="s">
-        <v>563</v>
-      </c>
-      <c r="C2" s="48" t="s">
+      <c r="Q17" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R17" s="42" t="s">
+        <v>481</v>
+      </c>
+      <c r="S17" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" s="42" t="s">
+        <v>604</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>607</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>513</v>
+      </c>
+      <c r="D18" s="43" t="s">
+        <v>608</v>
+      </c>
+      <c r="E18" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="42" t="s">
+        <v>609</v>
+      </c>
+      <c r="P18" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q18" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R18" s="42" t="s">
+        <v>484</v>
+      </c>
+      <c r="S18" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="42" t="s">
+        <v>604</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>610</v>
+      </c>
+      <c r="C19" s="42" t="s">
+        <v>611</v>
+      </c>
+      <c r="D19" s="43" t="s">
+        <v>612</v>
+      </c>
+      <c r="E19" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="42" t="s">
+        <v>609</v>
+      </c>
+      <c r="P19" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q19" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R19" s="42" t="s">
+        <v>485</v>
+      </c>
+      <c r="S19" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="42" t="s">
+        <v>604</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>613</v>
+      </c>
+      <c r="C20" s="42" t="s">
+        <v>614</v>
+      </c>
+      <c r="D20" s="43" t="s">
+        <v>615</v>
+      </c>
+      <c r="E20" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="42" t="s">
+        <v>616</v>
+      </c>
+      <c r="P20" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q20" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R20" s="42" t="s">
+        <v>486</v>
+      </c>
+      <c r="S20" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A21" s="42" t="s">
+        <v>604</v>
+      </c>
+      <c r="B21" s="42" t="s">
+        <v>617</v>
+      </c>
+      <c r="C21" s="42" t="s">
+        <v>618</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>619</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="42" t="s">
+        <v>609</v>
+      </c>
+      <c r="P21" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q21" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R21" s="42" t="s">
+        <v>487</v>
+      </c>
+      <c r="S21" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="42" t="s">
+        <v>620</v>
+      </c>
+      <c r="B22" s="42" t="s">
+        <v>621</v>
+      </c>
+      <c r="C22" s="42" t="s">
+        <v>622</v>
+      </c>
+      <c r="D22" s="43" t="s">
+        <v>623</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="42"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="42"/>
+      <c r="O22" s="42" t="s">
+        <v>616</v>
+      </c>
+      <c r="P22" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q22" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R22" s="42" t="s">
+        <v>488</v>
+      </c>
+      <c r="S22" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="42" t="s">
+        <v>624</v>
+      </c>
+      <c r="B23" s="42" t="s">
+        <v>625</v>
+      </c>
+      <c r="C23" s="42" t="s">
+        <v>626</v>
+      </c>
+      <c r="D23" s="43" t="s">
+        <v>627</v>
+      </c>
+      <c r="E23" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="42"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="42"/>
+      <c r="O23" s="42" t="s">
+        <v>616</v>
+      </c>
+      <c r="P23" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q23" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R23" s="42" t="s">
+        <v>489</v>
+      </c>
+      <c r="S23" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="42" t="s">
+        <v>628</v>
+      </c>
+      <c r="B24" s="42" t="s">
+        <v>629</v>
+      </c>
+      <c r="C24" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="49" t="s">
-        <v>564</v>
-      </c>
-      <c r="E2" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48" t="s">
-        <v>566</v>
-      </c>
-      <c r="P2" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q2" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R2" s="48" t="s">
-        <v>568</v>
-      </c>
-      <c r="S2" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
-        <v>523</v>
-      </c>
-      <c r="B3" s="48" t="s">
-        <v>569</v>
-      </c>
-      <c r="C3" s="48" t="s">
+      <c r="D24" s="43" t="s">
+        <v>630</v>
+      </c>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="42"/>
+      <c r="M24" s="42"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42" t="s">
+        <v>631</v>
+      </c>
+      <c r="P24" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q24" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R24" s="42" t="s">
+        <v>632</v>
+      </c>
+      <c r="S24" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A25" s="42" t="s">
+        <v>633</v>
+      </c>
+      <c r="B25" s="42" t="s">
+        <v>634</v>
+      </c>
+      <c r="C25" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="49" t="s">
-        <v>570</v>
-      </c>
-      <c r="E3" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="48"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48" t="s">
-        <v>571</v>
-      </c>
-      <c r="P3" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q3" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R3" s="48" t="s">
-        <v>572</v>
-      </c>
-      <c r="S3" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="48" t="s">
-        <v>573</v>
-      </c>
-      <c r="B4" s="48" t="s">
-        <v>574</v>
-      </c>
-      <c r="C4" s="48" t="s">
+      <c r="D25" s="43" t="s">
+        <v>635</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>513</v>
+      </c>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="42"/>
+      <c r="M25" s="42"/>
+      <c r="N25" s="42"/>
+      <c r="O25" s="42" t="s">
+        <v>493</v>
+      </c>
+      <c r="P25" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q25" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R25" s="42" t="s">
+        <v>636</v>
+      </c>
+      <c r="S25" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="42" t="s">
+        <v>637</v>
+      </c>
+      <c r="B26" s="42" t="s">
+        <v>638</v>
+      </c>
+      <c r="C26" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="49" t="s">
-        <v>575</v>
-      </c>
-      <c r="E4" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="48"/>
-      <c r="M4" s="48"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48" t="s">
-        <v>571</v>
-      </c>
-      <c r="P4" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q4" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R4" s="48" t="s">
-        <v>576</v>
-      </c>
-      <c r="S4" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
-        <v>577</v>
-      </c>
-      <c r="B5" s="48" t="s">
-        <v>578</v>
-      </c>
-      <c r="C5" s="48" t="s">
+      <c r="D26" s="43" t="s">
+        <v>639</v>
+      </c>
+      <c r="E26" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="F26" s="42" t="s">
+        <v>640</v>
+      </c>
+      <c r="G26" s="42"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="42"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="42"/>
+      <c r="O26" s="42" t="s">
+        <v>641</v>
+      </c>
+      <c r="P26" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q26" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="R26" s="42" t="s">
+        <v>642</v>
+      </c>
+      <c r="S26" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27" s="47" t="s">
+        <v>637</v>
+      </c>
+      <c r="B27" s="47" t="s">
+        <v>643</v>
+      </c>
+      <c r="C27" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="49" t="s">
-        <v>579</v>
-      </c>
-      <c r="E5" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="48"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48" t="s">
-        <v>571</v>
-      </c>
-      <c r="P5" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q5" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R5" s="48" t="s">
-        <v>580</v>
-      </c>
-      <c r="S5" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="48" t="s">
-        <v>581</v>
-      </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="49" t="s">
-        <v>582</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="48"/>
-      <c r="O6" s="48" t="s">
-        <v>583</v>
-      </c>
-      <c r="P6" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q6" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R6" s="51" t="s">
-        <v>584</v>
-      </c>
-      <c r="S6" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="48" t="s">
-        <v>581</v>
-      </c>
-      <c r="B7" s="48" t="s">
-        <v>523</v>
-      </c>
-      <c r="C7" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>585</v>
-      </c>
-      <c r="E7" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48"/>
-      <c r="N7" s="48"/>
-      <c r="O7" s="48" t="s">
-        <v>586</v>
-      </c>
-      <c r="P7" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q7" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R7" s="48" t="s">
-        <v>587</v>
-      </c>
-      <c r="S7" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="48" t="s">
-        <v>581</v>
-      </c>
-      <c r="B8" s="48" t="s">
-        <v>523</v>
-      </c>
-      <c r="C8" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="49" t="s">
-        <v>588</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="48"/>
-      <c r="N8" s="48"/>
-      <c r="O8" s="48" t="s">
-        <v>586</v>
-      </c>
-      <c r="P8" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q8" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R8" s="48" t="s">
-        <v>589</v>
-      </c>
-      <c r="S8" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="48" t="s">
-        <v>581</v>
-      </c>
-      <c r="B9" s="48" t="s">
-        <v>590</v>
-      </c>
-      <c r="C9" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="49" t="s">
-        <v>588</v>
-      </c>
-      <c r="E9" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
-      <c r="M9" s="48"/>
-      <c r="N9" s="48"/>
-      <c r="O9" s="48" t="s">
-        <v>586</v>
-      </c>
-      <c r="P9" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q9" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R9" s="48" t="s">
-        <v>591</v>
-      </c>
-      <c r="S9" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="48" t="s">
-        <v>581</v>
-      </c>
-      <c r="B10" s="48" t="s">
-        <v>592</v>
-      </c>
-      <c r="C10" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>593</v>
-      </c>
-      <c r="E10" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="48"/>
-      <c r="M10" s="48"/>
-      <c r="N10" s="48"/>
-      <c r="O10" s="48" t="s">
-        <v>586</v>
-      </c>
-      <c r="P10" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q10" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R10" s="48" t="s">
-        <v>594</v>
-      </c>
-      <c r="S10" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
-        <v>581</v>
-      </c>
-      <c r="B11" s="48" t="s">
-        <v>595</v>
-      </c>
-      <c r="C11" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>596</v>
-      </c>
-      <c r="E11" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="48"/>
-      <c r="M11" s="48"/>
-      <c r="N11" s="48"/>
-      <c r="O11" s="48" t="s">
-        <v>586</v>
-      </c>
-      <c r="P11" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q11" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R11" s="48" t="s">
-        <v>597</v>
-      </c>
-      <c r="S11" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="48" t="s">
-        <v>598</v>
-      </c>
-      <c r="B12" s="48" t="s">
-        <v>599</v>
-      </c>
-      <c r="C12" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="52"/>
-      <c r="E12" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="48"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="48"/>
-      <c r="O12" s="48" t="s">
-        <v>600</v>
-      </c>
-      <c r="P12" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q12" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R12" s="51" t="s">
-        <v>601</v>
-      </c>
-      <c r="S12" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="48" t="s">
-        <v>598</v>
-      </c>
-      <c r="B13" s="48" t="s">
-        <v>602</v>
-      </c>
-      <c r="C13" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="49" t="s">
-        <v>523</v>
-      </c>
-      <c r="E13" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="48"/>
-      <c r="K13" s="48"/>
-      <c r="L13" s="48"/>
-      <c r="M13" s="48"/>
-      <c r="N13" s="48"/>
-      <c r="O13" s="48" t="s">
-        <v>603</v>
-      </c>
-      <c r="P13" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q13" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R13" s="48" t="s">
-        <v>604</v>
-      </c>
-      <c r="S13" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="48" t="s">
-        <v>598</v>
-      </c>
-      <c r="B14" s="48" t="s">
-        <v>605</v>
-      </c>
-      <c r="C14" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="49" t="s">
-        <v>606</v>
-      </c>
-      <c r="E14" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="48"/>
-      <c r="M14" s="48"/>
-      <c r="N14" s="48"/>
-      <c r="O14" s="48" t="s">
-        <v>603</v>
-      </c>
-      <c r="P14" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q14" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R14" s="48" t="s">
-        <v>607</v>
-      </c>
-      <c r="S14" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="48" t="s">
-        <v>598</v>
-      </c>
-      <c r="B15" s="48" t="s">
-        <v>608</v>
-      </c>
-      <c r="C15" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="49" t="s">
-        <v>609</v>
-      </c>
-      <c r="E15" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="48"/>
-      <c r="L15" s="48"/>
-      <c r="M15" s="48"/>
-      <c r="N15" s="48"/>
-      <c r="O15" s="48" t="s">
-        <v>603</v>
-      </c>
-      <c r="P15" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q15" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R15" s="48" t="s">
-        <v>610</v>
-      </c>
-      <c r="S15" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="48" t="s">
-        <v>598</v>
-      </c>
-      <c r="B16" s="48" t="s">
-        <v>611</v>
-      </c>
-      <c r="C16" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="49" t="s">
-        <v>612</v>
-      </c>
-      <c r="E16" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="48"/>
-      <c r="K16" s="48"/>
-      <c r="L16" s="48"/>
-      <c r="M16" s="48"/>
-      <c r="N16" s="48"/>
-      <c r="O16" s="48" t="s">
-        <v>603</v>
-      </c>
-      <c r="P16" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q16" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R16" s="48" t="s">
-        <v>613</v>
-      </c>
-      <c r="S16" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="48" t="s">
-        <v>614</v>
-      </c>
-      <c r="B17" s="48" t="s">
-        <v>615</v>
-      </c>
-      <c r="C17" s="48"/>
-      <c r="D17" s="49" t="s">
-        <v>616</v>
-      </c>
-      <c r="E17" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="48"/>
-      <c r="L17" s="48"/>
-      <c r="M17" s="48"/>
-      <c r="N17" s="48"/>
-      <c r="O17" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="P17" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q17" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R17" s="48" t="s">
-        <v>491</v>
-      </c>
-      <c r="S17" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="48" t="s">
-        <v>614</v>
-      </c>
-      <c r="B18" s="48" t="s">
-        <v>617</v>
-      </c>
-      <c r="C18" s="48" t="s">
-        <v>523</v>
-      </c>
-      <c r="D18" s="49" t="s">
-        <v>618</v>
-      </c>
-      <c r="E18" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F18" s="48"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="48"/>
-      <c r="K18" s="48"/>
-      <c r="L18" s="48"/>
-      <c r="M18" s="48"/>
-      <c r="N18" s="48"/>
-      <c r="O18" s="48" t="s">
-        <v>619</v>
-      </c>
-      <c r="P18" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q18" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R18" s="48" t="s">
-        <v>494</v>
-      </c>
-      <c r="S18" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
-        <v>614</v>
-      </c>
-      <c r="B19" s="48" t="s">
-        <v>620</v>
-      </c>
-      <c r="C19" s="48" t="s">
-        <v>621</v>
-      </c>
-      <c r="D19" s="49" t="s">
-        <v>622</v>
-      </c>
-      <c r="E19" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48" t="s">
-        <v>619</v>
-      </c>
-      <c r="P19" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q19" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R19" s="48" t="s">
-        <v>495</v>
-      </c>
-      <c r="S19" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="48" t="s">
-        <v>614</v>
-      </c>
-      <c r="B20" s="48" t="s">
-        <v>623</v>
-      </c>
-      <c r="C20" s="48" t="s">
-        <v>624</v>
-      </c>
-      <c r="D20" s="49" t="s">
-        <v>625</v>
-      </c>
-      <c r="E20" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="48"/>
-      <c r="K20" s="48"/>
-      <c r="L20" s="48"/>
-      <c r="M20" s="48"/>
-      <c r="N20" s="48"/>
-      <c r="O20" s="48" t="s">
-        <v>626</v>
-      </c>
-      <c r="P20" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q20" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R20" s="48" t="s">
-        <v>496</v>
-      </c>
-      <c r="S20" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="48" t="s">
-        <v>614</v>
-      </c>
-      <c r="B21" s="48" t="s">
-        <v>627</v>
-      </c>
-      <c r="C21" s="48" t="s">
-        <v>628</v>
-      </c>
-      <c r="D21" s="49" t="s">
-        <v>629</v>
-      </c>
-      <c r="E21" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F21" s="48"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="48"/>
-      <c r="J21" s="48"/>
-      <c r="K21" s="48"/>
-      <c r="L21" s="48"/>
-      <c r="M21" s="48"/>
-      <c r="N21" s="48"/>
-      <c r="O21" s="48" t="s">
-        <v>619</v>
-      </c>
-      <c r="P21" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q21" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R21" s="48" t="s">
-        <v>497</v>
-      </c>
-      <c r="S21" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
-        <v>630</v>
-      </c>
-      <c r="B22" s="48" t="s">
-        <v>631</v>
-      </c>
-      <c r="C22" s="48" t="s">
-        <v>632</v>
-      </c>
-      <c r="D22" s="49" t="s">
-        <v>633</v>
-      </c>
-      <c r="E22" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="48"/>
-      <c r="K22" s="48"/>
-      <c r="L22" s="48"/>
-      <c r="M22" s="48"/>
-      <c r="N22" s="48"/>
-      <c r="O22" s="48" t="s">
-        <v>626</v>
-      </c>
-      <c r="P22" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q22" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R22" s="48" t="s">
-        <v>498</v>
-      </c>
-      <c r="S22" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="48" t="s">
-        <v>634</v>
-      </c>
-      <c r="B23" s="48" t="s">
-        <v>635</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>636</v>
-      </c>
-      <c r="D23" s="49" t="s">
-        <v>637</v>
-      </c>
-      <c r="E23" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F23" s="48"/>
-      <c r="G23" s="48"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="48"/>
-      <c r="K23" s="48"/>
-      <c r="L23" s="48"/>
-      <c r="M23" s="48"/>
-      <c r="N23" s="48"/>
-      <c r="O23" s="48" t="s">
-        <v>626</v>
-      </c>
-      <c r="P23" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q23" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R23" s="48" t="s">
-        <v>499</v>
-      </c>
-      <c r="S23" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="48" t="s">
-        <v>638</v>
-      </c>
-      <c r="B24" s="48" t="s">
-        <v>639</v>
-      </c>
-      <c r="C24" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="49" t="s">
-        <v>640</v>
-      </c>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="48"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="48"/>
-      <c r="M24" s="48"/>
-      <c r="N24" s="48"/>
-      <c r="O24" s="48" t="s">
-        <v>641</v>
-      </c>
-      <c r="P24" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q24" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R24" s="48" t="s">
-        <v>642</v>
-      </c>
-      <c r="S24" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="48" t="s">
-        <v>643</v>
-      </c>
-      <c r="B25" s="48" t="s">
+      <c r="D27" s="48" t="s">
         <v>644</v>
       </c>
-      <c r="C25" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="49" t="s">
+      <c r="E27" s="47" t="s">
+        <v>555</v>
+      </c>
+      <c r="F27" s="47"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="47"/>
+      <c r="K27" s="47"/>
+      <c r="L27" s="47"/>
+      <c r="M27" s="47"/>
+      <c r="N27" s="47"/>
+      <c r="O27" s="47" t="s">
         <v>645</v>
       </c>
-      <c r="E25" s="48" t="s">
-        <v>523</v>
-      </c>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="48"/>
-      <c r="K25" s="48"/>
-      <c r="L25" s="48"/>
-      <c r="M25" s="48"/>
-      <c r="N25" s="48"/>
-      <c r="O25" s="48" t="s">
-        <v>503</v>
-      </c>
-      <c r="P25" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q25" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R25" s="48" t="s">
+      <c r="P27" s="47" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q27" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="R27" s="47" t="s">
         <v>646</v>
       </c>
-      <c r="S25" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" s="48" t="s">
+      <c r="S27" s="47" t="s">
+        <v>504</v>
+      </c>
+      <c r="T27" s="50" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="47" t="s">
         <v>647</v>
       </c>
-      <c r="B26" s="48" t="s">
+      <c r="B28" s="47" t="s">
         <v>648</v>
       </c>
-      <c r="C26" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="49" t="s">
+      <c r="C28" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="48" t="s">
         <v>649</v>
       </c>
-      <c r="E26" s="48" t="s">
-        <v>565</v>
-      </c>
-      <c r="F26" s="48" t="s">
+      <c r="E28" s="47" t="s">
+        <v>555</v>
+      </c>
+      <c r="F28" s="47" t="s">
         <v>650</v>
       </c>
-      <c r="G26" s="48"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="48"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="48"/>
-      <c r="O26" s="48" t="s">
+      <c r="G28" s="47" t="s">
         <v>651</v>
       </c>
-      <c r="P26" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q26" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="R26" s="48" t="s">
+      <c r="H28" s="47" t="s">
         <v>652</v>
       </c>
-      <c r="S26" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="53" t="s">
-        <v>647</v>
-      </c>
-      <c r="B27" s="53" t="s">
+      <c r="I28" s="47" t="s">
         <v>653</v>
       </c>
-      <c r="C27" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" s="54" t="s">
+      <c r="J28" s="47" t="s">
         <v>654</v>
       </c>
-      <c r="E27" s="53" t="s">
-        <v>565</v>
-      </c>
-      <c r="F27" s="53"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="53"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="53"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="53"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="53" t="s">
+      <c r="K28" s="47" t="s">
         <v>655</v>
       </c>
-      <c r="P27" s="53" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q27" s="55" t="s">
-        <v>567</v>
-      </c>
-      <c r="R27" s="53" t="s">
+      <c r="L28" s="47" t="s">
         <v>656</v>
       </c>
-      <c r="S27" s="53" t="s">
-        <v>514</v>
-      </c>
-      <c r="T27" s="56" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" s="53" t="s">
+      <c r="M28" s="47" t="s">
         <v>657</v>
       </c>
-      <c r="B28" s="53" t="s">
+      <c r="N28" s="47" t="s">
         <v>658</v>
       </c>
-      <c r="C28" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="54" t="s">
+      <c r="O28" s="47" t="s">
+        <v>645</v>
+      </c>
+      <c r="P28" s="47" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q28" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="R28" s="47" t="s">
         <v>659</v>
       </c>
-      <c r="E28" s="53" t="s">
-        <v>565</v>
-      </c>
-      <c r="F28" s="53" t="s">
-        <v>660</v>
-      </c>
-      <c r="G28" s="53" t="s">
-        <v>661</v>
-      </c>
-      <c r="H28" s="53" t="s">
-        <v>662</v>
-      </c>
-      <c r="I28" s="53" t="s">
-        <v>663</v>
-      </c>
-      <c r="J28" s="53" t="s">
-        <v>664</v>
-      </c>
-      <c r="K28" s="53" t="s">
-        <v>665</v>
-      </c>
-      <c r="L28" s="53" t="s">
-        <v>666</v>
-      </c>
-      <c r="M28" s="53" t="s">
-        <v>667</v>
-      </c>
-      <c r="N28" s="53" t="s">
-        <v>668</v>
-      </c>
-      <c r="O28" s="53" t="s">
-        <v>655</v>
-      </c>
-      <c r="P28" s="53" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q28" s="55" t="s">
-        <v>567</v>
-      </c>
-      <c r="R28" s="53" t="s">
-        <v>669</v>
-      </c>
-      <c r="S28" s="53" t="s">
-        <v>514</v>
-      </c>
-      <c r="T28" s="56" t="s">
-        <v>685</v>
+      <c r="S28" s="47" t="s">
+        <v>504</v>
+      </c>
+      <c r="T28" s="50" t="s">
+        <v>675</v>
       </c>
     </row>
   </sheetData>
@@ -8868,7 +8959,7 @@
   <dimension ref="A1:U26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" style="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.140625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.42578125" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="84.5703125" style="11" bestFit="1" customWidth="1"/>
@@ -8890,91 +8981,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>535</v>
+      <c r="A1" s="12" t="s">
+        <v>525</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>478</v>
+        <v>467</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>468</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>435</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
-      <c r="I1" s="15"/>
+      <c r="I1" s="13"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
-      <c r="N1" s="15"/>
+      <c r="N1" s="13"/>
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
       <c r="Q1" s="4"/>
       <c r="R1" s="4"/>
-      <c r="S1" s="15"/>
+      <c r="S1" s="13"/>
       <c r="T1" s="4"/>
       <c r="U1" s="4"/>
     </row>
     <row r="2" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="58" t="s">
-        <v>536</v>
-      </c>
-      <c r="B2" s="59" t="s">
-        <v>536</v>
-      </c>
-      <c r="C2" s="59" t="s">
-        <v>489</v>
-      </c>
-      <c r="D2" s="59" t="s">
-        <v>537</v>
-      </c>
-      <c r="E2" s="59" t="s">
-        <v>538</v>
-      </c>
-      <c r="F2" s="59" t="s">
-        <v>514</v>
+      <c r="A2" s="52" t="s">
+        <v>526</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>526</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>479</v>
+      </c>
+      <c r="D2" s="53" t="s">
+        <v>527</v>
+      </c>
+      <c r="E2" s="53" t="s">
+        <v>528</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>504</v>
       </c>
       <c r="G2" s="4"/>
-      <c r="H2" s="15"/>
+      <c r="H2" s="13"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
-      <c r="M2" s="15"/>
+      <c r="M2" s="13"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
-      <c r="R2" s="15"/>
+      <c r="R2" s="13"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
     <row r="3" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="58"/>
-      <c r="B3" s="59" t="s">
-        <v>539</v>
-      </c>
-      <c r="C3" s="59" t="s">
-        <v>489</v>
-      </c>
-      <c r="D3" s="59" t="s">
-        <v>540</v>
-      </c>
-      <c r="E3" s="59" t="s">
-        <v>541</v>
-      </c>
-      <c r="F3" s="59" t="s">
-        <v>514</v>
+      <c r="A3" s="52"/>
+      <c r="B3" s="53" t="s">
+        <v>529</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>479</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>530</v>
+      </c>
+      <c r="E3" s="53" t="s">
+        <v>531</v>
+      </c>
+      <c r="F3" s="53" t="s">
+        <v>504</v>
       </c>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
@@ -8983,23 +9074,23 @@
       <c r="S3" s="4"/>
     </row>
     <row r="4" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="58" t="s">
-        <v>523</v>
-      </c>
-      <c r="B4" s="59" t="s">
-        <v>539</v>
-      </c>
-      <c r="C4" s="59" t="s">
-        <v>489</v>
-      </c>
-      <c r="D4" s="59" t="s">
-        <v>542</v>
-      </c>
-      <c r="E4" s="59" t="s">
-        <v>543</v>
-      </c>
-      <c r="F4" s="59" t="s">
-        <v>514</v>
+      <c r="A4" s="52" t="s">
+        <v>513</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>529</v>
+      </c>
+      <c r="C4" s="53" t="s">
+        <v>479</v>
+      </c>
+      <c r="D4" s="53" t="s">
+        <v>532</v>
+      </c>
+      <c r="E4" s="53" t="s">
+        <v>533</v>
+      </c>
+      <c r="F4" s="53" t="s">
+        <v>504</v>
       </c>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
@@ -9008,23 +9099,23 @@
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="57" t="s">
-        <v>544</v>
-      </c>
-      <c r="B5" s="40" t="s">
-        <v>545</v>
-      </c>
-      <c r="C5" s="40" t="s">
-        <v>489</v>
-      </c>
-      <c r="D5" s="40" t="s">
-        <v>546</v>
-      </c>
-      <c r="E5" s="40" t="s">
-        <v>547</v>
-      </c>
-      <c r="F5" s="40" t="s">
-        <v>492</v>
+      <c r="A5" s="51" t="s">
+        <v>534</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>535</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>536</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>537</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>482</v>
       </c>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
@@ -9033,23 +9124,23 @@
       <c r="S5" s="4"/>
     </row>
     <row r="6" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="58" t="s">
-        <v>548</v>
-      </c>
-      <c r="B6" s="59" t="s">
-        <v>548</v>
-      </c>
-      <c r="C6" s="59" t="s">
-        <v>489</v>
-      </c>
-      <c r="D6" s="59" t="s">
-        <v>549</v>
-      </c>
-      <c r="E6" s="59" t="s">
-        <v>550</v>
-      </c>
-      <c r="F6" s="59" t="s">
-        <v>514</v>
+      <c r="A6" s="52" t="s">
+        <v>538</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>538</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>479</v>
+      </c>
+      <c r="D6" s="53" t="s">
+        <v>539</v>
+      </c>
+      <c r="E6" s="53" t="s">
+        <v>540</v>
+      </c>
+      <c r="F6" s="53" t="s">
+        <v>504</v>
       </c>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
@@ -9058,23 +9149,23 @@
       <c r="S6" s="4"/>
     </row>
     <row r="7" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="58" t="s">
-        <v>551</v>
-      </c>
-      <c r="B7" s="59" t="s">
-        <v>536</v>
-      </c>
-      <c r="C7" s="59" t="s">
-        <v>489</v>
-      </c>
-      <c r="D7" s="59" t="s">
-        <v>552</v>
-      </c>
-      <c r="E7" s="59" t="s">
-        <v>553</v>
-      </c>
-      <c r="F7" s="59" t="s">
-        <v>514</v>
+      <c r="A7" s="52" t="s">
+        <v>541</v>
+      </c>
+      <c r="B7" s="53" t="s">
+        <v>526</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>479</v>
+      </c>
+      <c r="D7" s="53" t="s">
+        <v>542</v>
+      </c>
+      <c r="E7" s="53" t="s">
+        <v>543</v>
+      </c>
+      <c r="F7" s="53" t="s">
+        <v>504</v>
       </c>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
@@ -9083,23 +9174,23 @@
       <c r="S7" s="4"/>
     </row>
     <row r="8" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="57">
+      <c r="A8" s="51">
         <v>1000000</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="34" t="s">
+        <v>535</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>544</v>
+      </c>
+      <c r="E8" s="34" t="s">
         <v>545</v>
       </c>
-      <c r="C8" s="40" t="s">
-        <v>489</v>
-      </c>
-      <c r="D8" s="40" t="s">
-        <v>554</v>
-      </c>
-      <c r="E8" s="40" t="s">
-        <v>555</v>
-      </c>
-      <c r="F8" s="40" t="s">
-        <v>492</v>
+      <c r="F8" s="34" t="s">
+        <v>482</v>
       </c>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
@@ -9108,23 +9199,23 @@
       <c r="S8" s="4"/>
     </row>
     <row r="9" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="57" t="s">
-        <v>556</v>
-      </c>
-      <c r="B9" s="40" t="s">
-        <v>545</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>489</v>
-      </c>
-      <c r="D9" s="40" t="s">
-        <v>557</v>
-      </c>
-      <c r="E9" s="40" t="s">
-        <v>558</v>
-      </c>
-      <c r="F9" s="40" t="s">
-        <v>492</v>
+      <c r="A9" s="51" t="s">
+        <v>546</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>535</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>547</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>548</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>482</v>
       </c>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
@@ -9140,7 +9231,7 @@
       <c r="S10" s="4"/>
     </row>
     <row r="11" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
+      <c r="A11" s="12"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -9153,7 +9244,7 @@
       <c r="S11" s="4"/>
     </row>
     <row r="12" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
+      <c r="A12" s="12"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="E12" s="4"/>
@@ -9164,7 +9255,7 @@
       <c r="S12" s="4"/>
     </row>
     <row r="13" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
+      <c r="A13" s="12"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -9176,7 +9267,7 @@
       <c r="S13" s="4"/>
     </row>
     <row r="14" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
+      <c r="A14" s="12"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -9188,7 +9279,7 @@
       <c r="S14" s="4"/>
     </row>
     <row r="15" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
+      <c r="A15" s="12"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -9200,7 +9291,7 @@
       <c r="S15" s="4"/>
     </row>
     <row r="16" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
+      <c r="A16" s="12"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -9212,7 +9303,7 @@
       <c r="S16" s="4"/>
     </row>
     <row r="17" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
+      <c r="A17" s="12"/>
       <c r="B17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -9223,7 +9314,7 @@
       <c r="S17" s="4"/>
     </row>
     <row r="18" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
+      <c r="A18" s="12"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -9235,7 +9326,7 @@
       <c r="S18" s="4"/>
     </row>
     <row r="19" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
+      <c r="A19" s="12"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -9247,7 +9338,7 @@
       <c r="S19" s="4"/>
     </row>
     <row r="20" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
+      <c r="A20" s="12"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -9259,7 +9350,7 @@
       <c r="S20" s="4"/>
     </row>
     <row r="21" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
+      <c r="A21" s="12"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -9271,7 +9362,7 @@
       <c r="S21" s="4"/>
     </row>
     <row r="22" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
+      <c r="A22" s="12"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -9283,7 +9374,7 @@
       <c r="S22" s="4"/>
     </row>
     <row r="23" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14"/>
+      <c r="A23" s="12"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -9295,7 +9386,7 @@
       <c r="S23" s="4"/>
     </row>
     <row r="24" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="14"/>
+      <c r="A24" s="12"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -9306,7 +9397,7 @@
       <c r="S24" s="4"/>
     </row>
     <row r="25" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="14"/>
+      <c r="A25" s="12"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -9318,7 +9409,7 @@
       <c r="S25" s="4"/>
     </row>
     <row r="26" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="14"/>
+      <c r="A26" s="12"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -9352,7 +9443,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="44.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
@@ -9368,212 +9459,212 @@
       <c r="A1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>515</v>
+      <c r="B1" s="15" t="s">
+        <v>505</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>435</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="40" t="s">
-        <v>516</v>
-      </c>
-      <c r="D2" s="41" t="s">
-        <v>517</v>
-      </c>
-      <c r="E2" s="40" t="s">
-        <v>489</v>
-      </c>
-      <c r="F2" s="40" t="s">
-        <v>518</v>
-      </c>
-      <c r="G2" s="40" t="s">
-        <v>519</v>
-      </c>
-      <c r="H2" s="40" t="s">
-        <v>492</v>
+      <c r="B2" s="51"/>
+      <c r="C2" s="34" t="s">
+        <v>506</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>507</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="F2" s="34" t="s">
+        <v>508</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>509</v>
+      </c>
+      <c r="H2" s="34" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="57">
+      <c r="B3" s="51">
         <v>123</v>
       </c>
-      <c r="C3" s="40" t="s">
-        <v>520</v>
-      </c>
-      <c r="D3" s="40" t="s">
-        <v>521</v>
-      </c>
-      <c r="E3" s="40" t="s">
-        <v>489</v>
-      </c>
-      <c r="F3" s="40" t="s">
-        <v>518</v>
-      </c>
-      <c r="G3" s="40" t="s">
-        <v>522</v>
-      </c>
-      <c r="H3" s="40" t="s">
-        <v>492</v>
+      <c r="C3" s="34" t="s">
+        <v>510</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>511</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="F3" s="34" t="s">
+        <v>508</v>
+      </c>
+      <c r="G3" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="H3" s="34" t="s">
+        <v>482</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="51" t="s">
+        <v>513</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>514</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>515</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="F4" s="34" t="s">
+        <v>508</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>516</v>
+      </c>
+      <c r="H4" s="34" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>517</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>508</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>518</v>
+      </c>
+      <c r="H5" s="34" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="35" t="s">
+        <v>490</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>508</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>519</v>
+      </c>
+      <c r="H6" s="34" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>520</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>515</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>508</v>
+      </c>
+      <c r="G7" s="34" t="s">
+        <v>521</v>
+      </c>
+      <c r="H7" s="34" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="54" t="s">
+        <v>506</v>
+      </c>
+      <c r="D8" s="54" t="s">
+        <v>522</v>
+      </c>
+      <c r="E8" s="54" t="s">
+        <v>479</v>
+      </c>
+      <c r="F8" s="54" t="s">
         <v>523</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="G8" s="54" t="s">
         <v>524</v>
       </c>
-      <c r="D4" s="40" t="s">
-        <v>525</v>
-      </c>
-      <c r="E4" s="40" t="s">
-        <v>489</v>
-      </c>
-      <c r="F4" s="40" t="s">
-        <v>518</v>
-      </c>
-      <c r="G4" s="40" t="s">
-        <v>526</v>
-      </c>
-      <c r="H4" s="40" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="57" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="41" t="s">
-        <v>527</v>
-      </c>
-      <c r="E5" s="40" t="s">
-        <v>489</v>
-      </c>
-      <c r="F5" s="40" t="s">
-        <v>518</v>
-      </c>
-      <c r="G5" s="40" t="s">
-        <v>528</v>
-      </c>
-      <c r="H5" s="40" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="57" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="41" t="s">
-        <v>500</v>
-      </c>
-      <c r="E6" s="40" t="s">
-        <v>489</v>
-      </c>
-      <c r="F6" s="40" t="s">
-        <v>518</v>
-      </c>
-      <c r="G6" s="40" t="s">
-        <v>529</v>
-      </c>
-      <c r="H6" s="40" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="40" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="57" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>530</v>
-      </c>
-      <c r="D7" s="40" t="s">
-        <v>525</v>
-      </c>
-      <c r="E7" s="40" t="s">
-        <v>489</v>
-      </c>
-      <c r="F7" s="40" t="s">
-        <v>518</v>
-      </c>
-      <c r="G7" s="40" t="s">
-        <v>531</v>
-      </c>
-      <c r="H7" s="40" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="60" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="61" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="60" t="s">
-        <v>516</v>
-      </c>
-      <c r="D8" s="60" t="s">
-        <v>532</v>
-      </c>
-      <c r="E8" s="60" t="s">
-        <v>489</v>
-      </c>
-      <c r="F8" s="60" t="s">
-        <v>533</v>
-      </c>
-      <c r="G8" s="60" t="s">
-        <v>534</v>
-      </c>
-      <c r="H8" s="60" t="s">
-        <v>514</v>
+      <c r="H8" s="54" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
-      <c r="B9" s="17"/>
+      <c r="B9" s="15"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -9587,14 +9678,14 @@
     <row r="13" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:12" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="19"/>
-      <c r="L15" s="16"/>
+      <c r="B15" s="17"/>
+      <c r="L15" s="14"/>
     </row>
     <row r="16" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="2:12" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="19"/>
-      <c r="L18" s="16"/>
+      <c r="B18" s="17"/>
+      <c r="L18" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9609,300 +9700,300 @@
   <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="14.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.5703125" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.85546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="37.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" style="27" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="27"/>
+    <col min="1" max="3" width="14.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="25" t="s">
+        <v>476</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>477</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>467</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>468</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>469</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>435</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="31"/>
+      <c r="D2" s="42" t="s">
+        <v>478</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="F2" s="42" t="s">
+        <v>480</v>
+      </c>
+      <c r="G2" s="42" t="s">
+        <v>481</v>
+      </c>
+      <c r="H2" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="31"/>
+      <c r="D3" s="45" t="s">
+        <v>483</v>
+      </c>
+      <c r="E3" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="F3" s="42" t="s">
+        <v>480</v>
+      </c>
+      <c r="G3" s="42" t="s">
+        <v>484</v>
+      </c>
+      <c r="H3" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="31"/>
+      <c r="D4" s="45" t="s">
+        <v>483</v>
+      </c>
+      <c r="E4" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="F4" s="42" t="s">
+        <v>480</v>
+      </c>
+      <c r="G4" s="42" t="s">
+        <v>485</v>
+      </c>
+      <c r="H4" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="31"/>
+      <c r="D5" s="45" t="s">
+        <v>483</v>
+      </c>
+      <c r="E5" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="F5" s="42" t="s">
+        <v>480</v>
+      </c>
+      <c r="G5" s="42" t="s">
         <v>486</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="H5" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="31"/>
+      <c r="D6" s="45" t="s">
+        <v>483</v>
+      </c>
+      <c r="E6" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="F6" s="42" t="s">
+        <v>480</v>
+      </c>
+      <c r="G6" s="42" t="s">
         <v>487</v>
       </c>
-      <c r="D1" s="31" t="s">
-        <v>477</v>
-      </c>
-      <c r="E1" s="31" t="s">
-        <v>478</v>
-      </c>
-      <c r="F1" s="31" t="s">
+      <c r="H6" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="45" t="s">
+        <v>483</v>
+      </c>
+      <c r="E7" s="42" t="s">
         <v>479</v>
       </c>
-      <c r="G1" s="31" t="s">
-        <v>435</v>
-      </c>
-      <c r="H1" s="31" t="s">
+      <c r="F7" s="42" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="37"/>
-      <c r="D2" s="48" t="s">
+      <c r="G7" s="42" t="s">
         <v>488</v>
       </c>
-      <c r="E2" s="48" t="s">
+      <c r="H7" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D8" s="45" t="s">
+        <v>483</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="F8" s="42" t="s">
+        <v>480</v>
+      </c>
+      <c r="G8" s="42" t="s">
         <v>489</v>
       </c>
-      <c r="F2" s="48" t="s">
+      <c r="H8" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D9" s="45" t="s">
         <v>490</v>
       </c>
-      <c r="G2" s="48" t="s">
+      <c r="E9" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="F9" s="42" t="s">
         <v>491</v>
       </c>
-      <c r="H2" s="48" t="s">
+      <c r="G9" s="42" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="37"/>
-      <c r="D3" s="51" t="s">
+      <c r="H9" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D10" s="45" t="s">
         <v>493</v>
       </c>
-      <c r="E3" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="F3" s="48" t="s">
-        <v>490</v>
-      </c>
-      <c r="G3" s="48" t="s">
+      <c r="E10" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="F10" s="42" t="s">
+        <v>491</v>
+      </c>
+      <c r="G10" s="42" t="s">
         <v>494</v>
       </c>
-      <c r="H3" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="37"/>
-      <c r="D4" s="51" t="s">
+      <c r="H10" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D11" s="45" t="s">
         <v>493</v>
       </c>
-      <c r="E4" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="F4" s="48" t="s">
-        <v>490</v>
-      </c>
-      <c r="G4" s="48" t="s">
+      <c r="E11" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="F11" s="42" t="s">
+        <v>491</v>
+      </c>
+      <c r="G11" s="42" t="s">
         <v>495</v>
       </c>
-      <c r="H4" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="37"/>
-      <c r="D5" s="51" t="s">
-        <v>493</v>
-      </c>
-      <c r="E5" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="F5" s="48" t="s">
-        <v>490</v>
-      </c>
-      <c r="G5" s="48" t="s">
+      <c r="H11" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D12" s="45" t="s">
         <v>496</v>
       </c>
-      <c r="H5" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="37"/>
-      <c r="D6" s="51" t="s">
-        <v>493</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="F6" s="48" t="s">
-        <v>490</v>
-      </c>
-      <c r="G6" s="48" t="s">
+      <c r="E12" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="F12" s="42" t="s">
+        <v>491</v>
+      </c>
+      <c r="G12" s="42" t="s">
         <v>497</v>
       </c>
-      <c r="H6" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D7" s="51" t="s">
-        <v>493</v>
-      </c>
-      <c r="E7" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="F7" s="48" t="s">
-        <v>490</v>
-      </c>
-      <c r="G7" s="48" t="s">
+      <c r="H12" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D13" s="45" t="s">
+        <v>496</v>
+      </c>
+      <c r="E13" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="F13" s="42" t="s">
+        <v>491</v>
+      </c>
+      <c r="G13" s="42" t="s">
         <v>498</v>
       </c>
-      <c r="H7" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D8" s="51" t="s">
-        <v>493</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="F8" s="48" t="s">
-        <v>490</v>
-      </c>
-      <c r="G8" s="48" t="s">
+      <c r="H13" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D14" s="42" t="s">
         <v>499</v>
       </c>
-      <c r="H8" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D9" s="51" t="s">
+      <c r="E14" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="F14" s="42" t="s">
+        <v>491</v>
+      </c>
+      <c r="G14" s="42" t="s">
         <v>500</v>
       </c>
-      <c r="E9" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="F9" s="48" t="s">
+      <c r="H14" s="42" t="s">
+        <v>482</v>
+      </c>
+      <c r="I14" s="25" t="s">
         <v>501</v>
       </c>
-      <c r="G9" s="48" t="s">
+    </row>
+    <row r="15" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D15" s="42" t="s">
+        <v>499</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="F15" s="42" t="s">
+        <v>491</v>
+      </c>
+      <c r="G15" s="42" t="s">
         <v>502</v>
       </c>
-      <c r="H9" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D10" s="51" t="s">
+      <c r="H15" s="42" t="s">
+        <v>482</v>
+      </c>
+      <c r="I15" s="25" t="s">
         <v>503</v>
       </c>
-      <c r="E10" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="F10" s="48" t="s">
-        <v>501</v>
-      </c>
-      <c r="G10" s="48" t="s">
+    </row>
+    <row r="16" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D16" s="56"/>
+      <c r="E16" s="47" t="s">
+        <v>479</v>
+      </c>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="47" t="s">
         <v>504</v>
-      </c>
-      <c r="H10" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="51" t="s">
-        <v>503</v>
-      </c>
-      <c r="E11" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="F11" s="48" t="s">
-        <v>501</v>
-      </c>
-      <c r="G11" s="48" t="s">
-        <v>505</v>
-      </c>
-      <c r="H11" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D12" s="51" t="s">
-        <v>506</v>
-      </c>
-      <c r="E12" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="F12" s="48" t="s">
-        <v>501</v>
-      </c>
-      <c r="G12" s="48" t="s">
-        <v>507</v>
-      </c>
-      <c r="H12" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D13" s="51" t="s">
-        <v>506</v>
-      </c>
-      <c r="E13" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="F13" s="48" t="s">
-        <v>501</v>
-      </c>
-      <c r="G13" s="48" t="s">
-        <v>508</v>
-      </c>
-      <c r="H13" s="48" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D14" s="48" t="s">
-        <v>509</v>
-      </c>
-      <c r="E14" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="F14" s="48" t="s">
-        <v>501</v>
-      </c>
-      <c r="G14" s="48" t="s">
-        <v>510</v>
-      </c>
-      <c r="H14" s="48" t="s">
-        <v>492</v>
-      </c>
-      <c r="I14" s="31" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="48" t="s">
-        <v>509</v>
-      </c>
-      <c r="E15" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="F15" s="48" t="s">
-        <v>501</v>
-      </c>
-      <c r="G15" s="48" t="s">
-        <v>512</v>
-      </c>
-      <c r="H15" s="48" t="s">
-        <v>492</v>
-      </c>
-      <c r="I15" s="31" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D16" s="62"/>
-      <c r="E16" s="53" t="s">
-        <v>489</v>
-      </c>
-      <c r="F16" s="62"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="53" t="s">
-        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -9918,236 +10009,228 @@
   <dimension ref="A1:O1048576"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="10" width="14.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="34.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="36.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="35.85546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9" style="27" bestFit="1" customWidth="1"/>
-    <col min="16" max="23" width="14.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="27"/>
+    <col min="1" max="10" width="14.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="36.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="35.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9" style="21" bestFit="1" customWidth="1"/>
+    <col min="16" max="23" width="14.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>459</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>460</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>461</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>462</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>463</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>464</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>465</v>
+      </c>
+      <c r="J1" s="23" t="s">
+        <v>466</v>
+      </c>
+      <c r="K1" s="23" t="s">
+        <v>467</v>
+      </c>
+      <c r="L1" s="23" t="s">
         <v>468</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="M1" s="23" t="s">
         <v>469</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="N1" s="23" t="s">
+        <v>435</v>
+      </c>
+      <c r="O1" s="23" t="s">
         <v>470</v>
       </c>
-      <c r="E1" s="29" t="s">
+    </row>
+    <row r="2" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="57"/>
+      <c r="B2" s="58" t="s">
+        <v>677</v>
+      </c>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57" t="s">
+        <v>556</v>
+      </c>
+      <c r="L2" s="57" t="s">
+        <v>479</v>
+      </c>
+      <c r="M2" s="57" t="s">
+        <v>688</v>
+      </c>
+      <c r="N2" s="59" t="s">
         <v>471</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="O2" s="57" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="57" t="s">
+        <v>620</v>
+      </c>
+      <c r="B3" s="58"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57" t="s">
+        <v>590</v>
+      </c>
+      <c r="L3" s="57" t="s">
+        <v>479</v>
+      </c>
+      <c r="M3" s="57" t="s">
+        <v>688</v>
+      </c>
+      <c r="N3" s="59" t="s">
         <v>472</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="O3" s="57" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="57" t="s">
+        <v>620</v>
+      </c>
+      <c r="B4" s="58" t="s">
+        <v>679</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57" t="s">
+        <v>593</v>
+      </c>
+      <c r="L4" s="57" t="s">
+        <v>479</v>
+      </c>
+      <c r="M4" s="57" t="s">
+        <v>688</v>
+      </c>
+      <c r="N4" s="59" t="s">
         <v>473</v>
       </c>
-      <c r="H1" s="29" t="s">
+      <c r="O4" s="57" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="60" t="s">
+        <v>620</v>
+      </c>
+      <c r="B5" s="61" t="s">
+        <v>677</v>
+      </c>
+      <c r="C5" s="60" t="s">
+        <v>651</v>
+      </c>
+      <c r="D5" s="60" t="s">
+        <v>681</v>
+      </c>
+      <c r="E5" s="60" t="s">
+        <v>680</v>
+      </c>
+      <c r="F5" s="60" t="s">
+        <v>682</v>
+      </c>
+      <c r="G5" s="61" t="s">
+        <v>683</v>
+      </c>
+      <c r="H5" s="63" t="s">
+        <v>684</v>
+      </c>
+      <c r="I5" s="60" t="s">
+        <v>685</v>
+      </c>
+      <c r="J5" s="61" t="s">
+        <v>686</v>
+      </c>
+      <c r="K5" s="60" t="s">
+        <v>687</v>
+      </c>
+      <c r="L5" s="60" t="s">
+        <v>479</v>
+      </c>
+      <c r="M5" s="60" t="s">
+        <v>688</v>
+      </c>
+      <c r="N5" s="62" t="s">
         <v>474</v>
       </c>
-      <c r="I1" s="29" t="s">
+      <c r="O5" s="60" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="60" t="s">
+        <v>620</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>678</v>
+      </c>
+      <c r="K6" s="60" t="s">
+        <v>687</v>
+      </c>
+      <c r="L6" s="60" t="s">
+        <v>479</v>
+      </c>
+      <c r="M6" s="60" t="s">
+        <v>688</v>
+      </c>
+      <c r="N6" s="62" t="s">
         <v>475</v>
       </c>
-      <c r="J1" s="29" t="s">
-        <v>476</v>
-      </c>
-      <c r="K1" s="29" t="s">
-        <v>477</v>
-      </c>
-      <c r="L1" s="29" t="s">
-        <v>478</v>
-      </c>
-      <c r="M1" s="29" t="s">
-        <v>479</v>
-      </c>
-      <c r="N1" s="29" t="s">
-        <v>435</v>
-      </c>
-      <c r="O1" s="29" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64" t="s">
-        <v>687</v>
-      </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63"/>
-      <c r="K2" s="63" t="s">
-        <v>566</v>
-      </c>
-      <c r="L2" s="63" t="s">
-        <v>489</v>
-      </c>
-      <c r="M2" s="63" t="s">
-        <v>698</v>
-      </c>
-      <c r="N2" s="65" t="s">
-        <v>481</v>
-      </c>
-      <c r="O2" s="63" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
-        <v>630</v>
-      </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63" t="s">
-        <v>600</v>
-      </c>
-      <c r="L3" s="63" t="s">
-        <v>489</v>
-      </c>
-      <c r="M3" s="63" t="s">
-        <v>698</v>
-      </c>
-      <c r="N3" s="65" t="s">
-        <v>482</v>
-      </c>
-      <c r="O3" s="63" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="63" t="s">
-        <v>630</v>
-      </c>
-      <c r="B4" s="64" t="s">
-        <v>689</v>
-      </c>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="63" t="s">
-        <v>603</v>
-      </c>
-      <c r="L4" s="63" t="s">
-        <v>489</v>
-      </c>
-      <c r="M4" s="63" t="s">
-        <v>698</v>
-      </c>
-      <c r="N4" s="65" t="s">
-        <v>483</v>
-      </c>
-      <c r="O4" s="63" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="66" t="s">
-        <v>630</v>
-      </c>
-      <c r="B5" s="67" t="s">
-        <v>687</v>
-      </c>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="66" t="s">
-        <v>697</v>
-      </c>
-      <c r="L5" s="66" t="s">
-        <v>489</v>
-      </c>
-      <c r="M5" s="66" t="s">
-        <v>698</v>
-      </c>
-      <c r="N5" s="68" t="s">
-        <v>484</v>
-      </c>
-      <c r="O5" s="66" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="66" t="s">
-        <v>630</v>
-      </c>
-      <c r="B6" s="67" t="s">
-        <v>688</v>
-      </c>
-      <c r="C6" s="66" t="s">
-        <v>661</v>
-      </c>
-      <c r="D6" s="66" t="s">
-        <v>691</v>
-      </c>
-      <c r="E6" s="66" t="s">
-        <v>690</v>
-      </c>
-      <c r="F6" s="66" t="s">
+      <c r="O6" s="60" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N7" s="20"/>
+    </row>
+    <row r="1048576" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1048576" s="21" t="s">
         <v>692</v>
-      </c>
-      <c r="G6" s="67" t="s">
-        <v>693</v>
-      </c>
-      <c r="H6" s="69" t="s">
-        <v>694</v>
-      </c>
-      <c r="I6" s="66" t="s">
-        <v>695</v>
-      </c>
-      <c r="J6" s="67" t="s">
-        <v>696</v>
-      </c>
-      <c r="K6" s="66" t="s">
-        <v>697</v>
-      </c>
-      <c r="L6" s="66" t="s">
-        <v>489</v>
-      </c>
-      <c r="M6" s="66" t="s">
-        <v>698</v>
-      </c>
-      <c r="N6" s="68" t="s">
-        <v>485</v>
-      </c>
-      <c r="O6" s="66" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N7" s="26"/>
-    </row>
-    <row r="1048576" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1048576" s="27" t="s">
-        <v>702</v>
       </c>
     </row>
   </sheetData>
@@ -10175,217 +10258,217 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>459</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>460</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>461</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>462</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>463</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>464</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>465</v>
+      </c>
+      <c r="J1" s="23" t="s">
+        <v>466</v>
+      </c>
+      <c r="K1" s="23" t="s">
+        <v>467</v>
+      </c>
+      <c r="L1" s="23" t="s">
         <v>468</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="M1" s="23" t="s">
         <v>469</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="N1" s="23" t="s">
+        <v>435</v>
+      </c>
+      <c r="O1" s="23" t="s">
         <v>470</v>
       </c>
-      <c r="E1" s="29" t="s">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="57"/>
+      <c r="B2" s="58" t="s">
+        <v>677</v>
+      </c>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57" t="s">
+        <v>556</v>
+      </c>
+      <c r="L2" s="57" t="s">
+        <v>479</v>
+      </c>
+      <c r="M2" s="57" t="s">
+        <v>688</v>
+      </c>
+      <c r="N2" s="59" t="s">
         <v>471</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="O2" s="57" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="57" t="s">
+        <v>620</v>
+      </c>
+      <c r="B3" s="58"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57" t="s">
+        <v>590</v>
+      </c>
+      <c r="L3" s="57" t="s">
+        <v>479</v>
+      </c>
+      <c r="M3" s="57" t="s">
+        <v>688</v>
+      </c>
+      <c r="N3" s="59" t="s">
         <v>472</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="O3" s="57" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="57" t="s">
+        <v>620</v>
+      </c>
+      <c r="B4" s="58" t="s">
+        <v>679</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57" t="s">
+        <v>593</v>
+      </c>
+      <c r="L4" s="57" t="s">
+        <v>479</v>
+      </c>
+      <c r="M4" s="57" t="s">
+        <v>688</v>
+      </c>
+      <c r="N4" s="59" t="s">
         <v>473</v>
       </c>
-      <c r="H1" s="29" t="s">
+      <c r="O4" s="57" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="60" t="s">
+        <v>620</v>
+      </c>
+      <c r="B5" s="61" t="s">
+        <v>677</v>
+      </c>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="60" t="s">
+        <v>687</v>
+      </c>
+      <c r="L5" s="60" t="s">
+        <v>479</v>
+      </c>
+      <c r="M5" s="60" t="s">
+        <v>688</v>
+      </c>
+      <c r="N5" s="62" t="s">
         <v>474</v>
       </c>
-      <c r="I1" s="29" t="s">
+      <c r="O5" s="60" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="60" t="s">
+        <v>620</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>678</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>651</v>
+      </c>
+      <c r="D6" s="60" t="s">
+        <v>681</v>
+      </c>
+      <c r="E6" s="60" t="s">
+        <v>680</v>
+      </c>
+      <c r="F6" s="60" t="s">
+        <v>682</v>
+      </c>
+      <c r="G6" s="61" t="s">
+        <v>683</v>
+      </c>
+      <c r="H6" s="63" t="s">
+        <v>684</v>
+      </c>
+      <c r="I6" s="60" t="s">
+        <v>685</v>
+      </c>
+      <c r="J6" s="61" t="s">
+        <v>686</v>
+      </c>
+      <c r="K6" s="60" t="s">
+        <v>687</v>
+      </c>
+      <c r="L6" s="60" t="s">
+        <v>479</v>
+      </c>
+      <c r="M6" s="60" t="s">
+        <v>688</v>
+      </c>
+      <c r="N6" s="62" t="s">
         <v>475</v>
       </c>
-      <c r="J1" s="29" t="s">
-        <v>476</v>
-      </c>
-      <c r="K1" s="29" t="s">
-        <v>477</v>
-      </c>
-      <c r="L1" s="29" t="s">
-        <v>478</v>
-      </c>
-      <c r="M1" s="29" t="s">
-        <v>479</v>
-      </c>
-      <c r="N1" s="29" t="s">
-        <v>435</v>
-      </c>
-      <c r="O1" s="29" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64" t="s">
-        <v>687</v>
-      </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63"/>
-      <c r="K2" s="63" t="s">
-        <v>566</v>
-      </c>
-      <c r="L2" s="63" t="s">
-        <v>489</v>
-      </c>
-      <c r="M2" s="63" t="s">
-        <v>698</v>
-      </c>
-      <c r="N2" s="65" t="s">
-        <v>481</v>
-      </c>
-      <c r="O2" s="63" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
-        <v>630</v>
-      </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63" t="s">
-        <v>600</v>
-      </c>
-      <c r="L3" s="63" t="s">
-        <v>489</v>
-      </c>
-      <c r="M3" s="63" t="s">
-        <v>698</v>
-      </c>
-      <c r="N3" s="65" t="s">
-        <v>482</v>
-      </c>
-      <c r="O3" s="63" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="63" t="s">
-        <v>630</v>
-      </c>
-      <c r="B4" s="64" t="s">
-        <v>689</v>
-      </c>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="63" t="s">
-        <v>603</v>
-      </c>
-      <c r="L4" s="63" t="s">
-        <v>489</v>
-      </c>
-      <c r="M4" s="63" t="s">
-        <v>698</v>
-      </c>
-      <c r="N4" s="65" t="s">
-        <v>483</v>
-      </c>
-      <c r="O4" s="63" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="66" t="s">
-        <v>630</v>
-      </c>
-      <c r="B5" s="67" t="s">
-        <v>687</v>
-      </c>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="66" t="s">
-        <v>697</v>
-      </c>
-      <c r="L5" s="66" t="s">
-        <v>489</v>
-      </c>
-      <c r="M5" s="66" t="s">
-        <v>698</v>
-      </c>
-      <c r="N5" s="68" t="s">
-        <v>484</v>
-      </c>
-      <c r="O5" s="66" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="66" t="s">
-        <v>630</v>
-      </c>
-      <c r="B6" s="67" t="s">
-        <v>688</v>
-      </c>
-      <c r="C6" s="66" t="s">
-        <v>661</v>
-      </c>
-      <c r="D6" s="66" t="s">
-        <v>691</v>
-      </c>
-      <c r="E6" s="66" t="s">
-        <v>690</v>
-      </c>
-      <c r="F6" s="66" t="s">
-        <v>692</v>
-      </c>
-      <c r="G6" s="67" t="s">
-        <v>693</v>
-      </c>
-      <c r="H6" s="69" t="s">
-        <v>694</v>
-      </c>
-      <c r="I6" s="66" t="s">
-        <v>695</v>
-      </c>
-      <c r="J6" s="67" t="s">
-        <v>696</v>
-      </c>
-      <c r="K6" s="66" t="s">
-        <v>697</v>
-      </c>
-      <c r="L6" s="66" t="s">
-        <v>489</v>
-      </c>
-      <c r="M6" s="66" t="s">
-        <v>698</v>
-      </c>
-      <c r="N6" s="68" t="s">
-        <v>485</v>
-      </c>
-      <c r="O6" s="66" t="s">
-        <v>514</v>
+      <c r="O6" s="60" t="s">
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -10398,49 +10481,101 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="H1:L3"/>
+  <dimension ref="B1:L4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="14.140625" style="32" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="34.7109375" style="32" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="76.28515625" style="32" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" style="32" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="34.7109375" style="32" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="79.5703125" style="33" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="32"/>
+    <col min="1" max="1" width="14.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.5703125" style="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.7109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="76.28515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.7109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="79.5703125" style="27" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="8:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H1" s="32" t="s">
-        <v>477</v>
-      </c>
-      <c r="I1" s="33" t="s">
+    <row r="1" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="26" t="s">
+        <v>467</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>468</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>469</v>
+      </c>
+      <c r="E1" s="27" t="s">
         <v>435</v>
       </c>
-      <c r="J1" s="32" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="2" spans="8:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H2" s="21" t="s">
-        <v>699</v>
-      </c>
-      <c r="I2" s="34" t="s">
-        <v>466</v>
-      </c>
-      <c r="J2" s="32" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="3" spans="8:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H3" s="32" t="s">
-        <v>700</v>
-      </c>
-      <c r="I3" s="34" t="s">
-        <v>467</v>
-      </c>
-      <c r="J3" s="32" t="s">
-        <v>514</v>
+      <c r="F1" s="26" t="s">
+        <v>470</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="26" t="s">
+        <v>706</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>479</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>714</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>704</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>482</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="19" t="s">
+        <v>689</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>479</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>714</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>707</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>482</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="26" t="s">
+        <v>690</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>479</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>714</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>705</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>504</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>696</v>
       </c>
     </row>
   </sheetData>
@@ -10453,46 +10588,157 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="M1:N49"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="12" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="65.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7" style="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="21" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" style="64" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="13:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M1" s="4" t="s">
+    <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>709</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>698</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>697</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>467</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>468</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>469</v>
+      </c>
+      <c r="G1" s="23" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="2" spans="13:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M2" s="4" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="3" spans="13:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M3" s="4" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="4" spans="13:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M4" s="4" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="5" spans="13:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="13:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="13:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="13:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="13:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="13:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="13:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="13:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="13:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="13:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="13:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="13:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="H1" s="24" t="s">
+        <v>470</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>693</v>
+      </c>
+      <c r="J1" s="64"/>
+    </row>
+    <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
+        <v>710</v>
+      </c>
+      <c r="B2" s="68">
+        <v>1</v>
+      </c>
+      <c r="C2" s="67" t="s">
+        <v>711</v>
+      </c>
+      <c r="D2" s="66" t="s">
+        <v>708</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>479</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>714</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>454</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>694</v>
+      </c>
+      <c r="J2" s="64"/>
+    </row>
+    <row r="3" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="68">
+        <v>1</v>
+      </c>
+      <c r="C3" s="67" t="s">
+        <v>712</v>
+      </c>
+      <c r="D3" s="66" t="s">
+        <v>708</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>479</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>714</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>455</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="24" t="s">
+        <v>695</v>
+      </c>
+      <c r="J3" s="64"/>
+    </row>
+    <row r="4" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>526</v>
+      </c>
+      <c r="B4" s="68">
+        <v>5</v>
+      </c>
+      <c r="C4" s="67" t="s">
+        <v>713</v>
+      </c>
+      <c r="D4" s="66" t="s">
+        <v>708</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>479</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>714</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>456</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>696</v>
+      </c>
+      <c r="J4" s="64"/>
+    </row>
+    <row r="5" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I5" s="20"/>
+      <c r="J5" s="26"/>
+    </row>
+    <row r="6" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -10520,33 +10766,34 @@
     <row r="41" spans="14:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="42" spans="14:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" spans="14:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="14:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="N44" s="13" t="s">
-        <v>462</v>
+    <row r="44" spans="14:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N44" s="65" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="45" spans="14:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N45" s="4"/>
+      <c r="N45" s="20"/>
     </row>
     <row r="46" spans="14:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N46" s="4" t="s">
-        <v>463</v>
+      <c r="N46" s="20" t="s">
+        <v>699</v>
       </c>
     </row>
     <row r="47" spans="14:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N47" s="4" t="s">
-        <v>464</v>
+      <c r="N47" s="20" t="s">
+        <v>700</v>
       </c>
     </row>
     <row r="48" spans="14:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N48" s="4" t="s">
-        <v>465</v>
+      <c r="N48" s="20" t="s">
+        <v>701</v>
       </c>
     </row>
     <row r="49" spans="14:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N49" s="4"/>
+      <c r="N49" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/target/test-classes/data/User_Data.xlsx
+++ b/target/test-classes/data/User_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Zalo\DATN\Automation_AFF\src\test\resources\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22AA3D40-708D-4630-A562-53999C7F585F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8C2E35-2D28-45A3-A84F-E9289273895D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="330" yWindow="-120" windowWidth="28590" windowHeight="16440" tabRatio="920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="730">
   <si>
     <t>Cần để ý :</t>
   </si>
@@ -2253,6 +2253,42 @@
   </si>
   <si>
     <t>Khi code thêm 1 rồi xem có giảm về 0 được không</t>
+  </si>
+  <si>
+    <t>127.0.0.1/4200</t>
+  </si>
+  <si>
+    <t>127.0.0.1/4201</t>
+  </si>
+  <si>
+    <t>127.0.0.1/4202</t>
+  </si>
+  <si>
+    <t>127.0.0.1/4203</t>
+  </si>
+  <si>
+    <t>127.0.0.1/4204</t>
+  </si>
+  <si>
+    <t>127.0.0.1/4205</t>
+  </si>
+  <si>
+    <t>127.0.0.1/4206</t>
+  </si>
+  <si>
+    <t>127.0.0.1/4207</t>
+  </si>
+  <si>
+    <t>127.0.0.1/4208</t>
+  </si>
+  <si>
+    <t>127.0.0.1/4209</t>
+  </si>
+  <si>
+    <t>127.0.0.1/4210</t>
+  </si>
+  <si>
+    <t>127.0.0.1/4211</t>
   </si>
 </sst>
 </file>
@@ -2310,13 +2346,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
@@ -2393,6 +2422,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2421,7 +2456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2523,89 +2558,86 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2617,17 +2649,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2970,25 +3002,25 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="39" t="s">
         <v>661</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="38" t="s">
         <v>479</v>
       </c>
-      <c r="E2" s="41" t="s">
-        <v>557</v>
-      </c>
-      <c r="F2" s="39" t="s">
+      <c r="E2" s="40" t="s">
+        <v>718</v>
+      </c>
+      <c r="F2" s="38" t="s">
         <v>662</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="G2" s="38" t="s">
         <v>504</v>
       </c>
     </row>
@@ -3003,8 +3035,8 @@
       <c r="D3" s="34" t="s">
         <v>479</v>
       </c>
-      <c r="E3" s="36" t="s">
-        <v>557</v>
+      <c r="E3" s="40" t="s">
+        <v>719</v>
       </c>
       <c r="F3" s="34" t="s">
         <v>481</v>
@@ -3026,8 +3058,8 @@
       <c r="D4" s="34" t="s">
         <v>479</v>
       </c>
-      <c r="E4" s="36" t="s">
-        <v>557</v>
+      <c r="E4" s="40" t="s">
+        <v>720</v>
       </c>
       <c r="F4" s="34" t="s">
         <v>484</v>
@@ -3049,8 +3081,8 @@
       <c r="D5" s="34" t="s">
         <v>479</v>
       </c>
-      <c r="E5" s="36" t="s">
-        <v>557</v>
+      <c r="E5" s="40" t="s">
+        <v>721</v>
       </c>
       <c r="F5" s="34" t="s">
         <v>485</v>
@@ -3072,8 +3104,8 @@
       <c r="D6" s="34" t="s">
         <v>479</v>
       </c>
-      <c r="E6" s="36" t="s">
-        <v>557</v>
+      <c r="E6" s="40" t="s">
+        <v>722</v>
       </c>
       <c r="F6" s="34" t="s">
         <v>486</v>
@@ -3095,8 +3127,8 @@
       <c r="D7" s="34" t="s">
         <v>479</v>
       </c>
-      <c r="E7" s="36" t="s">
-        <v>557</v>
+      <c r="E7" s="40" t="s">
+        <v>723</v>
       </c>
       <c r="F7" s="34" t="s">
         <v>487</v>
@@ -3118,8 +3150,8 @@
       <c r="D8" s="34" t="s">
         <v>479</v>
       </c>
-      <c r="E8" s="36" t="s">
-        <v>557</v>
+      <c r="E8" s="40" t="s">
+        <v>724</v>
       </c>
       <c r="F8" s="34" t="s">
         <v>488</v>
@@ -3141,8 +3173,8 @@
       <c r="D9" s="34" t="s">
         <v>479</v>
       </c>
-      <c r="E9" s="36" t="s">
-        <v>557</v>
+      <c r="E9" s="40" t="s">
+        <v>725</v>
       </c>
       <c r="F9" s="34" t="s">
         <v>489</v>
@@ -3164,8 +3196,8 @@
       <c r="D10" s="34" t="s">
         <v>479</v>
       </c>
-      <c r="E10" s="36" t="s">
-        <v>557</v>
+      <c r="E10" s="40" t="s">
+        <v>726</v>
       </c>
       <c r="F10" s="34" t="s">
         <v>670</v>
@@ -3178,15 +3210,15 @@
       <c r="A11" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="37"/>
+      <c r="B11" s="36"/>
       <c r="C11" s="35" t="s">
         <v>631</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>479</v>
       </c>
-      <c r="E11" s="36" t="s">
-        <v>557</v>
+      <c r="E11" s="40" t="s">
+        <v>727</v>
       </c>
       <c r="F11" s="34" t="s">
         <v>632</v>
@@ -3208,8 +3240,8 @@
       <c r="D12" s="34" t="s">
         <v>479</v>
       </c>
-      <c r="E12" s="36" t="s">
-        <v>557</v>
+      <c r="E12" s="40" t="s">
+        <v>728</v>
       </c>
       <c r="F12" s="34" t="s">
         <v>636</v>
@@ -3231,8 +3263,8 @@
       <c r="D13" s="34" t="s">
         <v>479</v>
       </c>
-      <c r="E13" s="36" t="s">
-        <v>557</v>
+      <c r="E13" s="40" t="s">
+        <v>729</v>
       </c>
       <c r="F13" s="34" t="s">
         <v>673</v>
@@ -3242,15 +3274,16 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="38"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
+      <c r="A14" s="37"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3287,7 +3320,7 @@
       <c r="E1" s="20" t="s">
         <v>435</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="F1" s="63" t="s">
         <v>470</v>
       </c>
       <c r="G1" s="21" t="s">
@@ -3310,7 +3343,7 @@
       <c r="E2" s="20" t="s">
         <v>702</v>
       </c>
-      <c r="F2" s="64" t="s">
+      <c r="F2" s="63" t="s">
         <v>6</v>
       </c>
       <c r="G2" s="21" t="s">
@@ -3336,7 +3369,7 @@
       <c r="E3" s="20" t="s">
         <v>703</v>
       </c>
-      <c r="F3" s="64" t="s">
+      <c r="F3" s="63" t="s">
         <v>6</v>
       </c>
       <c r="G3" s="21" t="s">
@@ -3362,7 +3395,7 @@
       <c r="E4" s="20" t="s">
         <v>453</v>
       </c>
-      <c r="F4" s="64" t="s">
+      <c r="F4" s="63" t="s">
         <v>482</v>
       </c>
       <c r="G4" s="21" t="s">
@@ -3388,7 +3421,7 @@
     <col min="1" max="4" width="9.140625" style="21" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="21" bestFit="1" customWidth="1"/>
     <col min="6" max="10" width="9.140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="38" style="64" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="38" style="63" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="40.85546875" style="21" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="21"/>
   </cols>
@@ -3409,20 +3442,20 @@
       <c r="E1" s="20" t="s">
         <v>435</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="F1" s="63" t="s">
         <v>470</v>
       </c>
       <c r="G1" s="21" t="s">
         <v>693</v>
       </c>
       <c r="K1" s="20"/>
-      <c r="L1" s="64"/>
+      <c r="L1" s="63"/>
     </row>
     <row r="2" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E2" s="20" t="s">
         <v>451</v>
       </c>
-      <c r="F2" s="64" t="s">
+      <c r="F2" s="63" t="s">
         <v>6</v>
       </c>
       <c r="G2" s="21" t="s">
@@ -3433,7 +3466,7 @@
       <c r="E3" s="20" t="s">
         <v>452</v>
       </c>
-      <c r="F3" s="64" t="s">
+      <c r="F3" s="63" t="s">
         <v>6</v>
       </c>
       <c r="G3" s="21" t="s">
@@ -3442,7 +3475,7 @@
     </row>
     <row r="4" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E4" s="20"/>
-      <c r="F4" s="64"/>
+      <c r="F4" s="63"/>
     </row>
     <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3462,7 +3495,7 @@
     <row r="18" spans="11:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="11:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="20" spans="11:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K20" s="65"/>
+      <c r="K20" s="64"/>
     </row>
     <row r="21" spans="11:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="11:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3949,12 +3982,12 @@
         <v>8</v>
       </c>
       <c r="I15" s="6"/>
-      <c r="J15" s="70" t="s">
+      <c r="J15" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="K15" s="70"/>
-      <c r="L15" s="70"/>
-      <c r="M15" s="70"/>
+      <c r="K15" s="68"/>
+      <c r="L15" s="68"/>
+      <c r="M15" s="68"/>
       <c r="N15" s="7"/>
       <c r="O15" s="8">
         <v>1</v>
@@ -3980,12 +4013,12 @@
         <v>14</v>
       </c>
       <c r="I16" s="6"/>
-      <c r="J16" s="70" t="s">
+      <c r="J16" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="K16" s="70"/>
-      <c r="L16" s="70"/>
-      <c r="M16" s="70"/>
+      <c r="K16" s="68"/>
+      <c r="L16" s="68"/>
+      <c r="M16" s="68"/>
       <c r="N16" s="7"/>
       <c r="O16" s="8">
         <v>50</v>
@@ -4006,12 +4039,12 @@
         <v>19</v>
       </c>
       <c r="I17" s="6"/>
-      <c r="J17" s="70" t="s">
+      <c r="J17" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="K17" s="70"/>
-      <c r="L17" s="70"/>
-      <c r="M17" s="70"/>
+      <c r="K17" s="68"/>
+      <c r="L17" s="68"/>
+      <c r="M17" s="68"/>
       <c r="N17" s="7"/>
       <c r="O17" s="8">
         <v>51</v>
@@ -4035,12 +4068,12 @@
         <v>25</v>
       </c>
       <c r="I18" s="6"/>
-      <c r="J18" s="70" t="s">
+      <c r="J18" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="K18" s="70"/>
-      <c r="L18" s="70"/>
-      <c r="M18" s="70"/>
+      <c r="K18" s="68"/>
+      <c r="L18" s="68"/>
+      <c r="M18" s="68"/>
       <c r="N18" s="7"/>
       <c r="O18" s="8">
         <v>52</v>
@@ -4058,12 +4091,12 @@
         <v>29</v>
       </c>
       <c r="I19" s="6"/>
-      <c r="J19" s="70" t="s">
+      <c r="J19" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="K19" s="70"/>
-      <c r="L19" s="70"/>
-      <c r="M19" s="70"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="68"/>
+      <c r="M19" s="68"/>
       <c r="N19" s="7"/>
       <c r="O19" s="8">
         <v>53</v>
@@ -4112,12 +4145,12 @@
       <c r="R21" s="6"/>
     </row>
     <row r="22" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="72" t="s">
+      <c r="B22" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
       <c r="I22" s="6"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -4136,12 +4169,12 @@
       <c r="R22" s="6"/>
     </row>
     <row r="23" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="72" t="s">
+      <c r="B23" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="72"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
+      <c r="C23" s="69"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="69"/>
       <c r="F23" s="4" t="s">
         <v>42</v>
       </c>
@@ -4159,12 +4192,12 @@
       <c r="R23" s="6"/>
     </row>
     <row r="24" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="72" t="s">
+      <c r="B24" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
+      <c r="C24" s="69"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
       <c r="I24" s="6"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -4183,12 +4216,12 @@
       <c r="R24" s="6"/>
     </row>
     <row r="25" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="72" t="s">
+      <c r="B25" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="72"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="72"/>
+      <c r="C25" s="69"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
       <c r="I25" s="6"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -4207,12 +4240,12 @@
       <c r="R25" s="6"/>
     </row>
     <row r="26" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="72" t="s">
+      <c r="B26" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="72"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="72"/>
+      <c r="C26" s="69"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
       <c r="I26" s="6"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -4231,17 +4264,17 @@
       <c r="R26" s="6"/>
     </row>
     <row r="27" spans="2:18" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="72" t="s">
+      <c r="B27" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="72"/>
-      <c r="D27" s="72"/>
-      <c r="E27" s="72"/>
+      <c r="C27" s="69"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="69"/>
       <c r="I27" s="6"/>
-      <c r="J27" s="69"/>
-      <c r="K27" s="69"/>
-      <c r="L27" s="69"/>
-      <c r="M27" s="69"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="70"/>
+      <c r="M27" s="70"/>
       <c r="N27" s="7"/>
       <c r="O27" s="8">
         <v>61</v>
@@ -4255,17 +4288,17 @@
       <c r="R27" s="6"/>
     </row>
     <row r="28" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="72" t="s">
+      <c r="B28" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
+      <c r="C28" s="69"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
       <c r="I28" s="6"/>
-      <c r="J28" s="70"/>
-      <c r="K28" s="70"/>
-      <c r="L28" s="70"/>
-      <c r="M28" s="70"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="68"/>
+      <c r="L28" s="68"/>
+      <c r="M28" s="68"/>
       <c r="N28" s="9"/>
       <c r="O28" s="8">
         <v>62</v>
@@ -4280,10 +4313,10 @@
     </row>
     <row r="29" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I29" s="6"/>
-      <c r="J29" s="70"/>
-      <c r="K29" s="70"/>
-      <c r="L29" s="70"/>
-      <c r="M29" s="70"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="68"/>
+      <c r="L29" s="68"/>
+      <c r="M29" s="68"/>
       <c r="N29" s="9"/>
       <c r="O29" s="8">
         <v>63</v>
@@ -4298,10 +4331,10 @@
     </row>
     <row r="30" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I30" s="6"/>
-      <c r="J30" s="70"/>
-      <c r="K30" s="70"/>
-      <c r="L30" s="70"/>
-      <c r="M30" s="70"/>
+      <c r="J30" s="68"/>
+      <c r="K30" s="68"/>
+      <c r="L30" s="68"/>
+      <c r="M30" s="68"/>
       <c r="N30" s="9"/>
       <c r="O30" s="8">
         <v>64</v>
@@ -4316,10 +4349,10 @@
     </row>
     <row r="31" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I31" s="6"/>
-      <c r="J31" s="70"/>
-      <c r="K31" s="70"/>
-      <c r="L31" s="70"/>
-      <c r="M31" s="70"/>
+      <c r="J31" s="68"/>
+      <c r="K31" s="68"/>
+      <c r="L31" s="68"/>
+      <c r="M31" s="68"/>
       <c r="N31" s="9"/>
       <c r="O31" s="8">
         <v>65</v>
@@ -4334,10 +4367,10 @@
     </row>
     <row r="32" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I32" s="6"/>
-      <c r="J32" s="70"/>
-      <c r="K32" s="70"/>
-      <c r="L32" s="70"/>
-      <c r="M32" s="70"/>
+      <c r="J32" s="68"/>
+      <c r="K32" s="68"/>
+      <c r="L32" s="68"/>
+      <c r="M32" s="68"/>
       <c r="N32" s="9"/>
       <c r="O32" s="8">
         <v>66</v>
@@ -4352,10 +4385,10 @@
     </row>
     <row r="33" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I33" s="6"/>
-      <c r="J33" s="70"/>
-      <c r="K33" s="70"/>
-      <c r="L33" s="70"/>
-      <c r="M33" s="70"/>
+      <c r="J33" s="68"/>
+      <c r="K33" s="68"/>
+      <c r="L33" s="68"/>
+      <c r="M33" s="68"/>
       <c r="N33" s="9"/>
       <c r="O33" s="8">
         <v>67</v>
@@ -4370,10 +4403,10 @@
     </row>
     <row r="34" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I34" s="6"/>
-      <c r="J34" s="70"/>
-      <c r="K34" s="70"/>
-      <c r="L34" s="70"/>
-      <c r="M34" s="70"/>
+      <c r="J34" s="68"/>
+      <c r="K34" s="68"/>
+      <c r="L34" s="68"/>
+      <c r="M34" s="68"/>
       <c r="N34" s="9"/>
       <c r="O34" s="8">
         <v>68</v>
@@ -4388,10 +4421,10 @@
     </row>
     <row r="35" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I35" s="6"/>
-      <c r="J35" s="70"/>
-      <c r="K35" s="70"/>
-      <c r="L35" s="70"/>
-      <c r="M35" s="70"/>
+      <c r="J35" s="68"/>
+      <c r="K35" s="68"/>
+      <c r="L35" s="68"/>
+      <c r="M35" s="68"/>
       <c r="N35" s="9"/>
       <c r="O35" s="8">
         <v>69</v>
@@ -4406,10 +4439,10 @@
     </row>
     <row r="36" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I36" s="6"/>
-      <c r="J36" s="70"/>
-      <c r="K36" s="70"/>
-      <c r="L36" s="70"/>
-      <c r="M36" s="70"/>
+      <c r="J36" s="68"/>
+      <c r="K36" s="68"/>
+      <c r="L36" s="68"/>
+      <c r="M36" s="68"/>
       <c r="N36" s="9"/>
       <c r="O36" s="8">
         <v>70</v>
@@ -4427,10 +4460,10 @@
         <v>76</v>
       </c>
       <c r="I37" s="6"/>
-      <c r="J37" s="70"/>
-      <c r="K37" s="70"/>
-      <c r="L37" s="70"/>
-      <c r="M37" s="70"/>
+      <c r="J37" s="68"/>
+      <c r="K37" s="68"/>
+      <c r="L37" s="68"/>
+      <c r="M37" s="68"/>
       <c r="N37" s="9"/>
       <c r="O37" s="8">
         <v>71</v>
@@ -4445,10 +4478,10 @@
     </row>
     <row r="38" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I38" s="6"/>
-      <c r="J38" s="69"/>
-      <c r="K38" s="69"/>
-      <c r="L38" s="69"/>
-      <c r="M38" s="69"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
+      <c r="M38" s="70"/>
       <c r="N38" s="9"/>
       <c r="O38" s="8">
         <v>72</v>
@@ -4463,10 +4496,10 @@
     </row>
     <row r="39" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I39" s="6"/>
-      <c r="J39" s="69"/>
-      <c r="K39" s="69"/>
-      <c r="L39" s="69"/>
-      <c r="M39" s="69"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="70"/>
+      <c r="M39" s="70"/>
       <c r="N39" s="9"/>
       <c r="O39" s="8">
         <v>73</v>
@@ -4481,10 +4514,10 @@
     </row>
     <row r="40" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I40" s="6"/>
-      <c r="J40" s="69"/>
-      <c r="K40" s="69"/>
-      <c r="L40" s="69"/>
-      <c r="M40" s="69"/>
+      <c r="J40" s="70"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="70"/>
+      <c r="M40" s="70"/>
       <c r="N40" s="7"/>
       <c r="O40" s="8">
         <v>74</v>
@@ -4499,10 +4532,10 @@
     </row>
     <row r="41" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I41" s="6"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="69"/>
-      <c r="L41" s="69"/>
-      <c r="M41" s="69"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="70"/>
+      <c r="M41" s="70"/>
       <c r="N41" s="7"/>
       <c r="O41" s="8">
         <v>75</v>
@@ -4517,12 +4550,12 @@
     </row>
     <row r="42" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I42" s="6"/>
-      <c r="J42" s="70" t="s">
+      <c r="J42" s="68" t="s">
         <v>86</v>
       </c>
-      <c r="K42" s="70"/>
-      <c r="L42" s="70"/>
-      <c r="M42" s="70"/>
+      <c r="K42" s="68"/>
+      <c r="L42" s="68"/>
+      <c r="M42" s="68"/>
       <c r="N42" s="9"/>
       <c r="O42" s="8">
         <v>76</v>
@@ -4537,12 +4570,12 @@
     </row>
     <row r="43" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I43" s="71"/>
-      <c r="J43" s="70" t="s">
+      <c r="J43" s="68" t="s">
         <v>89</v>
       </c>
-      <c r="K43" s="70"/>
-      <c r="L43" s="70"/>
-      <c r="M43" s="70"/>
+      <c r="K43" s="68"/>
+      <c r="L43" s="68"/>
+      <c r="M43" s="68"/>
       <c r="N43" s="9"/>
       <c r="O43" s="8">
         <v>77</v>
@@ -4556,13 +4589,13 @@
       <c r="R43" s="6"/>
     </row>
     <row r="44" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I44" s="72"/>
-      <c r="J44" s="70" t="s">
+      <c r="I44" s="69"/>
+      <c r="J44" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="K44" s="70"/>
-      <c r="L44" s="70"/>
-      <c r="M44" s="70"/>
+      <c r="K44" s="68"/>
+      <c r="L44" s="68"/>
+      <c r="M44" s="68"/>
       <c r="N44" s="9"/>
       <c r="O44" s="8">
         <v>78</v>
@@ -4576,13 +4609,13 @@
       <c r="R44" s="6"/>
     </row>
     <row r="45" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I45" s="72"/>
-      <c r="J45" s="70" t="s">
+      <c r="I45" s="69"/>
+      <c r="J45" s="68" t="s">
         <v>95</v>
       </c>
-      <c r="K45" s="70"/>
-      <c r="L45" s="70"/>
-      <c r="M45" s="70"/>
+      <c r="K45" s="68"/>
+      <c r="L45" s="68"/>
+      <c r="M45" s="68"/>
       <c r="N45" s="9"/>
       <c r="O45" s="8">
         <v>79</v>
@@ -4596,13 +4629,13 @@
       <c r="R45" s="6"/>
     </row>
     <row r="46" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I46" s="72"/>
-      <c r="J46" s="70" t="s">
+      <c r="I46" s="69"/>
+      <c r="J46" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="K46" s="70"/>
-      <c r="L46" s="70"/>
-      <c r="M46" s="70"/>
+      <c r="K46" s="68"/>
+      <c r="L46" s="68"/>
+      <c r="M46" s="68"/>
       <c r="N46" s="9"/>
       <c r="O46" s="8">
         <v>80</v>
@@ -4616,13 +4649,13 @@
       <c r="R46" s="6"/>
     </row>
     <row r="47" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I47" s="72"/>
-      <c r="J47" s="70" t="s">
+      <c r="I47" s="69"/>
+      <c r="J47" s="68" t="s">
         <v>101</v>
       </c>
-      <c r="K47" s="70"/>
-      <c r="L47" s="70"/>
-      <c r="M47" s="70"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="68"/>
+      <c r="M47" s="68"/>
       <c r="N47" s="9"/>
       <c r="O47" s="8">
         <v>81</v>
@@ -4636,13 +4669,13 @@
       <c r="R47" s="6"/>
     </row>
     <row r="48" spans="2:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I48" s="72"/>
-      <c r="J48" s="70" t="s">
+      <c r="I48" s="69"/>
+      <c r="J48" s="68" t="s">
         <v>104</v>
       </c>
-      <c r="K48" s="70"/>
-      <c r="L48" s="70"/>
-      <c r="M48" s="70"/>
+      <c r="K48" s="68"/>
+      <c r="L48" s="68"/>
+      <c r="M48" s="68"/>
       <c r="N48" s="9"/>
       <c r="O48" s="8">
         <v>82</v>
@@ -4656,11 +4689,11 @@
       <c r="R48" s="6"/>
     </row>
     <row r="49" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I49" s="72"/>
-      <c r="J49" s="69"/>
-      <c r="K49" s="69"/>
-      <c r="L49" s="69"/>
-      <c r="M49" s="69"/>
+      <c r="I49" s="69"/>
+      <c r="J49" s="70"/>
+      <c r="K49" s="70"/>
+      <c r="L49" s="70"/>
+      <c r="M49" s="70"/>
       <c r="N49" s="9"/>
       <c r="O49" s="8">
         <v>83</v>
@@ -4674,11 +4707,11 @@
       <c r="R49" s="6"/>
     </row>
     <row r="50" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I50" s="72"/>
-      <c r="J50" s="69"/>
-      <c r="K50" s="69"/>
-      <c r="L50" s="69"/>
-      <c r="M50" s="69"/>
+      <c r="I50" s="69"/>
+      <c r="J50" s="70"/>
+      <c r="K50" s="70"/>
+      <c r="L50" s="70"/>
+      <c r="M50" s="70"/>
       <c r="N50" s="9"/>
       <c r="O50" s="8">
         <v>84</v>
@@ -4692,11 +4725,11 @@
       <c r="R50" s="6"/>
     </row>
     <row r="51" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I51" s="72"/>
-      <c r="J51" s="69"/>
-      <c r="K51" s="69"/>
-      <c r="L51" s="69"/>
-      <c r="M51" s="69"/>
+      <c r="I51" s="69"/>
+      <c r="J51" s="70"/>
+      <c r="K51" s="70"/>
+      <c r="L51" s="70"/>
+      <c r="M51" s="70"/>
       <c r="N51" s="9"/>
       <c r="O51" s="8">
         <v>85</v>
@@ -4710,11 +4743,11 @@
       <c r="R51" s="6"/>
     </row>
     <row r="52" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I52" s="72"/>
-      <c r="J52" s="69"/>
-      <c r="K52" s="69"/>
-      <c r="L52" s="69"/>
-      <c r="M52" s="69"/>
+      <c r="I52" s="69"/>
+      <c r="J52" s="70"/>
+      <c r="K52" s="70"/>
+      <c r="L52" s="70"/>
+      <c r="M52" s="70"/>
       <c r="N52" s="9"/>
       <c r="O52" s="8">
         <v>86</v>
@@ -4729,10 +4762,10 @@
     </row>
     <row r="53" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I53" s="6"/>
-      <c r="J53" s="69"/>
-      <c r="K53" s="69"/>
-      <c r="L53" s="69"/>
-      <c r="M53" s="69"/>
+      <c r="J53" s="70"/>
+      <c r="K53" s="70"/>
+      <c r="L53" s="70"/>
+      <c r="M53" s="70"/>
       <c r="N53" s="7"/>
       <c r="O53" s="8">
         <v>87</v>
@@ -4747,10 +4780,10 @@
     </row>
     <row r="54" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I54" s="6"/>
-      <c r="J54" s="69"/>
-      <c r="K54" s="69"/>
-      <c r="L54" s="69"/>
-      <c r="M54" s="69"/>
+      <c r="J54" s="70"/>
+      <c r="K54" s="70"/>
+      <c r="L54" s="70"/>
+      <c r="M54" s="70"/>
       <c r="N54" s="7"/>
       <c r="O54" s="8">
         <v>88</v>
@@ -4765,10 +4798,10 @@
     </row>
     <row r="55" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I55" s="6"/>
-      <c r="J55" s="69"/>
-      <c r="K55" s="69"/>
-      <c r="L55" s="69"/>
-      <c r="M55" s="69"/>
+      <c r="J55" s="70"/>
+      <c r="K55" s="70"/>
+      <c r="L55" s="70"/>
+      <c r="M55" s="70"/>
       <c r="N55" s="7"/>
       <c r="O55" s="8">
         <v>89</v>
@@ -4783,10 +4816,10 @@
     </row>
     <row r="56" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I56" s="6"/>
-      <c r="J56" s="69"/>
-      <c r="K56" s="69"/>
-      <c r="L56" s="69"/>
-      <c r="M56" s="69"/>
+      <c r="J56" s="70"/>
+      <c r="K56" s="70"/>
+      <c r="L56" s="70"/>
+      <c r="M56" s="70"/>
       <c r="N56" s="7"/>
       <c r="O56" s="8">
         <v>90</v>
@@ -4801,10 +4834,10 @@
     </row>
     <row r="57" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I57" s="6"/>
-      <c r="J57" s="69"/>
-      <c r="K57" s="69"/>
-      <c r="L57" s="69"/>
-      <c r="M57" s="69"/>
+      <c r="J57" s="70"/>
+      <c r="K57" s="70"/>
+      <c r="L57" s="70"/>
+      <c r="M57" s="70"/>
       <c r="N57" s="7"/>
       <c r="O57" s="8">
         <v>91</v>
@@ -4819,10 +4852,10 @@
     </row>
     <row r="58" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I58" s="6"/>
-      <c r="J58" s="69"/>
-      <c r="K58" s="69"/>
-      <c r="L58" s="69"/>
-      <c r="M58" s="69"/>
+      <c r="J58" s="70"/>
+      <c r="K58" s="70"/>
+      <c r="L58" s="70"/>
+      <c r="M58" s="70"/>
       <c r="N58" s="7"/>
       <c r="O58" s="8">
         <v>92</v>
@@ -4837,10 +4870,10 @@
     </row>
     <row r="59" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I59" s="6"/>
-      <c r="J59" s="69"/>
-      <c r="K59" s="69"/>
-      <c r="L59" s="69"/>
-      <c r="M59" s="69"/>
+      <c r="J59" s="70"/>
+      <c r="K59" s="70"/>
+      <c r="L59" s="70"/>
+      <c r="M59" s="70"/>
       <c r="N59" s="7"/>
       <c r="O59" s="8">
         <v>93</v>
@@ -4855,10 +4888,10 @@
     </row>
     <row r="60" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I60" s="6"/>
-      <c r="J60" s="69"/>
-      <c r="K60" s="69"/>
-      <c r="L60" s="69"/>
-      <c r="M60" s="69"/>
+      <c r="J60" s="70"/>
+      <c r="K60" s="70"/>
+      <c r="L60" s="70"/>
+      <c r="M60" s="70"/>
       <c r="N60" s="7"/>
       <c r="O60" s="8">
         <v>94</v>
@@ -4873,10 +4906,10 @@
     </row>
     <row r="61" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I61" s="6"/>
-      <c r="J61" s="69"/>
-      <c r="K61" s="69"/>
-      <c r="L61" s="69"/>
-      <c r="M61" s="69"/>
+      <c r="J61" s="70"/>
+      <c r="K61" s="70"/>
+      <c r="L61" s="70"/>
+      <c r="M61" s="70"/>
       <c r="N61" s="7"/>
       <c r="O61" s="8">
         <v>95</v>
@@ -4891,10 +4924,10 @@
     </row>
     <row r="62" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I62" s="6"/>
-      <c r="J62" s="69"/>
-      <c r="K62" s="69"/>
-      <c r="L62" s="69"/>
-      <c r="M62" s="69"/>
+      <c r="J62" s="70"/>
+      <c r="K62" s="70"/>
+      <c r="L62" s="70"/>
+      <c r="M62" s="70"/>
       <c r="N62" s="7"/>
       <c r="O62" s="8">
         <v>96</v>
@@ -4909,10 +4942,10 @@
     </row>
     <row r="63" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I63" s="6"/>
-      <c r="J63" s="69"/>
-      <c r="K63" s="69"/>
-      <c r="L63" s="69"/>
-      <c r="M63" s="69"/>
+      <c r="J63" s="70"/>
+      <c r="K63" s="70"/>
+      <c r="L63" s="70"/>
+      <c r="M63" s="70"/>
       <c r="N63" s="7"/>
       <c r="O63" s="8">
         <v>97</v>
@@ -4927,10 +4960,10 @@
     </row>
     <row r="64" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I64" s="6"/>
-      <c r="J64" s="69"/>
-      <c r="K64" s="69"/>
-      <c r="L64" s="69"/>
-      <c r="M64" s="69"/>
+      <c r="J64" s="70"/>
+      <c r="K64" s="70"/>
+      <c r="L64" s="70"/>
+      <c r="M64" s="70"/>
       <c r="N64" s="7"/>
       <c r="O64" s="8">
         <v>98</v>
@@ -4945,10 +4978,10 @@
     </row>
     <row r="65" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I65" s="6"/>
-      <c r="J65" s="69"/>
-      <c r="K65" s="69"/>
-      <c r="L65" s="69"/>
-      <c r="M65" s="69"/>
+      <c r="J65" s="70"/>
+      <c r="K65" s="70"/>
+      <c r="L65" s="70"/>
+      <c r="M65" s="70"/>
       <c r="N65" s="7"/>
       <c r="O65" s="8">
         <v>99</v>
@@ -4963,10 +4996,10 @@
     </row>
     <row r="66" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I66" s="6"/>
-      <c r="J66" s="69"/>
-      <c r="K66" s="69"/>
-      <c r="L66" s="69"/>
-      <c r="M66" s="69"/>
+      <c r="J66" s="70"/>
+      <c r="K66" s="70"/>
+      <c r="L66" s="70"/>
+      <c r="M66" s="70"/>
       <c r="N66" s="7"/>
       <c r="O66" s="8">
         <v>100</v>
@@ -4981,10 +5014,10 @@
     </row>
     <row r="67" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I67" s="6"/>
-      <c r="J67" s="69"/>
-      <c r="K67" s="69"/>
-      <c r="L67" s="69"/>
-      <c r="M67" s="69"/>
+      <c r="J67" s="70"/>
+      <c r="K67" s="70"/>
+      <c r="L67" s="70"/>
+      <c r="M67" s="70"/>
       <c r="N67" s="7"/>
       <c r="O67" s="8">
         <v>101</v>
@@ -4999,10 +5032,10 @@
     </row>
     <row r="68" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I68" s="6"/>
-      <c r="J68" s="69"/>
-      <c r="K68" s="69"/>
-      <c r="L68" s="69"/>
-      <c r="M68" s="69"/>
+      <c r="J68" s="70"/>
+      <c r="K68" s="70"/>
+      <c r="L68" s="70"/>
+      <c r="M68" s="70"/>
       <c r="N68" s="7"/>
       <c r="O68" s="8">
         <v>102</v>
@@ -5017,10 +5050,10 @@
     </row>
     <row r="69" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I69" s="6"/>
-      <c r="J69" s="69"/>
-      <c r="K69" s="69"/>
-      <c r="L69" s="69"/>
-      <c r="M69" s="69"/>
+      <c r="J69" s="70"/>
+      <c r="K69" s="70"/>
+      <c r="L69" s="70"/>
+      <c r="M69" s="70"/>
       <c r="N69" s="7"/>
       <c r="O69" s="8">
         <v>103</v>
@@ -5035,10 +5068,10 @@
     </row>
     <row r="70" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I70" s="6"/>
-      <c r="J70" s="69"/>
-      <c r="K70" s="69"/>
-      <c r="L70" s="69"/>
-      <c r="M70" s="69"/>
+      <c r="J70" s="70"/>
+      <c r="K70" s="70"/>
+      <c r="L70" s="70"/>
+      <c r="M70" s="70"/>
       <c r="N70" s="7"/>
       <c r="O70" s="8">
         <v>104</v>
@@ -5053,10 +5086,10 @@
     </row>
     <row r="71" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I71" s="6"/>
-      <c r="J71" s="69"/>
-      <c r="K71" s="69"/>
-      <c r="L71" s="69"/>
-      <c r="M71" s="69"/>
+      <c r="J71" s="70"/>
+      <c r="K71" s="70"/>
+      <c r="L71" s="70"/>
+      <c r="M71" s="70"/>
       <c r="N71" s="7"/>
       <c r="O71" s="8">
         <v>105</v>
@@ -5071,10 +5104,10 @@
     </row>
     <row r="72" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I72" s="6"/>
-      <c r="J72" s="69"/>
-      <c r="K72" s="69"/>
-      <c r="L72" s="69"/>
-      <c r="M72" s="69"/>
+      <c r="J72" s="70"/>
+      <c r="K72" s="70"/>
+      <c r="L72" s="70"/>
+      <c r="M72" s="70"/>
       <c r="N72" s="7"/>
       <c r="O72" s="8">
         <v>106</v>
@@ -5089,10 +5122,10 @@
     </row>
     <row r="73" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I73" s="6"/>
-      <c r="J73" s="69"/>
-      <c r="K73" s="69"/>
-      <c r="L73" s="69"/>
-      <c r="M73" s="69"/>
+      <c r="J73" s="70"/>
+      <c r="K73" s="70"/>
+      <c r="L73" s="70"/>
+      <c r="M73" s="70"/>
       <c r="N73" s="7"/>
       <c r="O73" s="8">
         <v>107</v>
@@ -5107,10 +5140,10 @@
     </row>
     <row r="74" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I74" s="6"/>
-      <c r="J74" s="69"/>
-      <c r="K74" s="69"/>
-      <c r="L74" s="69"/>
-      <c r="M74" s="69"/>
+      <c r="J74" s="70"/>
+      <c r="K74" s="70"/>
+      <c r="L74" s="70"/>
+      <c r="M74" s="70"/>
       <c r="N74" s="7"/>
       <c r="O74" s="8">
         <v>108</v>
@@ -5125,10 +5158,10 @@
     </row>
     <row r="75" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I75" s="6"/>
-      <c r="J75" s="69"/>
-      <c r="K75" s="69"/>
-      <c r="L75" s="69"/>
-      <c r="M75" s="69"/>
+      <c r="J75" s="70"/>
+      <c r="K75" s="70"/>
+      <c r="L75" s="70"/>
+      <c r="M75" s="70"/>
       <c r="N75" s="7"/>
       <c r="O75" s="8">
         <v>109</v>
@@ -5143,10 +5176,10 @@
     </row>
     <row r="76" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I76" s="6"/>
-      <c r="J76" s="69"/>
-      <c r="K76" s="69"/>
-      <c r="L76" s="69"/>
-      <c r="M76" s="69"/>
+      <c r="J76" s="70"/>
+      <c r="K76" s="70"/>
+      <c r="L76" s="70"/>
+      <c r="M76" s="70"/>
       <c r="N76" s="7"/>
       <c r="O76" s="8">
         <v>110</v>
@@ -5161,10 +5194,10 @@
     </row>
     <row r="77" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I77" s="6"/>
-      <c r="J77" s="69"/>
-      <c r="K77" s="69"/>
-      <c r="L77" s="69"/>
-      <c r="M77" s="69"/>
+      <c r="J77" s="70"/>
+      <c r="K77" s="70"/>
+      <c r="L77" s="70"/>
+      <c r="M77" s="70"/>
       <c r="N77" s="7"/>
       <c r="O77" s="8">
         <v>111</v>
@@ -5179,10 +5212,10 @@
     </row>
     <row r="78" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I78" s="6"/>
-      <c r="J78" s="69"/>
-      <c r="K78" s="69"/>
-      <c r="L78" s="69"/>
-      <c r="M78" s="69"/>
+      <c r="J78" s="70"/>
+      <c r="K78" s="70"/>
+      <c r="L78" s="70"/>
+      <c r="M78" s="70"/>
       <c r="N78" s="7"/>
       <c r="O78" s="8">
         <v>112</v>
@@ -5197,10 +5230,10 @@
     </row>
     <row r="79" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I79" s="6"/>
-      <c r="J79" s="69"/>
-      <c r="K79" s="69"/>
-      <c r="L79" s="69"/>
-      <c r="M79" s="69"/>
+      <c r="J79" s="70"/>
+      <c r="K79" s="70"/>
+      <c r="L79" s="70"/>
+      <c r="M79" s="70"/>
       <c r="N79" s="7"/>
       <c r="O79" s="8">
         <v>113</v>
@@ -5215,10 +5248,10 @@
     </row>
     <row r="80" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I80" s="6"/>
-      <c r="J80" s="69"/>
-      <c r="K80" s="69"/>
-      <c r="L80" s="69"/>
-      <c r="M80" s="69"/>
+      <c r="J80" s="70"/>
+      <c r="K80" s="70"/>
+      <c r="L80" s="70"/>
+      <c r="M80" s="70"/>
       <c r="N80" s="7"/>
       <c r="O80" s="8">
         <v>114</v>
@@ -5233,10 +5266,10 @@
     </row>
     <row r="81" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I81" s="6"/>
-      <c r="J81" s="69"/>
-      <c r="K81" s="69"/>
-      <c r="L81" s="69"/>
-      <c r="M81" s="69"/>
+      <c r="J81" s="70"/>
+      <c r="K81" s="70"/>
+      <c r="L81" s="70"/>
+      <c r="M81" s="70"/>
       <c r="N81" s="7"/>
       <c r="O81" s="8">
         <v>115</v>
@@ -5251,10 +5284,10 @@
     </row>
     <row r="82" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I82" s="6"/>
-      <c r="J82" s="69"/>
-      <c r="K82" s="69"/>
-      <c r="L82" s="69"/>
-      <c r="M82" s="69"/>
+      <c r="J82" s="70"/>
+      <c r="K82" s="70"/>
+      <c r="L82" s="70"/>
+      <c r="M82" s="70"/>
       <c r="N82" s="7"/>
       <c r="O82" s="8">
         <v>116</v>
@@ -5269,10 +5302,10 @@
     </row>
     <row r="83" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I83" s="6"/>
-      <c r="J83" s="69"/>
-      <c r="K83" s="69"/>
-      <c r="L83" s="69"/>
-      <c r="M83" s="69"/>
+      <c r="J83" s="70"/>
+      <c r="K83" s="70"/>
+      <c r="L83" s="70"/>
+      <c r="M83" s="70"/>
       <c r="N83" s="7"/>
       <c r="O83" s="8">
         <v>117</v>
@@ -5287,10 +5320,10 @@
     </row>
     <row r="84" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I84" s="6"/>
-      <c r="J84" s="69"/>
-      <c r="K84" s="69"/>
-      <c r="L84" s="69"/>
-      <c r="M84" s="69"/>
+      <c r="J84" s="70"/>
+      <c r="K84" s="70"/>
+      <c r="L84" s="70"/>
+      <c r="M84" s="70"/>
       <c r="N84" s="7"/>
       <c r="O84" s="8">
         <v>118</v>
@@ -5305,10 +5338,10 @@
     </row>
     <row r="85" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I85" s="6"/>
-      <c r="J85" s="69"/>
-      <c r="K85" s="69"/>
-      <c r="L85" s="69"/>
-      <c r="M85" s="69"/>
+      <c r="J85" s="70"/>
+      <c r="K85" s="70"/>
+      <c r="L85" s="70"/>
+      <c r="M85" s="70"/>
       <c r="N85" s="7"/>
       <c r="O85" s="8">
         <v>119</v>
@@ -5323,10 +5356,10 @@
     </row>
     <row r="86" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I86" s="6"/>
-      <c r="J86" s="69"/>
-      <c r="K86" s="69"/>
-      <c r="L86" s="69"/>
-      <c r="M86" s="69"/>
+      <c r="J86" s="70"/>
+      <c r="K86" s="70"/>
+      <c r="L86" s="70"/>
+      <c r="M86" s="70"/>
       <c r="N86" s="7"/>
       <c r="O86" s="8">
         <v>120</v>
@@ -5341,10 +5374,10 @@
     </row>
     <row r="87" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I87" s="6"/>
-      <c r="J87" s="69"/>
-      <c r="K87" s="69"/>
-      <c r="L87" s="69"/>
-      <c r="M87" s="69"/>
+      <c r="J87" s="70"/>
+      <c r="K87" s="70"/>
+      <c r="L87" s="70"/>
+      <c r="M87" s="70"/>
       <c r="N87" s="7"/>
       <c r="O87" s="8">
         <v>121</v>
@@ -5359,10 +5392,10 @@
     </row>
     <row r="88" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I88" s="6"/>
-      <c r="J88" s="69"/>
-      <c r="K88" s="69"/>
-      <c r="L88" s="69"/>
-      <c r="M88" s="69"/>
+      <c r="J88" s="70"/>
+      <c r="K88" s="70"/>
+      <c r="L88" s="70"/>
+      <c r="M88" s="70"/>
       <c r="N88" s="7"/>
       <c r="O88" s="8">
         <v>122</v>
@@ -5377,10 +5410,10 @@
     </row>
     <row r="89" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I89" s="6"/>
-      <c r="J89" s="69"/>
-      <c r="K89" s="69"/>
-      <c r="L89" s="69"/>
-      <c r="M89" s="69"/>
+      <c r="J89" s="70"/>
+      <c r="K89" s="70"/>
+      <c r="L89" s="70"/>
+      <c r="M89" s="70"/>
       <c r="N89" s="7"/>
       <c r="O89" s="8">
         <v>123</v>
@@ -5395,10 +5428,10 @@
     </row>
     <row r="90" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I90" s="6"/>
-      <c r="J90" s="69"/>
-      <c r="K90" s="69"/>
-      <c r="L90" s="69"/>
-      <c r="M90" s="69"/>
+      <c r="J90" s="70"/>
+      <c r="K90" s="70"/>
+      <c r="L90" s="70"/>
+      <c r="M90" s="70"/>
       <c r="N90" s="7"/>
       <c r="O90" s="8">
         <v>124</v>
@@ -5413,10 +5446,10 @@
     </row>
     <row r="91" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I91" s="6"/>
-      <c r="J91" s="69"/>
-      <c r="K91" s="69"/>
-      <c r="L91" s="69"/>
-      <c r="M91" s="69"/>
+      <c r="J91" s="70"/>
+      <c r="K91" s="70"/>
+      <c r="L91" s="70"/>
+      <c r="M91" s="70"/>
       <c r="N91" s="7"/>
       <c r="O91" s="8">
         <v>125</v>
@@ -5431,10 +5464,10 @@
     </row>
     <row r="92" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I92" s="6"/>
-      <c r="J92" s="69"/>
-      <c r="K92" s="69"/>
-      <c r="L92" s="69"/>
-      <c r="M92" s="69"/>
+      <c r="J92" s="70"/>
+      <c r="K92" s="70"/>
+      <c r="L92" s="70"/>
+      <c r="M92" s="70"/>
       <c r="N92" s="7"/>
       <c r="O92" s="8">
         <v>126</v>
@@ -5449,10 +5482,10 @@
     </row>
     <row r="93" spans="9:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I93" s="6"/>
-      <c r="J93" s="69"/>
-      <c r="K93" s="69"/>
-      <c r="L93" s="69"/>
-      <c r="M93" s="69"/>
+      <c r="J93" s="70"/>
+      <c r="K93" s="70"/>
+      <c r="L93" s="70"/>
+      <c r="M93" s="70"/>
       <c r="N93" s="7"/>
       <c r="O93" s="8">
         <v>127</v>
@@ -7645,31 +7678,47 @@
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="J18:M18"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="J93:M93"/>
+    <mergeCell ref="J88:M88"/>
+    <mergeCell ref="J89:M89"/>
+    <mergeCell ref="J90:M90"/>
+    <mergeCell ref="J91:M91"/>
+    <mergeCell ref="J92:M92"/>
+    <mergeCell ref="J83:M83"/>
+    <mergeCell ref="J84:M84"/>
+    <mergeCell ref="J85:M85"/>
+    <mergeCell ref="J86:M86"/>
+    <mergeCell ref="J87:M87"/>
+    <mergeCell ref="J78:M78"/>
+    <mergeCell ref="J79:M79"/>
+    <mergeCell ref="J80:M80"/>
+    <mergeCell ref="J81:M81"/>
+    <mergeCell ref="J82:M82"/>
+    <mergeCell ref="J73:M73"/>
+    <mergeCell ref="J74:M74"/>
+    <mergeCell ref="J75:M75"/>
+    <mergeCell ref="J76:M76"/>
+    <mergeCell ref="J77:M77"/>
+    <mergeCell ref="J68:M68"/>
+    <mergeCell ref="J69:M69"/>
+    <mergeCell ref="J70:M70"/>
+    <mergeCell ref="J71:M71"/>
+    <mergeCell ref="J72:M72"/>
+    <mergeCell ref="J63:M63"/>
+    <mergeCell ref="J64:M64"/>
+    <mergeCell ref="J65:M65"/>
+    <mergeCell ref="J66:M66"/>
+    <mergeCell ref="J67:M67"/>
+    <mergeCell ref="J58:M58"/>
+    <mergeCell ref="J59:M59"/>
+    <mergeCell ref="J60:M60"/>
+    <mergeCell ref="J61:M61"/>
+    <mergeCell ref="J62:M62"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="J54:M54"/>
+    <mergeCell ref="J55:M55"/>
+    <mergeCell ref="J56:M56"/>
+    <mergeCell ref="J57:M57"/>
     <mergeCell ref="J40:M40"/>
     <mergeCell ref="J41:M41"/>
     <mergeCell ref="J42:M42"/>
@@ -7684,47 +7733,31 @@
     <mergeCell ref="J50:M50"/>
     <mergeCell ref="J51:M51"/>
     <mergeCell ref="J52:M52"/>
-    <mergeCell ref="J53:M53"/>
-    <mergeCell ref="J54:M54"/>
-    <mergeCell ref="J55:M55"/>
-    <mergeCell ref="J56:M56"/>
-    <mergeCell ref="J57:M57"/>
-    <mergeCell ref="J58:M58"/>
-    <mergeCell ref="J59:M59"/>
-    <mergeCell ref="J60:M60"/>
-    <mergeCell ref="J61:M61"/>
-    <mergeCell ref="J62:M62"/>
-    <mergeCell ref="J63:M63"/>
-    <mergeCell ref="J64:M64"/>
-    <mergeCell ref="J65:M65"/>
-    <mergeCell ref="J66:M66"/>
-    <mergeCell ref="J67:M67"/>
-    <mergeCell ref="J68:M68"/>
-    <mergeCell ref="J69:M69"/>
-    <mergeCell ref="J70:M70"/>
-    <mergeCell ref="J71:M71"/>
-    <mergeCell ref="J72:M72"/>
-    <mergeCell ref="J73:M73"/>
-    <mergeCell ref="J74:M74"/>
-    <mergeCell ref="J75:M75"/>
-    <mergeCell ref="J76:M76"/>
-    <mergeCell ref="J77:M77"/>
-    <mergeCell ref="J78:M78"/>
-    <mergeCell ref="J79:M79"/>
-    <mergeCell ref="J80:M80"/>
-    <mergeCell ref="J81:M81"/>
-    <mergeCell ref="J82:M82"/>
-    <mergeCell ref="J83:M83"/>
-    <mergeCell ref="J84:M84"/>
-    <mergeCell ref="J85:M85"/>
-    <mergeCell ref="J86:M86"/>
-    <mergeCell ref="J87:M87"/>
-    <mergeCell ref="J93:M93"/>
-    <mergeCell ref="J88:M88"/>
-    <mergeCell ref="J89:M89"/>
-    <mergeCell ref="J90:M90"/>
-    <mergeCell ref="J91:M91"/>
-    <mergeCell ref="J92:M92"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="J19:M19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7824,1125 +7857,1125 @@
       <c r="U1" s="20"/>
     </row>
     <row r="2" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42"/>
-      <c r="B2" s="42" t="s">
+      <c r="A2" s="41"/>
+      <c r="B2" s="41" t="s">
         <v>553</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="42" t="s">
         <v>554</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42" t="s">
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41" t="s">
         <v>556</v>
       </c>
-      <c r="P2" s="42" t="s">
+      <c r="P2" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q2" s="44" t="s">
+      <c r="Q2" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R2" s="42" t="s">
+      <c r="R2" s="41" t="s">
         <v>558</v>
       </c>
-      <c r="S2" s="42" t="s">
+      <c r="S2" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="41" t="s">
         <v>513</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="41" t="s">
         <v>559</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="42" t="s">
         <v>560</v>
       </c>
-      <c r="E3" s="42" t="s">
+      <c r="E3" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="42" t="s">
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41" t="s">
         <v>561</v>
       </c>
-      <c r="P3" s="42" t="s">
+      <c r="P3" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q3" s="44" t="s">
+      <c r="Q3" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R3" s="42" t="s">
+      <c r="R3" s="41" t="s">
         <v>562</v>
       </c>
-      <c r="S3" s="42" t="s">
+      <c r="S3" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="41" t="s">
         <v>563</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="41" t="s">
         <v>564</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="42" t="s">
         <v>565</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="E4" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42"/>
-      <c r="O4" s="42" t="s">
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41" t="s">
         <v>561</v>
       </c>
-      <c r="P4" s="42" t="s">
+      <c r="P4" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q4" s="44" t="s">
+      <c r="Q4" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R4" s="42" t="s">
+      <c r="R4" s="41" t="s">
         <v>566</v>
       </c>
-      <c r="S4" s="42" t="s">
+      <c r="S4" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="41" t="s">
         <v>567</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="41" t="s">
         <v>568</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="43" t="s">
+      <c r="D5" s="42" t="s">
         <v>569</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="E5" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="42"/>
-      <c r="M5" s="42"/>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42" t="s">
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41" t="s">
         <v>561</v>
       </c>
-      <c r="P5" s="42" t="s">
+      <c r="P5" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q5" s="44" t="s">
+      <c r="Q5" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R5" s="42" t="s">
+      <c r="R5" s="41" t="s">
         <v>570</v>
       </c>
-      <c r="S5" s="42" t="s">
+      <c r="S5" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="41" t="s">
         <v>571</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42" t="s">
+      <c r="B6" s="41"/>
+      <c r="C6" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="42" t="s">
         <v>572</v>
       </c>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42" t="s">
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41" t="s">
         <v>573</v>
       </c>
-      <c r="P6" s="42" t="s">
+      <c r="P6" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q6" s="44" t="s">
+      <c r="Q6" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R6" s="45" t="s">
+      <c r="R6" s="44" t="s">
         <v>574</v>
       </c>
-      <c r="S6" s="42" t="s">
+      <c r="S6" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="41" t="s">
         <v>571</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="41" t="s">
         <v>513</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="43" t="s">
+      <c r="D7" s="42" t="s">
         <v>575</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="42"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="42" t="s">
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="41" t="s">
         <v>576</v>
       </c>
-      <c r="P7" s="42" t="s">
+      <c r="P7" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q7" s="44" t="s">
+      <c r="Q7" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R7" s="42" t="s">
+      <c r="R7" s="41" t="s">
         <v>577</v>
       </c>
-      <c r="S7" s="42" t="s">
+      <c r="S7" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="41" t="s">
         <v>571</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="41" t="s">
         <v>513</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="43" t="s">
+      <c r="D8" s="42" t="s">
         <v>578</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
-      <c r="N8" s="42"/>
-      <c r="O8" s="42" t="s">
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="41"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="41" t="s">
         <v>576</v>
       </c>
-      <c r="P8" s="42" t="s">
+      <c r="P8" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q8" s="44" t="s">
+      <c r="Q8" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R8" s="42" t="s">
+      <c r="R8" s="41" t="s">
         <v>579</v>
       </c>
-      <c r="S8" s="42" t="s">
+      <c r="S8" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="41" t="s">
         <v>571</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="41" t="s">
         <v>580</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="43" t="s">
+      <c r="D9" s="42" t="s">
         <v>578</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="42"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="42"/>
-      <c r="N9" s="42"/>
-      <c r="O9" s="42" t="s">
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="41" t="s">
         <v>576</v>
       </c>
-      <c r="P9" s="42" t="s">
+      <c r="P9" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q9" s="44" t="s">
+      <c r="Q9" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R9" s="42" t="s">
+      <c r="R9" s="41" t="s">
         <v>581</v>
       </c>
-      <c r="S9" s="42" t="s">
+      <c r="S9" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="41" t="s">
         <v>571</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="41" t="s">
         <v>582</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="43" t="s">
+      <c r="D10" s="42" t="s">
         <v>583</v>
       </c>
-      <c r="E10" s="42" t="s">
+      <c r="E10" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="42"/>
-      <c r="O10" s="42" t="s">
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="41" t="s">
         <v>576</v>
       </c>
-      <c r="P10" s="42" t="s">
+      <c r="P10" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q10" s="44" t="s">
+      <c r="Q10" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R10" s="42" t="s">
+      <c r="R10" s="41" t="s">
         <v>584</v>
       </c>
-      <c r="S10" s="42" t="s">
+      <c r="S10" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="41" t="s">
         <v>571</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="41" t="s">
         <v>585</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="43" t="s">
+      <c r="D11" s="42" t="s">
         <v>586</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="E11" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="42"/>
-      <c r="M11" s="42"/>
-      <c r="N11" s="42"/>
-      <c r="O11" s="42" t="s">
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="41"/>
+      <c r="N11" s="41"/>
+      <c r="O11" s="41" t="s">
         <v>576</v>
       </c>
-      <c r="P11" s="42" t="s">
+      <c r="P11" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q11" s="44" t="s">
+      <c r="Q11" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R11" s="42" t="s">
+      <c r="R11" s="41" t="s">
         <v>587</v>
       </c>
-      <c r="S11" s="42" t="s">
+      <c r="S11" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="41" t="s">
         <v>588</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="41" t="s">
         <v>589</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="46"/>
-      <c r="E12" s="42" t="s">
+      <c r="D12" s="45"/>
+      <c r="E12" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
-      <c r="K12" s="42"/>
-      <c r="L12" s="42"/>
-      <c r="M12" s="42"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="42" t="s">
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="41"/>
+      <c r="L12" s="41"/>
+      <c r="M12" s="41"/>
+      <c r="N12" s="41"/>
+      <c r="O12" s="41" t="s">
         <v>590</v>
       </c>
-      <c r="P12" s="42" t="s">
+      <c r="P12" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q12" s="44" t="s">
+      <c r="Q12" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R12" s="45" t="s">
+      <c r="R12" s="44" t="s">
         <v>591</v>
       </c>
-      <c r="S12" s="42" t="s">
+      <c r="S12" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="41" t="s">
         <v>588</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="41" t="s">
         <v>592</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="43" t="s">
+      <c r="D13" s="42" t="s">
         <v>513</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="42"/>
-      <c r="K13" s="42"/>
-      <c r="L13" s="42"/>
-      <c r="M13" s="42"/>
-      <c r="N13" s="42"/>
-      <c r="O13" s="42" t="s">
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41"/>
+      <c r="O13" s="41" t="s">
         <v>593</v>
       </c>
-      <c r="P13" s="42" t="s">
+      <c r="P13" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q13" s="44" t="s">
+      <c r="Q13" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R13" s="42" t="s">
+      <c r="R13" s="41" t="s">
         <v>594</v>
       </c>
-      <c r="S13" s="42" t="s">
+      <c r="S13" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="41" t="s">
         <v>588</v>
       </c>
-      <c r="B14" s="42" t="s">
+      <c r="B14" s="41" t="s">
         <v>595</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="C14" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="43" t="s">
+      <c r="D14" s="42" t="s">
         <v>596</v>
       </c>
-      <c r="E14" s="42" t="s">
+      <c r="E14" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="42"/>
-      <c r="L14" s="42"/>
-      <c r="M14" s="42"/>
-      <c r="N14" s="42"/>
-      <c r="O14" s="42" t="s">
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="41"/>
+      <c r="M14" s="41"/>
+      <c r="N14" s="41"/>
+      <c r="O14" s="41" t="s">
         <v>593</v>
       </c>
-      <c r="P14" s="42" t="s">
+      <c r="P14" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q14" s="44" t="s">
+      <c r="Q14" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R14" s="42" t="s">
+      <c r="R14" s="41" t="s">
         <v>597</v>
       </c>
-      <c r="S14" s="42" t="s">
+      <c r="S14" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="42" t="s">
+      <c r="A15" s="41" t="s">
         <v>588</v>
       </c>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="41" t="s">
         <v>598</v>
       </c>
-      <c r="C15" s="42" t="s">
+      <c r="C15" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="43" t="s">
+      <c r="D15" s="42" t="s">
         <v>599</v>
       </c>
-      <c r="E15" s="42" t="s">
+      <c r="E15" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="42"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="42"/>
-      <c r="M15" s="42"/>
-      <c r="N15" s="42"/>
-      <c r="O15" s="42" t="s">
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="41" t="s">
         <v>593</v>
       </c>
-      <c r="P15" s="42" t="s">
+      <c r="P15" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q15" s="44" t="s">
+      <c r="Q15" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R15" s="42" t="s">
+      <c r="R15" s="41" t="s">
         <v>600</v>
       </c>
-      <c r="S15" s="42" t="s">
+      <c r="S15" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="41" t="s">
         <v>588</v>
       </c>
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="41" t="s">
         <v>601</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="43" t="s">
+      <c r="D16" s="42" t="s">
         <v>602</v>
       </c>
-      <c r="E16" s="42" t="s">
+      <c r="E16" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="42"/>
-      <c r="K16" s="42"/>
-      <c r="L16" s="42"/>
-      <c r="M16" s="42"/>
-      <c r="N16" s="42"/>
-      <c r="O16" s="42" t="s">
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="41" t="s">
         <v>593</v>
       </c>
-      <c r="P16" s="42" t="s">
+      <c r="P16" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q16" s="44" t="s">
+      <c r="Q16" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R16" s="42" t="s">
+      <c r="R16" s="41" t="s">
         <v>603</v>
       </c>
-      <c r="S16" s="42" t="s">
+      <c r="S16" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="42" t="s">
+      <c r="A17" s="41" t="s">
         <v>604</v>
       </c>
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="41" t="s">
         <v>605</v>
       </c>
-      <c r="C17" s="42"/>
-      <c r="D17" s="43" t="s">
+      <c r="C17" s="41"/>
+      <c r="D17" s="42" t="s">
         <v>606</v>
       </c>
-      <c r="E17" s="42" t="s">
+      <c r="E17" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
-      <c r="L17" s="42"/>
-      <c r="M17" s="42"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="42" t="s">
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="41"/>
+      <c r="M17" s="41"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="41" t="s">
         <v>478</v>
       </c>
-      <c r="P17" s="42" t="s">
+      <c r="P17" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q17" s="44" t="s">
+      <c r="Q17" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R17" s="42" t="s">
+      <c r="R17" s="41" t="s">
         <v>481</v>
       </c>
-      <c r="S17" s="42" t="s">
+      <c r="S17" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="41" t="s">
         <v>604</v>
       </c>
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="41" t="s">
         <v>607</v>
       </c>
-      <c r="C18" s="42" t="s">
+      <c r="C18" s="41" t="s">
         <v>513</v>
       </c>
-      <c r="D18" s="43" t="s">
+      <c r="D18" s="42" t="s">
         <v>608</v>
       </c>
-      <c r="E18" s="42" t="s">
+      <c r="E18" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="42" t="s">
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="41" t="s">
         <v>609</v>
       </c>
-      <c r="P18" s="42" t="s">
+      <c r="P18" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q18" s="44" t="s">
+      <c r="Q18" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R18" s="42" t="s">
+      <c r="R18" s="41" t="s">
         <v>484</v>
       </c>
-      <c r="S18" s="42" t="s">
+      <c r="S18" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="42" t="s">
+      <c r="A19" s="41" t="s">
         <v>604</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="41" t="s">
         <v>610</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="41" t="s">
         <v>611</v>
       </c>
-      <c r="D19" s="43" t="s">
+      <c r="D19" s="42" t="s">
         <v>612</v>
       </c>
-      <c r="E19" s="42" t="s">
+      <c r="E19" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="42" t="s">
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="41" t="s">
         <v>609</v>
       </c>
-      <c r="P19" s="42" t="s">
+      <c r="P19" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q19" s="44" t="s">
+      <c r="Q19" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R19" s="42" t="s">
+      <c r="R19" s="41" t="s">
         <v>485</v>
       </c>
-      <c r="S19" s="42" t="s">
+      <c r="S19" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="42" t="s">
+      <c r="A20" s="41" t="s">
         <v>604</v>
       </c>
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="41" t="s">
         <v>613</v>
       </c>
-      <c r="C20" s="42" t="s">
+      <c r="C20" s="41" t="s">
         <v>614</v>
       </c>
-      <c r="D20" s="43" t="s">
+      <c r="D20" s="42" t="s">
         <v>615</v>
       </c>
-      <c r="E20" s="42" t="s">
+      <c r="E20" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="42"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="42"/>
-      <c r="O20" s="42" t="s">
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="41"/>
+      <c r="L20" s="41"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="41" t="s">
         <v>616</v>
       </c>
-      <c r="P20" s="42" t="s">
+      <c r="P20" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q20" s="44" t="s">
+      <c r="Q20" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R20" s="42" t="s">
+      <c r="R20" s="41" t="s">
         <v>486</v>
       </c>
-      <c r="S20" s="42" t="s">
+      <c r="S20" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="42" t="s">
+      <c r="A21" s="41" t="s">
         <v>604</v>
       </c>
-      <c r="B21" s="42" t="s">
+      <c r="B21" s="41" t="s">
         <v>617</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="41" t="s">
         <v>618</v>
       </c>
-      <c r="D21" s="43" t="s">
+      <c r="D21" s="42" t="s">
         <v>619</v>
       </c>
-      <c r="E21" s="42" t="s">
+      <c r="E21" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="42"/>
-      <c r="K21" s="42"/>
-      <c r="L21" s="42"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="42"/>
-      <c r="O21" s="42" t="s">
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="41"/>
+      <c r="L21" s="41"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="41"/>
+      <c r="O21" s="41" t="s">
         <v>609</v>
       </c>
-      <c r="P21" s="42" t="s">
+      <c r="P21" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q21" s="44" t="s">
+      <c r="Q21" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R21" s="42" t="s">
+      <c r="R21" s="41" t="s">
         <v>487</v>
       </c>
-      <c r="S21" s="42" t="s">
+      <c r="S21" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="42" t="s">
+      <c r="A22" s="41" t="s">
         <v>620</v>
       </c>
-      <c r="B22" s="42" t="s">
+      <c r="B22" s="41" t="s">
         <v>621</v>
       </c>
-      <c r="C22" s="42" t="s">
+      <c r="C22" s="41" t="s">
         <v>622</v>
       </c>
-      <c r="D22" s="43" t="s">
+      <c r="D22" s="42" t="s">
         <v>623</v>
       </c>
-      <c r="E22" s="42" t="s">
+      <c r="E22" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="42"/>
-      <c r="J22" s="42"/>
-      <c r="K22" s="42"/>
-      <c r="L22" s="42"/>
-      <c r="M22" s="42"/>
-      <c r="N22" s="42"/>
-      <c r="O22" s="42" t="s">
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="41"/>
+      <c r="L22" s="41"/>
+      <c r="M22" s="41"/>
+      <c r="N22" s="41"/>
+      <c r="O22" s="41" t="s">
         <v>616</v>
       </c>
-      <c r="P22" s="42" t="s">
+      <c r="P22" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q22" s="44" t="s">
+      <c r="Q22" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R22" s="42" t="s">
+      <c r="R22" s="41" t="s">
         <v>488</v>
       </c>
-      <c r="S22" s="42" t="s">
+      <c r="S22" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="41" t="s">
         <v>624</v>
       </c>
-      <c r="B23" s="42" t="s">
+      <c r="B23" s="41" t="s">
         <v>625</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="41" t="s">
         <v>626</v>
       </c>
-      <c r="D23" s="43" t="s">
+      <c r="D23" s="42" t="s">
         <v>627</v>
       </c>
-      <c r="E23" s="42" t="s">
+      <c r="E23" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42"/>
-      <c r="K23" s="42"/>
-      <c r="L23" s="42"/>
-      <c r="M23" s="42"/>
-      <c r="N23" s="42"/>
-      <c r="O23" s="42" t="s">
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="41"/>
+      <c r="K23" s="41"/>
+      <c r="L23" s="41"/>
+      <c r="M23" s="41"/>
+      <c r="N23" s="41"/>
+      <c r="O23" s="41" t="s">
         <v>616</v>
       </c>
-      <c r="P23" s="42" t="s">
+      <c r="P23" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q23" s="44" t="s">
+      <c r="Q23" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R23" s="42" t="s">
+      <c r="R23" s="41" t="s">
         <v>489</v>
       </c>
-      <c r="S23" s="42" t="s">
+      <c r="S23" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="42" t="s">
+      <c r="A24" s="41" t="s">
         <v>628</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="41" t="s">
         <v>629</v>
       </c>
-      <c r="C24" s="42" t="s">
+      <c r="C24" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="43" t="s">
+      <c r="D24" s="42" t="s">
         <v>630</v>
       </c>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="42"/>
-      <c r="K24" s="42"/>
-      <c r="L24" s="42"/>
-      <c r="M24" s="42"/>
-      <c r="N24" s="42"/>
-      <c r="O24" s="42" t="s">
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="41"/>
+      <c r="K24" s="41"/>
+      <c r="L24" s="41"/>
+      <c r="M24" s="41"/>
+      <c r="N24" s="41"/>
+      <c r="O24" s="41" t="s">
         <v>631</v>
       </c>
-      <c r="P24" s="42" t="s">
+      <c r="P24" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q24" s="44" t="s">
+      <c r="Q24" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R24" s="42" t="s">
+      <c r="R24" s="41" t="s">
         <v>632</v>
       </c>
-      <c r="S24" s="42" t="s">
+      <c r="S24" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="41" t="s">
         <v>633</v>
       </c>
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="41" t="s">
         <v>634</v>
       </c>
-      <c r="C25" s="42" t="s">
+      <c r="C25" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D25" s="43" t="s">
+      <c r="D25" s="42" t="s">
         <v>635</v>
       </c>
-      <c r="E25" s="42" t="s">
+      <c r="E25" s="41" t="s">
         <v>513</v>
       </c>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="42"/>
-      <c r="K25" s="42"/>
-      <c r="L25" s="42"/>
-      <c r="M25" s="42"/>
-      <c r="N25" s="42"/>
-      <c r="O25" s="42" t="s">
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="41"/>
+      <c r="L25" s="41"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="41"/>
+      <c r="O25" s="41" t="s">
         <v>493</v>
       </c>
-      <c r="P25" s="42" t="s">
+      <c r="P25" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q25" s="44" t="s">
+      <c r="Q25" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R25" s="42" t="s">
+      <c r="R25" s="41" t="s">
         <v>636</v>
       </c>
-      <c r="S25" s="42" t="s">
+      <c r="S25" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" s="42" t="s">
+      <c r="A26" s="41" t="s">
         <v>637</v>
       </c>
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="41" t="s">
         <v>638</v>
       </c>
-      <c r="C26" s="42" t="s">
+      <c r="C26" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="43" t="s">
+      <c r="D26" s="42" t="s">
         <v>639</v>
       </c>
-      <c r="E26" s="42" t="s">
+      <c r="E26" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="F26" s="42" t="s">
+      <c r="F26" s="41" t="s">
         <v>640</v>
       </c>
-      <c r="G26" s="42"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="42"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="42"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="42"/>
-      <c r="O26" s="42" t="s">
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="41"/>
+      <c r="L26" s="41"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="41" t="s">
         <v>641</v>
       </c>
-      <c r="P26" s="42" t="s">
+      <c r="P26" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="Q26" s="44" t="s">
+      <c r="Q26" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="R26" s="42" t="s">
+      <c r="R26" s="41" t="s">
         <v>642</v>
       </c>
-      <c r="S26" s="42" t="s">
+      <c r="S26" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="46" t="s">
         <v>637</v>
       </c>
-      <c r="B27" s="47" t="s">
+      <c r="B27" s="46" t="s">
         <v>643</v>
       </c>
-      <c r="C27" s="47" t="s">
+      <c r="C27" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="48" t="s">
+      <c r="D27" s="47" t="s">
         <v>644</v>
       </c>
-      <c r="E27" s="47" t="s">
+      <c r="E27" s="46" t="s">
         <v>555</v>
       </c>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="47" t="s">
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="46"/>
+      <c r="N27" s="46"/>
+      <c r="O27" s="46" t="s">
         <v>645</v>
       </c>
-      <c r="P27" s="47" t="s">
+      <c r="P27" s="46" t="s">
         <v>479</v>
       </c>
-      <c r="Q27" s="49" t="s">
+      <c r="Q27" s="48" t="s">
         <v>557</v>
       </c>
-      <c r="R27" s="47" t="s">
+      <c r="R27" s="46" t="s">
         <v>646</v>
       </c>
-      <c r="S27" s="47" t="s">
+      <c r="S27" s="46" t="s">
         <v>504</v>
       </c>
-      <c r="T27" s="50" t="s">
+      <c r="T27" s="49" t="s">
         <v>676</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" s="47" t="s">
+      <c r="A28" s="46" t="s">
         <v>647</v>
       </c>
-      <c r="B28" s="47" t="s">
+      <c r="B28" s="46" t="s">
         <v>648</v>
       </c>
-      <c r="C28" s="47" t="s">
+      <c r="C28" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="48" t="s">
+      <c r="D28" s="47" t="s">
         <v>649</v>
       </c>
-      <c r="E28" s="47" t="s">
+      <c r="E28" s="46" t="s">
         <v>555</v>
       </c>
-      <c r="F28" s="47" t="s">
+      <c r="F28" s="46" t="s">
         <v>650</v>
       </c>
-      <c r="G28" s="47" t="s">
+      <c r="G28" s="46" t="s">
         <v>651</v>
       </c>
-      <c r="H28" s="47" t="s">
+      <c r="H28" s="46" t="s">
         <v>652</v>
       </c>
-      <c r="I28" s="47" t="s">
+      <c r="I28" s="46" t="s">
         <v>653</v>
       </c>
-      <c r="J28" s="47" t="s">
+      <c r="J28" s="46" t="s">
         <v>654</v>
       </c>
-      <c r="K28" s="47" t="s">
+      <c r="K28" s="46" t="s">
         <v>655</v>
       </c>
-      <c r="L28" s="47" t="s">
+      <c r="L28" s="46" t="s">
         <v>656</v>
       </c>
-      <c r="M28" s="47" t="s">
+      <c r="M28" s="46" t="s">
         <v>657</v>
       </c>
-      <c r="N28" s="47" t="s">
+      <c r="N28" s="46" t="s">
         <v>658</v>
       </c>
-      <c r="O28" s="47" t="s">
+      <c r="O28" s="46" t="s">
         <v>645</v>
       </c>
-      <c r="P28" s="47" t="s">
+      <c r="P28" s="46" t="s">
         <v>479</v>
       </c>
-      <c r="Q28" s="49" t="s">
+      <c r="Q28" s="48" t="s">
         <v>557</v>
       </c>
-      <c r="R28" s="47" t="s">
+      <c r="R28" s="46" t="s">
         <v>659</v>
       </c>
-      <c r="S28" s="47" t="s">
+      <c r="S28" s="46" t="s">
         <v>504</v>
       </c>
-      <c r="T28" s="50" t="s">
+      <c r="T28" s="49" t="s">
         <v>675</v>
       </c>
     </row>
@@ -9016,22 +9049,22 @@
       <c r="U1" s="4"/>
     </row>
     <row r="2" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="51" t="s">
         <v>526</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="52" t="s">
         <v>526</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="52" t="s">
         <v>479</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="52" t="s">
         <v>527</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="52" t="s">
         <v>528</v>
       </c>
-      <c r="F2" s="53" t="s">
+      <c r="F2" s="52" t="s">
         <v>504</v>
       </c>
       <c r="G2" s="4"/>
@@ -9051,20 +9084,20 @@
       <c r="U2" s="4"/>
     </row>
     <row r="3" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53" t="s">
+      <c r="A3" s="51"/>
+      <c r="B3" s="52" t="s">
         <v>529</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="52" t="s">
         <v>479</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="D3" s="52" t="s">
         <v>530</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="52" t="s">
         <v>531</v>
       </c>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="52" t="s">
         <v>504</v>
       </c>
       <c r="O3" s="4"/>
@@ -9074,22 +9107,22 @@
       <c r="S3" s="4"/>
     </row>
     <row r="4" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="51" t="s">
         <v>513</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="52" t="s">
         <v>529</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="52" t="s">
         <v>479</v>
       </c>
-      <c r="D4" s="53" t="s">
+      <c r="D4" s="52" t="s">
         <v>532</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="E4" s="52" t="s">
         <v>533</v>
       </c>
-      <c r="F4" s="53" t="s">
+      <c r="F4" s="52" t="s">
         <v>504</v>
       </c>
       <c r="O4" s="4"/>
@@ -9099,7 +9132,7 @@
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="50" t="s">
         <v>534</v>
       </c>
       <c r="B5" s="34" t="s">
@@ -9124,22 +9157,22 @@
       <c r="S5" s="4"/>
     </row>
     <row r="6" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="51" t="s">
         <v>538</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="52" t="s">
         <v>538</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="52" t="s">
         <v>479</v>
       </c>
-      <c r="D6" s="53" t="s">
+      <c r="D6" s="52" t="s">
         <v>539</v>
       </c>
-      <c r="E6" s="53" t="s">
+      <c r="E6" s="52" t="s">
         <v>540</v>
       </c>
-      <c r="F6" s="53" t="s">
+      <c r="F6" s="52" t="s">
         <v>504</v>
       </c>
       <c r="O6" s="4"/>
@@ -9149,22 +9182,22 @@
       <c r="S6" s="4"/>
     </row>
     <row r="7" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="51" t="s">
         <v>541</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="B7" s="52" t="s">
         <v>526</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" s="52" t="s">
         <v>479</v>
       </c>
-      <c r="D7" s="53" t="s">
+      <c r="D7" s="52" t="s">
         <v>542</v>
       </c>
-      <c r="E7" s="53" t="s">
+      <c r="E7" s="52" t="s">
         <v>543</v>
       </c>
-      <c r="F7" s="53" t="s">
+      <c r="F7" s="52" t="s">
         <v>504</v>
       </c>
       <c r="O7" s="4"/>
@@ -9174,7 +9207,7 @@
       <c r="S7" s="4"/>
     </row>
     <row r="8" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="51">
+      <c r="A8" s="50">
         <v>1000000</v>
       </c>
       <c r="B8" s="34" t="s">
@@ -9199,7 +9232,7 @@
       <c r="S8" s="4"/>
     </row>
     <row r="9" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="51" t="s">
+      <c r="A9" s="50" t="s">
         <v>546</v>
       </c>
       <c r="B9" s="34" t="s">
@@ -9485,7 +9518,7 @@
       <c r="A2" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="51"/>
+      <c r="B2" s="50"/>
       <c r="C2" s="34" t="s">
         <v>506</v>
       </c>
@@ -9509,7 +9542,7 @@
       <c r="A3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="51">
+      <c r="B3" s="50">
         <v>123</v>
       </c>
       <c r="C3" s="34" t="s">
@@ -9538,7 +9571,7 @@
       <c r="A4" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="50" t="s">
         <v>513</v>
       </c>
       <c r="C4" s="34" t="s">
@@ -9564,7 +9597,7 @@
       <c r="A5" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="50" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="34" t="s">
@@ -9590,7 +9623,7 @@
       <c r="A6" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="50" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="34"/>
@@ -9614,7 +9647,7 @@
       <c r="A7" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="50" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="34" t="s">
@@ -9637,28 +9670,28 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="55" t="s">
+      <c r="B8" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="53" t="s">
         <v>506</v>
       </c>
-      <c r="D8" s="54" t="s">
+      <c r="D8" s="53" t="s">
         <v>522</v>
       </c>
-      <c r="E8" s="54" t="s">
+      <c r="E8" s="53" t="s">
         <v>479</v>
       </c>
-      <c r="F8" s="54" t="s">
+      <c r="F8" s="53" t="s">
         <v>523</v>
       </c>
-      <c r="G8" s="54" t="s">
+      <c r="G8" s="53" t="s">
         <v>524</v>
       </c>
-      <c r="H8" s="54" t="s">
+      <c r="H8" s="53" t="s">
         <v>504</v>
       </c>
     </row>
@@ -9738,227 +9771,227 @@
     </row>
     <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="31"/>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="41" t="s">
         <v>478</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="F2" s="42" t="s">
+      <c r="F2" s="41" t="s">
         <v>480</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="41" t="s">
         <v>481</v>
       </c>
-      <c r="H2" s="42" t="s">
+      <c r="H2" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="31"/>
-      <c r="D3" s="45" t="s">
+      <c r="D3" s="44" t="s">
         <v>483</v>
       </c>
-      <c r="E3" s="42" t="s">
+      <c r="E3" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="F3" s="41" t="s">
         <v>480</v>
       </c>
-      <c r="G3" s="42" t="s">
+      <c r="G3" s="41" t="s">
         <v>484</v>
       </c>
-      <c r="H3" s="42" t="s">
+      <c r="H3" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="31"/>
-      <c r="D4" s="45" t="s">
+      <c r="D4" s="44" t="s">
         <v>483</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="E4" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="F4" s="42" t="s">
+      <c r="F4" s="41" t="s">
         <v>480</v>
       </c>
-      <c r="G4" s="42" t="s">
+      <c r="G4" s="41" t="s">
         <v>485</v>
       </c>
-      <c r="H4" s="42" t="s">
+      <c r="H4" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="31"/>
-      <c r="D5" s="45" t="s">
+      <c r="D5" s="44" t="s">
         <v>483</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="E5" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="41" t="s">
         <v>480</v>
       </c>
-      <c r="G5" s="42" t="s">
+      <c r="G5" s="41" t="s">
         <v>486</v>
       </c>
-      <c r="H5" s="42" t="s">
+      <c r="H5" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="31"/>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="44" t="s">
         <v>483</v>
       </c>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="F6" s="42" t="s">
+      <c r="F6" s="41" t="s">
         <v>480</v>
       </c>
-      <c r="G6" s="42" t="s">
+      <c r="G6" s="41" t="s">
         <v>487</v>
       </c>
-      <c r="H6" s="42" t="s">
+      <c r="H6" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D7" s="45" t="s">
+      <c r="D7" s="44" t="s">
         <v>483</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="F7" s="42" t="s">
+      <c r="F7" s="41" t="s">
         <v>480</v>
       </c>
-      <c r="G7" s="42" t="s">
+      <c r="G7" s="41" t="s">
         <v>488</v>
       </c>
-      <c r="H7" s="42" t="s">
+      <c r="H7" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D8" s="45" t="s">
+      <c r="D8" s="44" t="s">
         <v>483</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="F8" s="42" t="s">
+      <c r="F8" s="41" t="s">
         <v>480</v>
       </c>
-      <c r="G8" s="42" t="s">
+      <c r="G8" s="41" t="s">
         <v>489</v>
       </c>
-      <c r="H8" s="42" t="s">
+      <c r="H8" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D9" s="45" t="s">
+      <c r="D9" s="44" t="s">
         <v>490</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="F9" s="42" t="s">
+      <c r="F9" s="41" t="s">
         <v>491</v>
       </c>
-      <c r="G9" s="42" t="s">
+      <c r="G9" s="41" t="s">
         <v>492</v>
       </c>
-      <c r="H9" s="42" t="s">
+      <c r="H9" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D10" s="45" t="s">
+      <c r="D10" s="44" t="s">
         <v>493</v>
       </c>
-      <c r="E10" s="42" t="s">
+      <c r="E10" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="F10" s="42" t="s">
+      <c r="F10" s="41" t="s">
         <v>491</v>
       </c>
-      <c r="G10" s="42" t="s">
+      <c r="G10" s="41" t="s">
         <v>494</v>
       </c>
-      <c r="H10" s="42" t="s">
+      <c r="H10" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="45" t="s">
+      <c r="D11" s="44" t="s">
         <v>493</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="E11" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="F11" s="42" t="s">
+      <c r="F11" s="41" t="s">
         <v>491</v>
       </c>
-      <c r="G11" s="42" t="s">
+      <c r="G11" s="41" t="s">
         <v>495</v>
       </c>
-      <c r="H11" s="42" t="s">
+      <c r="H11" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D12" s="45" t="s">
+      <c r="D12" s="44" t="s">
         <v>496</v>
       </c>
-      <c r="E12" s="42" t="s">
+      <c r="E12" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="F12" s="42" t="s">
+      <c r="F12" s="41" t="s">
         <v>491</v>
       </c>
-      <c r="G12" s="42" t="s">
+      <c r="G12" s="41" t="s">
         <v>497</v>
       </c>
-      <c r="H12" s="42" t="s">
+      <c r="H12" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D13" s="45" t="s">
+      <c r="D13" s="44" t="s">
         <v>496</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="F13" s="42" t="s">
+      <c r="F13" s="41" t="s">
         <v>491</v>
       </c>
-      <c r="G13" s="42" t="s">
+      <c r="G13" s="41" t="s">
         <v>498</v>
       </c>
-      <c r="H13" s="42" t="s">
+      <c r="H13" s="41" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D14" s="42" t="s">
+      <c r="D14" s="41" t="s">
         <v>499</v>
       </c>
-      <c r="E14" s="42" t="s">
+      <c r="E14" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="F14" s="42" t="s">
+      <c r="F14" s="41" t="s">
         <v>491</v>
       </c>
-      <c r="G14" s="42" t="s">
+      <c r="G14" s="41" t="s">
         <v>500</v>
       </c>
-      <c r="H14" s="42" t="s">
+      <c r="H14" s="41" t="s">
         <v>482</v>
       </c>
       <c r="I14" s="25" t="s">
@@ -9966,19 +9999,19 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="42" t="s">
+      <c r="D15" s="41" t="s">
         <v>499</v>
       </c>
-      <c r="E15" s="42" t="s">
+      <c r="E15" s="41" t="s">
         <v>479</v>
       </c>
-      <c r="F15" s="42" t="s">
+      <c r="F15" s="41" t="s">
         <v>491</v>
       </c>
-      <c r="G15" s="42" t="s">
+      <c r="G15" s="41" t="s">
         <v>502</v>
       </c>
-      <c r="H15" s="42" t="s">
+      <c r="H15" s="41" t="s">
         <v>482</v>
       </c>
       <c r="I15" s="25" t="s">
@@ -9986,13 +10019,13 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D16" s="56"/>
-      <c r="E16" s="47" t="s">
+      <c r="D16" s="55"/>
+      <c r="E16" s="46" t="s">
         <v>479</v>
       </c>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="47" t="s">
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="46" t="s">
         <v>504</v>
       </c>
     </row>
@@ -10067,161 +10100,161 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="57"/>
-      <c r="B2" s="58" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57" t="s">
         <v>677</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57" t="s">
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56" t="s">
         <v>556</v>
       </c>
-      <c r="L2" s="57" t="s">
+      <c r="L2" s="56" t="s">
         <v>479</v>
       </c>
-      <c r="M2" s="57" t="s">
+      <c r="M2" s="56" t="s">
         <v>688</v>
       </c>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="58" t="s">
         <v>471</v>
       </c>
-      <c r="O2" s="57" t="s">
+      <c r="O2" s="56" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="56" t="s">
         <v>620</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57" t="s">
+      <c r="B3" s="57"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56" t="s">
         <v>590</v>
       </c>
-      <c r="L3" s="57" t="s">
+      <c r="L3" s="56" t="s">
         <v>479</v>
       </c>
-      <c r="M3" s="57" t="s">
+      <c r="M3" s="56" t="s">
         <v>688</v>
       </c>
-      <c r="N3" s="59" t="s">
+      <c r="N3" s="58" t="s">
         <v>472</v>
       </c>
-      <c r="O3" s="57" t="s">
+      <c r="O3" s="56" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="56" t="s">
         <v>620</v>
       </c>
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="57" t="s">
         <v>679</v>
       </c>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57" t="s">
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56" t="s">
         <v>593</v>
       </c>
-      <c r="L4" s="57" t="s">
+      <c r="L4" s="56" t="s">
         <v>479</v>
       </c>
-      <c r="M4" s="57" t="s">
+      <c r="M4" s="56" t="s">
         <v>688</v>
       </c>
-      <c r="N4" s="59" t="s">
+      <c r="N4" s="58" t="s">
         <v>473</v>
       </c>
-      <c r="O4" s="57" t="s">
+      <c r="O4" s="56" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="59" t="s">
         <v>620</v>
       </c>
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="60" t="s">
         <v>677</v>
       </c>
-      <c r="C5" s="60" t="s">
+      <c r="C5" s="59" t="s">
         <v>651</v>
       </c>
-      <c r="D5" s="60" t="s">
+      <c r="D5" s="59" t="s">
         <v>681</v>
       </c>
-      <c r="E5" s="60" t="s">
+      <c r="E5" s="59" t="s">
         <v>680</v>
       </c>
-      <c r="F5" s="60" t="s">
+      <c r="F5" s="59" t="s">
         <v>682</v>
       </c>
-      <c r="G5" s="61" t="s">
+      <c r="G5" s="60" t="s">
         <v>683</v>
       </c>
-      <c r="H5" s="63" t="s">
+      <c r="H5" s="62" t="s">
         <v>684</v>
       </c>
-      <c r="I5" s="60" t="s">
+      <c r="I5" s="59" t="s">
         <v>685</v>
       </c>
-      <c r="J5" s="61" t="s">
+      <c r="J5" s="60" t="s">
         <v>686</v>
       </c>
-      <c r="K5" s="60" t="s">
+      <c r="K5" s="59" t="s">
         <v>687</v>
       </c>
-      <c r="L5" s="60" t="s">
+      <c r="L5" s="59" t="s">
         <v>479</v>
       </c>
-      <c r="M5" s="60" t="s">
+      <c r="M5" s="59" t="s">
         <v>688</v>
       </c>
-      <c r="N5" s="62" t="s">
+      <c r="N5" s="61" t="s">
         <v>474</v>
       </c>
-      <c r="O5" s="60" t="s">
+      <c r="O5" s="59" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="59" t="s">
         <v>620</v>
       </c>
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="60" t="s">
         <v>678</v>
       </c>
-      <c r="K6" s="60" t="s">
+      <c r="K6" s="59" t="s">
         <v>687</v>
       </c>
-      <c r="L6" s="60" t="s">
+      <c r="L6" s="59" t="s">
         <v>479</v>
       </c>
-      <c r="M6" s="60" t="s">
+      <c r="M6" s="59" t="s">
         <v>688</v>
       </c>
-      <c r="N6" s="62" t="s">
+      <c r="N6" s="61" t="s">
         <v>475</v>
       </c>
-      <c r="O6" s="60" t="s">
+      <c r="O6" s="59" t="s">
         <v>504</v>
       </c>
     </row>
@@ -10305,169 +10338,169 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="57"/>
-      <c r="B2" s="58" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57" t="s">
         <v>677</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57" t="s">
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56" t="s">
         <v>556</v>
       </c>
-      <c r="L2" s="57" t="s">
+      <c r="L2" s="56" t="s">
         <v>479</v>
       </c>
-      <c r="M2" s="57" t="s">
+      <c r="M2" s="56" t="s">
         <v>688</v>
       </c>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="58" t="s">
         <v>471</v>
       </c>
-      <c r="O2" s="57" t="s">
+      <c r="O2" s="56" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="56" t="s">
         <v>620</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57" t="s">
+      <c r="B3" s="57"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56" t="s">
         <v>590</v>
       </c>
-      <c r="L3" s="57" t="s">
+      <c r="L3" s="56" t="s">
         <v>479</v>
       </c>
-      <c r="M3" s="57" t="s">
+      <c r="M3" s="56" t="s">
         <v>688</v>
       </c>
-      <c r="N3" s="59" t="s">
+      <c r="N3" s="58" t="s">
         <v>472</v>
       </c>
-      <c r="O3" s="57" t="s">
+      <c r="O3" s="56" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="56" t="s">
         <v>620</v>
       </c>
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="57" t="s">
         <v>679</v>
       </c>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57" t="s">
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56" t="s">
         <v>593</v>
       </c>
-      <c r="L4" s="57" t="s">
+      <c r="L4" s="56" t="s">
         <v>479</v>
       </c>
-      <c r="M4" s="57" t="s">
+      <c r="M4" s="56" t="s">
         <v>688</v>
       </c>
-      <c r="N4" s="59" t="s">
+      <c r="N4" s="58" t="s">
         <v>473</v>
       </c>
-      <c r="O4" s="57" t="s">
+      <c r="O4" s="56" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="59" t="s">
         <v>620</v>
       </c>
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="60" t="s">
         <v>677</v>
       </c>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="60" t="s">
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59" t="s">
         <v>687</v>
       </c>
-      <c r="L5" s="60" t="s">
+      <c r="L5" s="59" t="s">
         <v>479</v>
       </c>
-      <c r="M5" s="60" t="s">
+      <c r="M5" s="59" t="s">
         <v>688</v>
       </c>
-      <c r="N5" s="62" t="s">
+      <c r="N5" s="61" t="s">
         <v>474</v>
       </c>
-      <c r="O5" s="60" t="s">
+      <c r="O5" s="59" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="59" t="s">
         <v>620</v>
       </c>
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="60" t="s">
         <v>678</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="59" t="s">
         <v>651</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="59" t="s">
         <v>681</v>
       </c>
-      <c r="E6" s="60" t="s">
+      <c r="E6" s="59" t="s">
         <v>680</v>
       </c>
-      <c r="F6" s="60" t="s">
+      <c r="F6" s="59" t="s">
         <v>682</v>
       </c>
-      <c r="G6" s="61" t="s">
+      <c r="G6" s="60" t="s">
         <v>683</v>
       </c>
-      <c r="H6" s="63" t="s">
+      <c r="H6" s="62" t="s">
         <v>684</v>
       </c>
-      <c r="I6" s="60" t="s">
+      <c r="I6" s="59" t="s">
         <v>685</v>
       </c>
-      <c r="J6" s="61" t="s">
+      <c r="J6" s="60" t="s">
         <v>686</v>
       </c>
-      <c r="K6" s="60" t="s">
+      <c r="K6" s="59" t="s">
         <v>687</v>
       </c>
-      <c r="L6" s="60" t="s">
+      <c r="L6" s="59" t="s">
         <v>479</v>
       </c>
-      <c r="M6" s="60" t="s">
+      <c r="M6" s="59" t="s">
         <v>688</v>
       </c>
-      <c r="N6" s="62" t="s">
+      <c r="N6" s="61" t="s">
         <v>475</v>
       </c>
-      <c r="O6" s="60" t="s">
+      <c r="O6" s="59" t="s">
         <v>504</v>
       </c>
     </row>
@@ -10603,7 +10636,7 @@
     <col min="10" max="10" width="9" style="21" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9.140625" style="21" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="31.28515625" style="21" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.140625" style="64" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" style="63" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9.140625" style="21"/>
   </cols>
   <sheetData>
@@ -10635,19 +10668,19 @@
       <c r="I1" s="24" t="s">
         <v>693</v>
       </c>
-      <c r="J1" s="64"/>
+      <c r="J1" s="63"/>
     </row>
     <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>710</v>
       </c>
-      <c r="B2" s="68">
+      <c r="B2" s="67">
         <v>1</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="66" t="s">
         <v>711</v>
       </c>
-      <c r="D2" s="66" t="s">
+      <c r="D2" s="65" t="s">
         <v>708</v>
       </c>
       <c r="E2" s="24" t="s">
@@ -10665,16 +10698,16 @@
       <c r="I2" s="24" t="s">
         <v>694</v>
       </c>
-      <c r="J2" s="64"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="68">
+      <c r="B3" s="67">
         <v>1</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="66" t="s">
         <v>712</v>
       </c>
-      <c r="D3" s="66" t="s">
+      <c r="D3" s="65" t="s">
         <v>708</v>
       </c>
       <c r="E3" s="24" t="s">
@@ -10692,19 +10725,19 @@
       <c r="I3" s="24" t="s">
         <v>695</v>
       </c>
-      <c r="J3" s="64"/>
+      <c r="J3" s="63"/>
     </row>
     <row r="4" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
         <v>526</v>
       </c>
-      <c r="B4" s="68">
+      <c r="B4" s="67">
         <v>5</v>
       </c>
-      <c r="C4" s="67" t="s">
+      <c r="C4" s="66" t="s">
         <v>713</v>
       </c>
-      <c r="D4" s="66" t="s">
+      <c r="D4" s="65" t="s">
         <v>708</v>
       </c>
       <c r="E4" s="24" t="s">
@@ -10722,7 +10755,7 @@
       <c r="I4" s="24" t="s">
         <v>696</v>
       </c>
-      <c r="J4" s="64"/>
+      <c r="J4" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I5" s="20"/>
@@ -10767,7 +10800,7 @@
     <row r="42" spans="14:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" spans="14:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="44" spans="14:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N44" s="65" t="s">
+      <c r="N44" s="64" t="s">
         <v>457</v>
       </c>
     </row>
